--- a/iniziative/136596/ICD_PREADVISING_LDV_EVENT_SOURCE_v11.xlsx
+++ b/iniziative/136596/ICD_PREADVISING_LDV_EVENT_SOURCE_v11.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracciato unico preadvising" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapping inverso EURODIS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapping EURODIS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EURODIS non mappati" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda mapping" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tracciato unico preadvising" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mapping inverso EURODIS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mapping EURODIS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="EURODIS non mappati" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Legenda mapping" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracciato unico preadvising'!$A$1:$J$577</definedName>
@@ -254,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -361,6 +361,18 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -7120,7 +7132,7 @@
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">
+          <t>
  </t>
         </is>
       </c>
@@ -8157,7 +8169,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D247" s="3" t="n"/>
@@ -13955,7 +13967,7 @@
       </c>
       <c r="I444" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  </t>
+          <t>  </t>
         </is>
       </c>
       <c r="J444" s="3" t="n"/>
@@ -18097,7 +18109,7 @@
     </row>
     <row r="2">
       <c r="A2" s="17" t="n"/>
-      <c r="B2" s="52" t="inlineStr">
+      <c r="B2" s="56" t="inlineStr">
         <is>
           <t>edReference</t>
         </is>
@@ -18108,31 +18120,31 @@
 IT: Numero univoco della spedizione nella rete EURODIS. Per la definizione di dettaglio vedere il documento A02 del manuale di rete EURODIS.</t>
         </is>
       </c>
-      <c r="D2" s="52" t="inlineStr">
+      <c r="D2" s="56" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E2" s="52" t="inlineStr"/>
-      <c r="F2" s="52" t="inlineStr">
+      <c r="E2" s="56" t="inlineStr"/>
+      <c r="F2" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G2" s="52" t="inlineStr">
+      <c r="G2" s="56" t="inlineStr">
         <is>
           <t>spedizione.rif_spedizione</t>
         </is>
       </c>
-      <c r="H2" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="52" t="n">
+      <c r="H2" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="56" t="n">
         <v>25</v>
       </c>
-      <c r="J2" s="53" t="inlineStr">
+      <c r="J2" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -18142,7 +18154,7 @@
           <t>Decisione 22-Oct. Numero decimale (max 13 cifre) -&gt; stringa senza decimali (ICD 25)</t>
         </is>
       </c>
-      <c r="L2" s="52" t="inlineStr">
+      <c r="L2" s="56" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -18150,7 +18162,7 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="n"/>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="56" t="inlineStr">
         <is>
           <t>referencedEurodisShipmentNumber</t>
         </is>
@@ -18161,25 +18173,25 @@
 IT: Numero EURODIS della spedizione originaria. Obbligatorio per i tipi "R", "D" e "A"; condizionato per "P"; facoltativo per "E".</t>
         </is>
       </c>
-      <c r="D3" s="52" t="inlineStr">
+      <c r="D3" s="56" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E3" s="52" t="inlineStr"/>
-      <c r="F3" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G3" s="52" t="inlineStr">
+      <c r="E3" s="56" t="inlineStr"/>
+      <c r="F3" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H3" s="52" t="inlineStr"/>
-      <c r="I3" s="52" t="inlineStr"/>
-      <c r="J3" s="54" t="inlineStr">
+      <c r="H3" s="56" t="inlineStr"/>
+      <c r="I3" s="56" t="inlineStr"/>
+      <c r="J3" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18189,7 +18201,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L3" s="52" t="inlineStr">
+      <c r="L3" s="56" t="inlineStr">
         <is>
           <t>PA-17</t>
         </is>
@@ -18201,7 +18213,7 @@
           <t>[era su spedizione.verso] Campo da ingnorare</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>shipmentTypeIndicator</t>
         </is>
@@ -18212,27 +18224,27 @@
 IT: N = normale; A = ordine di ritiro; P = spedizione risultante da un ordine di ritiro; R = reso; X = AUX-PAN; B = spedizione normale in neighbourhood business (NB); D = reso in NB; E = ritiro in NB; C = spedizione B2C (facoltativo, da concordare fra partner mittente e partner di consegna); Y = B2C in NB; L = richiesta di reso; M = reso dal destinatario (solo verso il partner di consegna iniziale; trasmesso come "R" ai partner di transito e consegna, come "E" in NB); W = spedizione distribuita senza EUROPLATE.</t>
         </is>
       </c>
-      <c r="D4" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E4" s="52" t="n">
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="F4" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="52" t="inlineStr"/>
-      <c r="I4" s="52" t="inlineStr"/>
-      <c r="J4" s="54" t="inlineStr">
+      <c r="H4" s="56" t="inlineStr"/>
+      <c r="I4" s="56" t="inlineStr"/>
+      <c r="J4" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18242,7 +18254,7 @@
           <t>Da ignorare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L4" s="52" t="inlineStr"/>
+      <c r="L4" s="56" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="37" t="inlineStr">
@@ -18250,7 +18262,7 @@
           <t>[era su spedizione.codice_prodotto] Campo da ingnorare</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>lineHaulIndicator</t>
         </is>
@@ -18261,27 +18273,27 @@
 IT: Deve essere "N" (normale), "D" (iniezione diretta) o "L" (trazione diretta).</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E5" s="52" t="n">
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E5" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="52" t="inlineStr">
+      <c r="F5" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="G5" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr"/>
-      <c r="I5" s="52" t="inlineStr"/>
-      <c r="J5" s="54" t="inlineStr">
+      <c r="H5" s="56" t="inlineStr"/>
+      <c r="I5" s="56" t="inlineStr"/>
+      <c r="J5" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18291,7 +18303,7 @@
           <t>Da ignorare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L5" s="52" t="inlineStr"/>
+      <c r="L5" s="56" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="37" t="inlineStr">
@@ -18300,7 +18312,7 @@
 [era su spedizione.ora_spedizione] no questa data ignorala clearanceTimestamp</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="56" t="inlineStr">
         <is>
           <t>clearanceTimestamp</t>
         </is>
@@ -18311,25 +18323,25 @@
 IT: Data e ora di creazione del dataset PAN della spedizione. Es. "2000-01-31T18:30:00.000Z" = 31/01/2000 ore 18:30.</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>date-time</t>
         </is>
       </c>
-      <c r="E6" s="52" t="inlineStr"/>
-      <c r="F6" s="52" t="inlineStr">
+      <c r="E6" s="56" t="inlineStr"/>
+      <c r="F6" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G6" s="52" t="inlineStr">
+      <c r="G6" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="52" t="inlineStr"/>
-      <c r="I6" s="52" t="inlineStr"/>
-      <c r="J6" s="54" t="inlineStr">
+      <c r="H6" s="56" t="inlineStr"/>
+      <c r="I6" s="56" t="inlineStr"/>
+      <c r="J6" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18339,7 +18351,7 @@
           <t>Da ignorare: per data e ora spedizione si usa entranceTimestamp (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L6" s="52" t="inlineStr"/>
+      <c r="L6" s="56" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="37" t="inlineStr">
@@ -18348,7 +18360,7 @@
 spedizione.ora_spedizione e spedizione.data_spedizione</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>entranceTimestamp</t>
         </is>
@@ -18359,41 +18371,41 @@
 IT: Data di ingresso della spedizione nel sistema domestico del partner, cioè quando è stata fisicamente consegnata. Es. "2000-01-31T18:30:00.000Z".</t>
         </is>
       </c>
-      <c r="D7" s="52" t="inlineStr">
+      <c r="D7" s="56" t="inlineStr">
         <is>
           <t>date-time</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr"/>
-      <c r="F7" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G7" s="52" t="inlineStr">
+      <c r="E7" s="56" t="inlineStr"/>
+      <c r="F7" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" s="56" t="inlineStr">
         <is>
           <t>spedizione.data_spedizione</t>
         </is>
       </c>
-      <c r="H7" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I7" s="52" t="n">
+      <c r="H7" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="53" t="inlineStr">
+      <c r="J7" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>yyyy-MM-dd (commento Diego 23-Oct: clearanceTimestamp si ignora)</t>
-        </is>
-      </c>
-      <c r="L7" s="52" t="inlineStr">
+          <t>yyyy-MM-dd (commento Diego 23-Oct: clearanceTimestamp si ignora). Conflitto: il riscontro SDA mappa clearanceTimestamp -&gt; shipmentDate (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L7" s="56" t="inlineStr">
         <is>
           <t>DF-01</t>
         </is>
@@ -18401,7 +18413,7 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="n"/>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="56" t="inlineStr">
         <is>
           <t>entranceTimestamp</t>
         </is>
@@ -18412,31 +18424,31 @@
 IT: Data di ingresso della spedizione nel sistema domestico del partner, cioè quando è stata fisicamente consegnata. Es. "2000-01-31T18:30:00.000Z".</t>
         </is>
       </c>
-      <c r="D8" s="52" t="inlineStr">
+      <c r="D8" s="56" t="inlineStr">
         <is>
           <t>date-time</t>
         </is>
       </c>
-      <c r="E8" s="52" t="inlineStr"/>
-      <c r="F8" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G8" s="52" t="inlineStr">
+      <c r="E8" s="56" t="inlineStr"/>
+      <c r="F8" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" s="56" t="inlineStr">
         <is>
           <t>spedizione.ora_spedizione</t>
         </is>
       </c>
-      <c r="H8" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I8" s="52" t="n">
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="53" t="inlineStr">
+      <c r="J8" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -18446,7 +18458,7 @@
           <t>HH:mm:ss (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L8" s="52" t="inlineStr">
+      <c r="L8" s="56" t="inlineStr">
         <is>
           <t>DF-01</t>
         </is>
@@ -18454,7 +18466,7 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="n"/>
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>numberOfHandlingUnits</t>
         </is>
@@ -18465,31 +18477,31 @@
 IT: Totale di colli e pallet. Deve coincidere con il numero di colli trasmessi.</t>
         </is>
       </c>
-      <c r="D9" s="52" t="inlineStr">
+      <c r="D9" s="56" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E9" s="52" t="inlineStr"/>
-      <c r="F9" s="52" t="inlineStr">
+      <c r="E9" s="56" t="inlineStr"/>
+      <c r="F9" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G9" s="52" t="inlineStr">
+      <c r="G9" s="56" t="inlineStr">
         <is>
           <t>spedizione.numero_colli</t>
         </is>
       </c>
-      <c r="H9" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="52" t="n">
+      <c r="H9" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="55" t="inlineStr">
+      <c r="J9" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18499,11 +18511,11 @@
           <t>Verificare coerenza con len(collis)</t>
         </is>
       </c>
-      <c r="L9" s="52" t="inlineStr"/>
+      <c r="L9" s="56" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n"/>
-      <c r="B10" s="52" t="inlineStr">
+      <c r="B10" s="56" t="inlineStr">
         <is>
           <t>shipmentWeight</t>
         </is>
@@ -18514,29 +18526,29 @@
 IT: Peso in chilogrammi con due decimali.</t>
         </is>
       </c>
-      <c r="D10" s="52" t="inlineStr">
+      <c r="D10" s="56" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E10" s="52" t="inlineStr"/>
-      <c r="F10" s="52" t="inlineStr">
+      <c r="E10" s="56" t="inlineStr"/>
+      <c r="F10" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G10" s="52" t="inlineStr">
+      <c r="G10" s="56" t="inlineStr">
         <is>
           <t>spedizione.internazionale.peso</t>
         </is>
       </c>
-      <c r="H10" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="52" t="n"/>
-      <c r="J10" s="53" t="inlineStr">
+      <c r="H10" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="56" t="n"/>
+      <c r="J10" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -18546,11 +18558,11 @@
           <t>kg -&gt; grammi (x1000)</t>
         </is>
       </c>
-      <c r="L10" s="52" t="inlineStr"/>
+      <c r="L10" s="56" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n"/>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>consignorsCustomerNumberAtDispatchPartner</t>
         </is>
@@ -18560,27 +18572,27 @@
           <t>IT: (Nessuna descrizione nello swagger) Codice cliente del mittente presso il partner che spedisce.</t>
         </is>
       </c>
-      <c r="D11" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E11" s="52" t="n">
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F11" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G11" s="52" t="inlineStr">
+      <c r="F11" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G11" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="52" t="inlineStr"/>
-      <c r="I11" s="52" t="inlineStr"/>
-      <c r="J11" s="54" t="inlineStr">
+      <c r="H11" s="56" t="inlineStr"/>
+      <c r="I11" s="56" t="inlineStr"/>
+      <c r="J11" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18590,11 +18602,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L11" s="52" t="inlineStr"/>
+      <c r="L11" s="56" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n"/>
-      <c r="B12" s="52" t="inlineStr">
+      <c r="B12" s="56" t="inlineStr">
         <is>
           <t>consignorsReference</t>
         </is>
@@ -18604,27 +18616,27 @@
           <t>IT: (Nessuna descrizione nello swagger) Riferimento del mittente.</t>
         </is>
       </c>
-      <c r="D12" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E12" s="52" t="n">
+      <c r="D12" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E12" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F12" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G12" s="52" t="inlineStr">
+      <c r="F12" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G12" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="52" t="inlineStr"/>
-      <c r="I12" s="52" t="inlineStr"/>
-      <c r="J12" s="54" t="inlineStr">
+      <c r="H12" s="56" t="inlineStr"/>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18634,11 +18646,11 @@
           <t>Nessun campo ICD libero (rif_spedizione e' edReference)</t>
         </is>
       </c>
-      <c r="L12" s="52" t="inlineStr"/>
+      <c r="L12" s="56" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n"/>
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
         <is>
           <t>dispatchPartnersDomesticShipmentNumber</t>
         </is>
@@ -18648,33 +18660,33 @@
           <t>IT: (Nessuna descrizione nello swagger) Numero di spedizione domestico del partner che spedisce.</t>
         </is>
       </c>
-      <c r="D13" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E13" s="52" t="n">
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E13" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F13" s="52" t="inlineStr">
+      <c r="F13" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G13" s="52" t="inlineStr">
+      <c r="G13" s="56" t="inlineStr">
         <is>
           <t>spedizione.id_ldv_partner_master</t>
         </is>
       </c>
-      <c r="H13" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="52" t="n">
+      <c r="H13" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="56" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="55" t="inlineStr">
+      <c r="J13" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18684,7 +18696,7 @@
           <t>Numero spedizione del partner mittente (35 &lt;= 50)</t>
         </is>
       </c>
-      <c r="L13" s="52" t="inlineStr">
+      <c r="L13" s="56" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -18696,7 +18708,7 @@
           <t xml:space="preserve">non interessa </t>
         </is>
       </c>
-      <c r="B14" s="52" t="inlineStr">
+      <c r="B14" s="56" t="inlineStr">
         <is>
           <t>truckLicensePlate</t>
         </is>
@@ -18707,27 +18719,27 @@
 IT: Targa del camion (e del rimorchio).</t>
         </is>
       </c>
-      <c r="D14" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E14" s="52" t="n">
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E14" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F14" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G14" s="52" t="inlineStr">
+      <c r="F14" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G14" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="52" t="inlineStr"/>
-      <c r="I14" s="52" t="inlineStr"/>
-      <c r="J14" s="54" t="inlineStr">
+      <c r="H14" s="56" t="inlineStr"/>
+      <c r="I14" s="56" t="inlineStr"/>
+      <c r="J14" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18737,7 +18749,7 @@
           <t>Non interessa (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L14" s="52" t="inlineStr"/>
+      <c r="L14" s="56" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="37" t="inlineStr">
@@ -18746,7 +18758,7 @@
 [era su spedizione.internazionale.addebito_oneri] da non mappare</t>
         </is>
       </c>
-      <c r="B15" s="52" t="inlineStr">
+      <c r="B15" s="56" t="inlineStr">
         <is>
           <t>termsOfDeliveryText</t>
         </is>
@@ -18757,27 +18769,27 @@
 IT: Facoltativo per spedizioni intra-UE, obbligatorio per paesi extra-UE. Deve essere un Incoterm ufficiale DPU o EXW (per ritiri e resi) oppure uno degli Incoterm interni di rete DDC e DDX.</t>
         </is>
       </c>
-      <c r="D15" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E15" s="52" t="n">
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E15" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F15" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G15" s="52" t="inlineStr">
+      <c r="F15" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G15" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="52" t="inlineStr"/>
-      <c r="I15" s="52" t="inlineStr"/>
-      <c r="J15" s="54" t="inlineStr">
+      <c r="H15" s="56" t="inlineStr"/>
+      <c r="I15" s="56" t="inlineStr"/>
+      <c r="J15" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18787,11 +18799,11 @@
           <t>Da non mappare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L15" s="52" t="inlineStr"/>
+      <c r="L15" s="56" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n"/>
-      <c r="B16" s="52" t="inlineStr">
+      <c r="B16" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.contactName</t>
         </is>
@@ -18802,33 +18814,33 @@
 IT: Nome del contatto all'indirizzo, stampato sulla 2a riga indirizzo dell'EUROPLATE. Per le spedizioni PUDO contiene il nome del negozio.</t>
         </is>
       </c>
-      <c r="D16" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E16" s="52" t="n">
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E16" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G16" s="52" t="inlineStr">
+      <c r="F16" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G16" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.rif_contatto</t>
         </is>
       </c>
-      <c r="H16" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" s="52" t="n">
+      <c r="H16" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="J16" s="55" t="inlineStr">
+      <c r="J16" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18838,7 +18850,7 @@
           <t>Valore integrale (sorgente 40, ICD 35): non si tronca</t>
         </is>
       </c>
-      <c r="L16" s="52" t="inlineStr">
+      <c r="L16" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -18846,7 +18858,7 @@
     </row>
     <row r="17">
       <c r="A17" s="17" t="n"/>
-      <c r="B17" s="52" t="inlineStr">
+      <c r="B17" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.contactTelephone</t>
         </is>
@@ -18857,33 +18869,33 @@
 IT: Condizione per il servizio di prenotazione consegna: se il servizio è concordato fra i partner e il flag di prenotazione è presente in DeliveryService.</t>
         </is>
       </c>
-      <c r="D17" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E17" s="52" t="n">
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E17" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="F17" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G17" s="52" t="inlineStr">
+      <c r="F17" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G17" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.telefono</t>
         </is>
       </c>
-      <c r="H17" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I17" s="52" t="n">
+      <c r="H17" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I17" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="J17" s="55" t="inlineStr">
+      <c r="J17" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18893,11 +18905,11 @@
           <t>30 -&gt; 30</t>
         </is>
       </c>
-      <c r="L17" s="52" t="inlineStr"/>
+      <c r="L17" s="56" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n"/>
-      <c r="B18" s="52" t="inlineStr">
+      <c r="B18" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.alternativeContactTelephone</t>
         </is>
@@ -18908,27 +18920,27 @@
 IT: Telefono di contatto alternativo (alfanumerico per ammettere il prefisso internazionale).</t>
         </is>
       </c>
-      <c r="D18" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E18" s="52" t="n">
+      <c r="D18" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E18" s="56" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G18" s="52" t="inlineStr">
+      <c r="F18" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="52" t="inlineStr"/>
-      <c r="I18" s="52" t="inlineStr"/>
-      <c r="J18" s="54" t="inlineStr">
+      <c r="H18" s="56" t="inlineStr"/>
+      <c r="I18" s="56" t="inlineStr"/>
+      <c r="J18" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18938,7 +18950,7 @@
           <t>Il tracciato non ha un secondo numero di telefono: da chiedere se serve (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L18" s="52" t="inlineStr">
+      <c r="L18" s="56" t="inlineStr">
         <is>
           <t>DF-15</t>
         </is>
@@ -18950,7 +18962,7 @@
           <t xml:space="preserve">[era su spedizione.destinatario.prefisso_cellulare] no consigneeAddress.contactSMS tutto su cellulare </t>
         </is>
       </c>
-      <c r="B19" s="52" t="inlineStr">
+      <c r="B19" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.contactSMS</t>
         </is>
@@ -18961,33 +18973,33 @@
 IT: Numero SMS del contatto principale. Formato: prefisso internazionale (+XX) seguito dal numero. Es. +491711234567.</t>
         </is>
       </c>
-      <c r="D19" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E19" s="52" t="n">
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E19" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F19" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G19" s="52" t="inlineStr">
+      <c r="F19" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G19" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.cellulare</t>
         </is>
       </c>
-      <c r="H19" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I19" s="52" t="n">
+      <c r="H19" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="J19" s="55" t="inlineStr">
+      <c r="J19" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18997,7 +19009,7 @@
           <t>Valore integrale, formato +XX... (sorgente 35, ICD 30): non si tronca</t>
         </is>
       </c>
-      <c r="L19" s="52" t="inlineStr">
+      <c r="L19" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19005,7 +19017,7 @@
     </row>
     <row r="20">
       <c r="A20" s="17" t="n"/>
-      <c r="B20" s="52" t="inlineStr">
+      <c r="B20" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.contactEMail</t>
         </is>
@@ -19016,33 +19028,33 @@
 IT: Indirizzo email del contatto principale; vedere anche l'allegato A09 - matrice del servizio di preavviso via email.</t>
         </is>
       </c>
-      <c r="D20" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E20" s="52" t="n">
+      <c r="D20" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E20" s="56" t="n">
         <v>80</v>
       </c>
-      <c r="F20" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G20" s="52" t="inlineStr">
+      <c r="F20" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G20" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.email</t>
         </is>
       </c>
-      <c r="H20" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="52" t="n">
+      <c r="H20" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="56" t="n">
         <v>50</v>
       </c>
-      <c r="J20" s="55" t="inlineStr">
+      <c r="J20" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19052,7 +19064,7 @@
           <t>Valore integrale (sorgente 80, ICD 50): non si tronca</t>
         </is>
       </c>
-      <c r="L20" s="52" t="inlineStr">
+      <c r="L20" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19060,7 +19072,7 @@
     </row>
     <row r="21">
       <c r="A21" s="17" t="n"/>
-      <c r="B21" s="52" t="inlineStr">
+      <c r="B21" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.companyName</t>
         </is>
@@ -19071,33 +19083,33 @@
 IT: Per spedizioni "toB" nome dell'azienda o organizzazione; per spedizioni "toC" nome del destinatario. Stampato sulla 1a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D21" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E21" s="52" t="n">
+      <c r="D21" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F21" s="52" t="inlineStr">
+      <c r="F21" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G21" s="52" t="inlineStr">
+      <c r="G21" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.ragione_sociale</t>
         </is>
       </c>
-      <c r="H21" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I21" s="52" t="n">
+      <c r="H21" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I21" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="J21" s="55" t="inlineStr">
+      <c r="J21" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19107,11 +19119,11 @@
           <t>40 -&gt; 40</t>
         </is>
       </c>
-      <c r="L21" s="52" t="inlineStr"/>
+      <c r="L21" s="56" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n"/>
-      <c r="B22" s="52" t="inlineStr">
+      <c r="B22" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.additionalAddressInfo1</t>
         </is>
@@ -19122,33 +19134,33 @@
 IT: Informazioni aggiuntive sull'indirizzo (reparto, edificio, piano, codice porta, stanza, numero locker...). Stampato sulla 3a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D22" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E22" s="52" t="n">
+      <c r="D22" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F22" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G22" s="52" t="inlineStr">
+      <c r="F22" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G22" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.note1</t>
         </is>
       </c>
-      <c r="H22" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="52" t="n">
+      <c r="H22" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I22" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="J22" s="55" t="inlineStr">
+      <c r="J22" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19158,7 +19170,7 @@
           <t>Valore integrale (sorgente 40): non si tronca</t>
         </is>
       </c>
-      <c r="L22" s="52" t="inlineStr">
+      <c r="L22" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19166,7 +19178,7 @@
     </row>
     <row r="23">
       <c r="A23" s="17" t="n"/>
-      <c r="B23" s="52" t="inlineStr">
+      <c r="B23" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.additionalAddressInfo2</t>
         </is>
@@ -19177,33 +19189,33 @@
 IT: Informazioni aggiuntive sull'indirizzo (reparto, edificio, piano, codice porta, stanza, numero locker...). Stampato sulla 4a riga indirizzo dell'EUROPLATE. Per le spedizioni PUDO contiene PS (Parcel Shop) o PT (Parcel Terminal).</t>
         </is>
       </c>
-      <c r="D23" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E23" s="52" t="n">
+      <c r="D23" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E23" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F23" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G23" s="52" t="inlineStr">
+      <c r="F23" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G23" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.note2</t>
         </is>
       </c>
-      <c r="H23" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I23" s="52" t="n">
+      <c r="H23" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I23" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="J23" s="55" t="inlineStr">
+      <c r="J23" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19213,7 +19225,7 @@
           <t>Valore integrale (sorgente 40): non si tronca</t>
         </is>
       </c>
-      <c r="L23" s="52" t="inlineStr">
+      <c r="L23" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19221,7 +19233,7 @@
     </row>
     <row r="24">
       <c r="A24" s="17" t="n"/>
-      <c r="B24" s="52" t="inlineStr">
+      <c r="B24" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.street</t>
         </is>
@@ -19232,33 +19244,33 @@
 IT: Via + numero civico, se il civico non è trasmesso a parte nel campo StreetNumber. Stampato sulla 5a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D24" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E24" s="52" t="n">
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E24" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F24" s="52" t="inlineStr">
+      <c r="F24" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G24" s="52" t="inlineStr">
+      <c r="G24" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.indirizzo</t>
         </is>
       </c>
-      <c r="H24" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="52" t="n">
+      <c r="H24" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="J24" s="55" t="inlineStr">
+      <c r="J24" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19268,11 +19280,11 @@
           <t>40 -&gt; 40</t>
         </is>
       </c>
-      <c r="L24" s="52" t="inlineStr"/>
+      <c r="L24" s="56" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n"/>
-      <c r="B25" s="52" t="inlineStr">
+      <c r="B25" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.streetNumber</t>
         </is>
@@ -19283,33 +19295,33 @@
 IT: Numero civico, stampato sulla 5a riga dell'EUROPLATE. Solo se il sistema del partner mittente supporta la trasmissione separata del civico; altrimenti il civico va nello stesso campo della via.</t>
         </is>
       </c>
-      <c r="D25" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E25" s="52" t="n">
+      <c r="D25" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E25" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F25" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G25" s="52" t="inlineStr">
+      <c r="F25" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G25" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.numero_civico</t>
         </is>
       </c>
-      <c r="H25" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I25" s="52" t="n">
+      <c r="H25" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I25" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J25" s="55" t="inlineStr">
+      <c r="J25" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19319,7 +19331,7 @@
           <t>Valore integrale (sorgente 40, ICD 5): non si tronca</t>
         </is>
       </c>
-      <c r="L25" s="52" t="inlineStr">
+      <c r="L25" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19327,7 +19339,7 @@
     </row>
     <row r="26">
       <c r="A26" s="17" t="n"/>
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.region</t>
         </is>
@@ -19338,33 +19350,33 @@
 IT: Regione, provincia o contea.</t>
         </is>
       </c>
-      <c r="D26" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E26" s="52" t="n">
+      <c r="D26" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E26" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F26" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G26" s="52" t="inlineStr">
+      <c r="F26" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G26" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.provincia</t>
         </is>
       </c>
-      <c r="H26" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I26" s="52" t="n">
+      <c r="H26" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="54" t="inlineStr">
+      <c r="J26" s="58" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -19374,7 +19386,7 @@
           <t>region (40, testo libero) non e' la sigla provincia: valorizzare solo se IT e sigla valida, altrimenti lasciare alla normalizzazione</t>
         </is>
       </c>
-      <c r="L26" s="52" t="inlineStr">
+      <c r="L26" s="56" t="inlineStr">
         <is>
           <t>PA-22</t>
         </is>
@@ -19382,7 +19394,7 @@
     </row>
     <row r="27">
       <c r="A27" s="17" t="n"/>
-      <c r="B27" s="52" t="inlineStr">
+      <c r="B27" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.city</t>
         </is>
@@ -19393,33 +19405,33 @@
 IT: Città o località postale, stampata sulla 6a riga dell'EUROPLATE troncata a 30 caratteri.</t>
         </is>
       </c>
-      <c r="D27" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="52" t="n">
+      <c r="D27" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E27" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F27" s="52" t="inlineStr">
+      <c r="F27" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G27" s="52" t="inlineStr">
+      <c r="G27" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.localita</t>
         </is>
       </c>
-      <c r="H27" s="52" t="inlineStr">
+      <c r="H27" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I27" s="52" t="n">
+      <c r="I27" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="J27" s="55" t="inlineStr">
+      <c r="J27" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19429,11 +19441,11 @@
           <t>Obbligatorio ICD; obbligatorio anche in EURODIS</t>
         </is>
       </c>
-      <c r="L27" s="52" t="inlineStr"/>
+      <c r="L27" s="56" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n"/>
-      <c r="B28" s="52" t="inlineStr">
+      <c r="B28" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.zipcode</t>
         </is>
@@ -19444,33 +19456,33 @@
 IT: CAP, stampato sulla 6a riga dell'EUROPLATE (alfanumerico per il Regno Unito, senza indicatore di nazione; formato validato, corrispondenza con l'indirizzo no).</t>
         </is>
       </c>
-      <c r="D28" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="52" t="n">
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F28" s="52" t="inlineStr">
+      <c r="F28" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G28" s="52" t="inlineStr">
+      <c r="G28" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.cap</t>
         </is>
       </c>
-      <c r="H28" s="52" t="inlineStr">
+      <c r="H28" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I28" s="52" t="n">
+      <c r="I28" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="J28" s="55" t="inlineStr">
+      <c r="J28" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19480,11 +19492,11 @@
           <t>Obbligatorio ICD; obbligatorio anche in EURODIS</t>
         </is>
       </c>
-      <c r="L28" s="52" t="inlineStr"/>
+      <c r="L28" s="56" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>
-      <c r="B29" s="52" t="inlineStr">
+      <c r="B29" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.countryCode</t>
         </is>
@@ -19495,33 +19507,33 @@
 IT: Codice nazione ISO 3166 alpha-2, verificato sul database della piattaforma. Stampato sulla 6a riga dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D29" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E29" s="52" t="n">
+      <c r="D29" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E29" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="52" t="inlineStr">
+      <c r="F29" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G29" s="52" t="inlineStr">
+      <c r="G29" s="56" t="inlineStr">
         <is>
           <t>spedizione.destinatario.codice_nazione_iso_2</t>
         </is>
       </c>
-      <c r="H29" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I29" s="52" t="n">
+      <c r="H29" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="55" t="inlineStr">
+      <c r="J29" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19531,11 +19543,11 @@
           <t>countryCode e' ISO2: va solo qui (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L29" s="52" t="inlineStr"/>
+      <c r="L29" s="56" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n"/>
-      <c r="B30" s="52" t="inlineStr">
+      <c r="B30" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.additionalConsigneeInfo</t>
         </is>
@@ -19546,31 +19558,31 @@
 IT: Informazioni aggiuntive del mittente per il destinatario o istruzioni di consegna.</t>
         </is>
       </c>
-      <c r="D30" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E30" s="52" t="n">
+      <c r="D30" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E30" s="56" t="n">
         <v>70</v>
       </c>
-      <c r="F30" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G30" s="52" t="inlineStr">
+      <c r="F30" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G30" s="56" t="inlineStr">
         <is>
           <t>spedizione.consegna.note</t>
         </is>
       </c>
-      <c r="H30" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="52" t="n"/>
-      <c r="J30" s="53" t="inlineStr">
+      <c r="H30" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="56" t="n"/>
+      <c r="J30" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -19580,11 +19592,11 @@
           <t>Istruzioni di consegna: concatenare i due campi se entrambi presenti (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L30" s="52" t="inlineStr"/>
+      <c r="L30" s="56" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n"/>
-      <c r="B31" s="52" t="inlineStr">
+      <c r="B31" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.gatewayAssigned</t>
         </is>
@@ -19595,27 +19607,27 @@
 IT: Codice del gateway assegnato all'indirizzo (gateway di ingresso per l'indirizzo di consegna, di uscita per quello del mittente), come da manuale di rete A12.</t>
         </is>
       </c>
-      <c r="D31" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E31" s="52" t="n">
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E31" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G31" s="52" t="inlineStr">
+      <c r="F31" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G31" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H31" s="52" t="inlineStr"/>
-      <c r="I31" s="52" t="inlineStr"/>
-      <c r="J31" s="54" t="inlineStr">
+      <c r="H31" s="56" t="inlineStr"/>
+      <c r="I31" s="56" t="inlineStr"/>
+      <c r="J31" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -19625,15 +19637,15 @@
           <t>Da non mappare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L31" s="52" t="inlineStr"/>
+      <c r="L31" s="56" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">[era su spedizione.codici_servizi] da non mappare ma mettilo come punto aperto di sevirita bassa </t>
-        </is>
-      </c>
-      <c r="B32" s="52" t="inlineStr">
+          <t xml:space="preserve">[era su —] [era su spedizione.codici_servizi] da non mappare ma mettilo come punto aperto di sevirita bassa </t>
+        </is>
+      </c>
+      <c r="B32" s="56" t="inlineStr">
         <is>
           <t>consigneeAddress.pudoID</t>
         </is>
@@ -19644,2384 +19656,2397 @@
 IT: Id della stazione PUDO (punto di ritiro e consegna) per le spedizioni con servizio di consegna Z.</t>
         </is>
       </c>
-      <c r="D32" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E32" s="52" t="n">
+      <c r="D32" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E32" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F32" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G32" s="52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="52" t="inlineStr"/>
-      <c r="I32" s="52" t="inlineStr"/>
-      <c r="J32" s="54" t="inlineStr">
-        <is>
-          <t>NON MAPPATO</t>
+      <c r="F32" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G32" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.codici_servizi</t>
+        </is>
+      </c>
+      <c r="H32" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I32" s="56" t="n">
+        <v>255</v>
+      </c>
+      <c r="J32" s="57" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
         </is>
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
-          <t>Da non mappare per ora (commento Diego 23-Oct)</t>
-        </is>
-      </c>
-      <c r="L32" s="52" t="inlineStr">
-        <is>
-          <t>DF-14</t>
+          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, W, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
+        </is>
+      </c>
+      <c r="L32" s="56" t="inlineStr">
+        <is>
+          <t>DF-05, DF-07, DF-21, DF-22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n"/>
-      <c r="B33" s="52" t="inlineStr">
+      <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>consigneeAddress.pudoID</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Id of the PUDO (Pick-up and Drop-off) station for shipments with delivery service Z
+IT: Id della stazione PUDO (punto di ritiro e consegna) per le spedizioni con servizio di consegna Z.</t>
+        </is>
+      </c>
+      <c r="D33" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E33" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="F33" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G33" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.consegna.codice_frazionario</t>
+        </is>
+      </c>
+      <c r="H33" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="J33" s="57" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>Solo con deliveryService = Z: PUDO ID, e' il node di APT000947 (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L33" s="56" t="inlineStr">
+        <is>
+          <t>DF-14, DF-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="n"/>
+      <c r="B34" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.contactName</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Contact name at the address, printed on EUROPLATE address 2. line
 IT: Nome del contatto all'indirizzo, stampato sulla 2a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D33" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E33" s="52" t="n">
+      <c r="D34" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E34" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F33" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G33" s="52" t="inlineStr">
+      <c r="F34" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G34" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.rif_contatto</t>
         </is>
       </c>
-      <c r="H33" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="52" t="n">
+      <c r="H34" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="J33" s="55" t="inlineStr">
+      <c r="J34" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K33" s="17" t="inlineStr">
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>Valore integrale (sorgente 40, ICD 35): non si tronca</t>
         </is>
       </c>
-      <c r="L33" s="52" t="inlineStr">
+      <c r="L34" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="17" t="n"/>
-      <c r="B34" s="52" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="17" t="n"/>
+      <c r="B35" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.contactTelephone</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>Condition for booking-in service: if booking in service is bil. agreed between partners and booking in flag is provided in DeliveryService
 IT: Condizione per il servizio di prenotazione consegna: se il servizio è concordato fra i partner e il flag di prenotazione è presente in DeliveryService.</t>
         </is>
       </c>
-      <c r="D34" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E34" s="52" t="n">
+      <c r="D35" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E35" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="F34" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G34" s="52" t="inlineStr">
+      <c r="F35" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G35" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.telefono</t>
         </is>
       </c>
-      <c r="H34" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="52" t="n">
+      <c r="H35" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="J34" s="55" t="inlineStr">
+      <c r="J35" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K34" s="17" t="inlineStr">
+      <c r="K35" s="17" t="inlineStr">
         <is>
           <t>30 -&gt; 30</t>
         </is>
       </c>
-      <c r="L34" s="52" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="L35" s="56" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">segna che noi non abbiamo il seconod numero di telegono da chiedere se serve </t>
         </is>
       </c>
-      <c r="B35" s="52" t="inlineStr">
+      <c r="B36" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.alternativeContactTelephone</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Alternative contact telephone (alpha to account for international dialling code)
 IT: Telefono di contatto alternativo (alfanumerico per ammettere il prefisso internazionale).</t>
         </is>
       </c>
-      <c r="D35" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E35" s="52" t="n">
+      <c r="D36" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E36" s="56" t="n">
         <v>20</v>
       </c>
-      <c r="F35" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G35" s="52" t="inlineStr">
+      <c r="F36" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G36" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H35" s="52" t="inlineStr"/>
-      <c r="I35" s="52" t="inlineStr"/>
-      <c r="J35" s="54" t="inlineStr">
+      <c r="H36" s="56" t="inlineStr"/>
+      <c r="I36" s="56" t="inlineStr"/>
+      <c r="J36" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K35" s="17" t="inlineStr">
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>Il tracciato non ha un secondo numero di telefono: da chiedere se serve (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L35" s="52" t="inlineStr">
+      <c r="L36" s="56" t="inlineStr">
         <is>
           <t>DF-15</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="52" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="17" t="n"/>
+      <c r="B37" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.contactSMS</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>SMS number for primary contact. Format: country prefix (+XX) followed by the phone number. Example +491711234567
 IT: Numero SMS del contatto principale. Formato: prefisso internazionale (+XX) seguito dal numero. Es. +491711234567.</t>
         </is>
       </c>
-      <c r="D36" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E36" s="52" t="n">
+      <c r="D37" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E37" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F36" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G36" s="52" t="inlineStr">
+      <c r="F37" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G37" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.cellulare</t>
         </is>
       </c>
-      <c r="H36" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I36" s="52" t="n">
+      <c r="H37" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I37" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="J36" s="55" t="inlineStr">
+      <c r="J37" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K36" s="17" t="inlineStr">
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>Valore integrale, formato +XX... (sorgente 35, ICD 30): non si tronca</t>
         </is>
       </c>
-      <c r="L36" s="52" t="inlineStr">
+      <c r="L37" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="n"/>
-      <c r="B37" s="52" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="n"/>
+      <c r="B38" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.contactEMail</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>EMail address of primary contact, see also Annex A09 - E-Mail Pre-advice Service Matrix
 IT: Indirizzo email del contatto principale; vedere anche l'allegato A09 - matrice del servizio di preavviso via email.</t>
         </is>
       </c>
-      <c r="D37" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E37" s="52" t="n">
+      <c r="D38" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E38" s="56" t="n">
         <v>80</v>
       </c>
-      <c r="F37" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G37" s="52" t="inlineStr">
+      <c r="F38" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G38" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.email</t>
         </is>
       </c>
-      <c r="H37" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I37" s="52" t="n">
+      <c r="H38" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="56" t="n">
         <v>50</v>
       </c>
-      <c r="J37" s="55" t="inlineStr">
+      <c r="J38" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K37" s="17" t="inlineStr">
+      <c r="K38" s="17" t="inlineStr">
         <is>
           <t>Valore integrale (sorgente 80, ICD 50): non si tronca</t>
         </is>
       </c>
-      <c r="L37" s="52" t="inlineStr">
+      <c r="L38" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="n"/>
-      <c r="B38" s="52" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="17" t="n"/>
+      <c r="B39" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.companyName</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>For "toB" shipments name of the company or organisation; for "toC" shipments name of the receiver; printed on EUROPLATE address 1.line
 IT: Per spedizioni "toB" nome dell'azienda o organizzazione; per spedizioni "toC" nome del destinatario. Stampato sulla 1a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D38" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E38" s="52" t="n">
+      <c r="D39" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E39" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F38" s="52" t="inlineStr">
+      <c r="F39" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G38" s="52" t="inlineStr">
+      <c r="G39" s="56" t="inlineStr">
         <is>
           <t>cliente.ragione_sociale</t>
         </is>
       </c>
-      <c r="H38" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" s="52" t="n"/>
-      <c r="J38" s="55" t="inlineStr">
+      <c r="H39" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="56" t="n"/>
+      <c r="J39" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K38" s="17" t="inlineStr">
+      <c r="K39" s="17" t="inlineStr">
         <is>
           <t>nell'esempio EUD_INVIOFILE coincide con la ragione sociale del mittente</t>
         </is>
       </c>
-      <c r="L38" s="52" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="n"/>
-      <c r="B39" s="52" t="inlineStr">
+      <c r="L39" s="56" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="n"/>
+      <c r="B40" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.companyName</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>For "toB" shipments name of the company or organisation; for "toC" shipments name of the receiver; printed on EUROPLATE address 1.line
 IT: Per spedizioni "toB" nome dell'azienda o organizzazione; per spedizioni "toC" nome del destinatario. Stampato sulla 1a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D39" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E39" s="52" t="n">
+      <c r="D40" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E40" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F39" s="52" t="inlineStr">
+      <c r="F40" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G39" s="52" t="inlineStr">
+      <c r="G40" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.ragione_sociale</t>
         </is>
       </c>
-      <c r="H39" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="52" t="n">
+      <c r="H40" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I40" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="J39" s="55" t="inlineStr">
+      <c r="J40" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K39" s="17" t="inlineStr">
+      <c r="K40" s="17" t="inlineStr">
         <is>
           <t>40 -&gt; 40</t>
         </is>
       </c>
-      <c r="L39" s="52" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="n"/>
-      <c r="B40" s="52" t="inlineStr">
+      <c r="L40" s="56" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="n"/>
+      <c r="B41" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.additionalAddressInfo1</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>To be used to indicate additional address information like department, building name, floor, door code (i.e digicode France), room number, parcel machine number etc. printed on EUROPLATE address 3.line
 IT: Informazioni aggiuntive sull'indirizzo (reparto, edificio, piano, codice porta, stanza, numero locker...). Stampato sulla 3a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D40" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E40" s="52" t="n">
+      <c r="D41" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F40" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G40" s="52" t="inlineStr">
+      <c r="F41" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G41" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.note1</t>
         </is>
       </c>
-      <c r="H40" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I40" s="52" t="n">
+      <c r="H41" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="J40" s="55" t="inlineStr">
+      <c r="J41" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K40" s="17" t="inlineStr">
+      <c r="K41" s="17" t="inlineStr">
         <is>
           <t>Valore integrale (sorgente 40): non si tronca</t>
         </is>
       </c>
-      <c r="L40" s="52" t="inlineStr">
+      <c r="L41" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="17" t="n"/>
-      <c r="B41" s="52" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="17" t="n"/>
+      <c r="B42" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.additionalAddressInfo2</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>To be used to indicate additional address information like department, building name, flor, door code (i.e digicode France), room number, parcel machine number etc. printed on EUROPLATE address 4.line
 IT: Informazioni aggiuntive sull'indirizzo (reparto, edificio, piano, codice porta, stanza, numero locker...). Stampato sulla 4a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D41" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E41" s="52" t="n">
+      <c r="D42" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E42" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F41" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G41" s="52" t="inlineStr">
+      <c r="F42" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G42" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.note2</t>
         </is>
       </c>
-      <c r="H41" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="52" t="n">
+      <c r="H42" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="J41" s="55" t="inlineStr">
+      <c r="J42" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K41" s="17" t="inlineStr">
+      <c r="K42" s="17" t="inlineStr">
         <is>
           <t>Valore integrale (sorgente 40): non si tronca</t>
         </is>
       </c>
-      <c r="L41" s="52" t="inlineStr">
+      <c r="L42" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="17" t="n"/>
-      <c r="B42" s="52" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="17" t="n"/>
+      <c r="B43" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.street</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>Street + Street number, if street number is not transmitted separately in field StreetNumber; printed on EUROPLATE address 5 line
 IT: Via + numero civico, se il civico non è trasmesso a parte nel campo StreetNumber. Stampato sulla 5a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D42" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E42" s="52" t="n">
+      <c r="D43" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E43" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F42" s="52" t="inlineStr">
+      <c r="F43" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G42" s="52" t="inlineStr">
+      <c r="G43" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.indirizzo</t>
         </is>
       </c>
-      <c r="H42" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="52" t="n">
+      <c r="H43" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="J42" s="55" t="inlineStr">
+      <c r="J43" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K42" s="17" t="inlineStr">
+      <c r="K43" s="17" t="inlineStr">
         <is>
           <t>40 -&gt; 40</t>
         </is>
       </c>
-      <c r="L42" s="52" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="n"/>
-      <c r="B43" s="52" t="inlineStr">
+      <c r="L43" s="56" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="n"/>
+      <c r="B44" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.streetNumber</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>Street number printed on EUROPLATE address 5. line Condition: In case the dispatch partner's IT system supports the separated transmission of the street number. If the dispatch partner’s IT system does not support a separate transmission for street number, the street number must be provided in the same field as for the street name
 IT: Numero civico, stampato sulla 5a riga dell'EUROPLATE. Solo se il sistema del partner mittente supporta la trasmissione separata del civico; altrimenti il civico va nello stesso campo della via.</t>
         </is>
       </c>
-      <c r="D43" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E43" s="52" t="n">
+      <c r="D44" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E44" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F43" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G43" s="52" t="inlineStr">
+      <c r="F44" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G44" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.numero_civico</t>
         </is>
       </c>
-      <c r="H43" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="52" t="n">
+      <c r="H44" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J43" s="55" t="inlineStr">
+      <c r="J44" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K43" s="17" t="inlineStr">
+      <c r="K44" s="17" t="inlineStr">
         <is>
           <t>Valore integrale (sorgente 40, ICD 5): non si tronca</t>
         </is>
       </c>
-      <c r="L43" s="52" t="inlineStr">
+      <c r="L44" s="56" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="17" t="n"/>
-      <c r="B44" s="52" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="17" t="n"/>
+      <c r="B45" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.region</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>Field to indicate region, province, county
 IT: Regione, provincia o contea.</t>
         </is>
       </c>
-      <c r="D44" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E44" s="52" t="n">
+      <c r="D45" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E45" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F44" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G44" s="52" t="inlineStr">
+      <c r="F45" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G45" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.provincia</t>
         </is>
       </c>
-      <c r="H44" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I44" s="52" t="n">
+      <c r="H45" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J44" s="54" t="inlineStr">
+      <c r="J45" s="58" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
       </c>
-      <c r="K44" s="17" t="inlineStr">
+      <c r="K45" s="17" t="inlineStr">
         <is>
           <t>region (40, testo libero) non e' la sigla provincia: valorizzare solo se IT e sigla valida, altrimenti lasciare alla normalizzazione</t>
         </is>
       </c>
-      <c r="L44" s="52" t="inlineStr">
+      <c r="L45" s="56" t="inlineStr">
         <is>
           <t>PA-22</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="17" t="n"/>
-      <c r="B45" s="52" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="17" t="n"/>
+      <c r="B46" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.city</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>City or Post Town printed on EUROPLATE address 6. line cut down to 30 digits
 IT: Città o località postale, stampata sulla 6a riga dell'EUROPLATE troncata a 30 caratteri.</t>
         </is>
       </c>
-      <c r="D45" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E45" s="52" t="n">
+      <c r="D46" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E46" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F45" s="52" t="inlineStr">
+      <c r="F46" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G45" s="52" t="inlineStr">
+      <c r="G46" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.localita</t>
         </is>
       </c>
-      <c r="H45" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="52" t="n">
+      <c r="H46" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="J45" s="55" t="inlineStr">
+      <c r="J46" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K45" s="17" t="inlineStr">
+      <c r="K46" s="17" t="inlineStr">
         <is>
           <t>35 -&gt; 40</t>
         </is>
       </c>
-      <c r="L45" s="52" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="52" t="inlineStr">
+      <c r="L46" s="56" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="n"/>
+      <c r="B47" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.zipcode</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>Zip code printed on EUROPLATE address 6. line (alpha to account for UK, no country indicator to be included, post code format to be validated but not validated to address)
 IT: CAP, stampato sulla 6a riga dell'EUROPLATE (alfanumerico per il Regno Unito, senza indicatore di nazione; formato validato, corrispondenza con l'indirizzo no).</t>
         </is>
       </c>
-      <c r="D46" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E46" s="52" t="n">
+      <c r="D47" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E47" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F46" s="52" t="inlineStr">
+      <c r="F47" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G46" s="52" t="inlineStr">
+      <c r="G47" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.cap</t>
         </is>
       </c>
-      <c r="H46" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I46" s="52" t="n">
+      <c r="H47" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="J46" s="55" t="inlineStr">
+      <c r="J47" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K46" s="17" t="inlineStr">
+      <c r="K47" s="17" t="inlineStr">
         <is>
           <t>9 -&gt; 9. CAP esteri ammessi</t>
         </is>
       </c>
-      <c r="L46" s="52" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="37" t="inlineStr">
+      <c r="L47" s="56" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="37" t="inlineStr">
         <is>
           <t>[era su spedizione.importi.nazione_mittente_iso_cc] shipperAddress.countryCode Da descrizione è ISO due quindi va rimmappato solo dentro codice_nazione_iso_2 e non negli altri campi 
 [era su spedizione.tipo_spedizione] questo è proprio sbagliato non centra nulla tipo_spedizione</t>
         </is>
       </c>
-      <c r="B47" s="52" t="inlineStr">
+      <c r="B48" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.countryCode</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>Country code (ISO 3166- 2 alpha country code list checked against platform database); printed on EUROPLATE address 6. line
 IT: Codice nazione ISO 3166 alpha-2, verificato sul database della piattaforma. Stampato sulla 6a riga dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D47" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E47" s="52" t="n">
+      <c r="D48" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E48" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="52" t="inlineStr">
+      <c r="F48" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G47" s="52" t="inlineStr">
+      <c r="G48" s="56" t="inlineStr">
         <is>
           <t>spedizione.mittente.codice_nazione_iso_2</t>
         </is>
       </c>
-      <c r="H47" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I47" s="52" t="n">
+      <c r="H48" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I48" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J47" s="55" t="inlineStr">
+      <c r="J48" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K47" s="17" t="inlineStr">
+      <c r="K48" s="17" t="inlineStr">
         <is>
           <t>countryCode e' ISO2: va solo qui (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L47" s="52" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="37" t="inlineStr">
+      <c r="L48" s="56" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">[era su —] dovrsti avere note anche dentro consegna </t>
         </is>
       </c>
-      <c r="B48" s="52" t="inlineStr">
+      <c r="B49" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.additionalConsigneeInfo</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>Additional information from shipper to consignee or delivery instructions
 IT: Informazioni aggiuntive del mittente per il destinatario o istruzioni di consegna.</t>
         </is>
       </c>
-      <c r="D48" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E48" s="52" t="n">
+      <c r="D49" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E49" s="56" t="n">
         <v>70</v>
       </c>
-      <c r="F48" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G48" s="52" t="inlineStr">
+      <c r="F49" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G49" s="56" t="inlineStr">
         <is>
           <t>spedizione.consegna.note</t>
         </is>
       </c>
-      <c r="H48" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I48" s="52" t="n"/>
-      <c r="J48" s="53" t="inlineStr">
+      <c r="H49" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I49" s="56" t="n"/>
+      <c r="J49" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
-      <c r="K48" s="17" t="inlineStr">
+      <c r="K49" s="17" t="inlineStr">
         <is>
           <t>Istruzioni di consegna: concatenare i due campi se entrambi presenti (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L48" s="52" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="37" t="inlineStr">
+      <c r="L49" s="56" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="37" t="inlineStr">
         <is>
           <t>no n mappare</t>
         </is>
       </c>
-      <c r="B49" s="52" t="inlineStr">
+      <c r="B50" s="56" t="inlineStr">
         <is>
           <t>shipperAddress.gatewayAssigned</t>
         </is>
       </c>
-      <c r="C49" s="17" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>Gateway code assigned to the address (e.g. Inbound gateway for delivery address, Outbound gateway for shippers’ address) as defined in A12 Network manual
 IT: Codice del gateway assegnato all'indirizzo (gateway di ingresso per l'indirizzo di consegna, di uscita per quello del mittente), come da manuale di rete A12.</t>
         </is>
       </c>
-      <c r="D49" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E49" s="52" t="n">
+      <c r="D50" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E50" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="F49" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G49" s="52" t="inlineStr">
+      <c r="F50" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G50" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H49" s="52" t="inlineStr"/>
-      <c r="I49" s="52" t="inlineStr"/>
-      <c r="J49" s="54" t="inlineStr">
+      <c r="H50" s="56" t="inlineStr"/>
+      <c r="I50" s="56" t="inlineStr"/>
+      <c r="J50" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K49" s="17" t="inlineStr">
+      <c r="K50" s="17" t="inlineStr">
         <is>
           <t>Da non mappare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L49" s="52" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="52" t="inlineStr">
-        <is>
-          <t>returnAddress</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>IT: (Oggetto) Indirizzo di reso.</t>
-        </is>
-      </c>
-      <c r="D50" s="52" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E50" s="52" t="inlineStr"/>
-      <c r="F50" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G50" s="52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="52" t="inlineStr"/>
-      <c r="I50" s="52" t="inlineStr"/>
-      <c r="J50" s="54" t="inlineStr">
-        <is>
-          <t>NON MAPPATO</t>
-        </is>
-      </c>
-      <c r="K50" s="17" t="inlineStr">
-        <is>
-          <t>Nessun oggetto ICD per indirizzo di reso</t>
-        </is>
-      </c>
-      <c r="L50" s="52" t="inlineStr">
-        <is>
-          <t>PA-17</t>
-        </is>
-      </c>
+      <c r="L50" s="56" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n"/>
-      <c r="B51" s="52" t="inlineStr">
-        <is>
-          <t>remunerationAddress</t>
+      <c r="B51" s="56" t="inlineStr">
+        <is>
+          <t>returnAddress</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>IT: (Oggetto) Indirizzo di fatturazione/remunerazione.</t>
-        </is>
-      </c>
-      <c r="D51" s="52" t="inlineStr">
+          <t>IT: (Oggetto) Indirizzo di reso.</t>
+        </is>
+      </c>
+      <c r="D51" s="56" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E51" s="52" t="inlineStr"/>
-      <c r="F51" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G51" s="52" t="inlineStr">
+      <c r="E51" s="56" t="inlineStr"/>
+      <c r="F51" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G51" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H51" s="52" t="inlineStr"/>
-      <c r="I51" s="52" t="inlineStr"/>
-      <c r="J51" s="54" t="inlineStr">
+      <c r="H51" s="56" t="inlineStr"/>
+      <c r="I51" s="56" t="inlineStr"/>
+      <c r="J51" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
       <c r="K51" s="17" t="inlineStr">
         <is>
-          <t>Nessun oggetto ICD</t>
-        </is>
-      </c>
-      <c r="L51" s="52" t="inlineStr"/>
+          <t>Nessun oggetto ICD per indirizzo di reso</t>
+        </is>
+      </c>
+      <c r="L51" s="56" t="inlineStr">
+        <is>
+          <t>PA-17</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="n"/>
-      <c r="B52" s="52" t="inlineStr">
+      <c r="B52" s="56" t="inlineStr">
+        <is>
+          <t>remunerationAddress</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>IT: (Oggetto) Indirizzo di fatturazione/remunerazione.</t>
+        </is>
+      </c>
+      <c r="D52" s="56" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E52" s="56" t="inlineStr"/>
+      <c r="F52" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G52" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="56" t="inlineStr"/>
+      <c r="I52" s="56" t="inlineStr"/>
+      <c r="J52" s="58" t="inlineStr">
+        <is>
+          <t>NON MAPPATO</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
+        <is>
+          <t>Nessun oggetto ICD</t>
+        </is>
+      </c>
+      <c r="L52" s="56" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="n"/>
+      <c r="B53" s="56" t="inlineStr">
         <is>
           <t>bookingInAddress</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>IT: (Oggetto) Indirizzo per la prenotazione della consegna.</t>
         </is>
       </c>
-      <c r="D52" s="52" t="inlineStr">
+      <c r="D53" s="56" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E52" s="52" t="inlineStr"/>
-      <c r="F52" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G52" s="52" t="inlineStr">
+      <c r="E53" s="56" t="inlineStr"/>
+      <c r="F53" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G53" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H52" s="52" t="inlineStr"/>
-      <c r="I52" s="52" t="inlineStr"/>
-      <c r="J52" s="54" t="inlineStr">
+      <c r="H53" s="56" t="inlineStr"/>
+      <c r="I53" s="56" t="inlineStr"/>
+      <c r="J53" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K52" s="17" t="inlineStr">
+      <c r="K53" s="17" t="inlineStr">
         <is>
           <t>Nessun oggetto ICD</t>
         </is>
       </c>
-      <c r="L52" s="52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="37" t="inlineStr">
-        <is>
-          <t>[era su spedizione.codice_prodotto] spedizione.codice_prodotto il codice prodotto è interno cosi come il id_servizio ,l'applicativo recuperara tutto chiamando ce-rules con id_ldv in ingresso
+      <c r="L53" s="56" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>[era su —] [era su spedizione.codice_prodotto] spedizione.codice_prodotto il codice prodotto è interno cosi come il id_servizio ,l'applicativo recuperara tutto chiamando ce-rules con id_ldv in ingresso
 [era su spedizione.codici_servizi] punto aperto</t>
         </is>
       </c>
-      <c r="B53" s="52" t="inlineStr">
+      <c r="B54" s="56" t="inlineStr">
         <is>
           <t>deliveryService.deliveryService</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>Must be D (Day), T (Timed), M (Morning), A (Afternoon), E (Evening), 6 (Saturday), 7 (Sunday), B (Book in), W (Delivery window), F (Delivery before 10:00) or Z (Pick-up and Drop-off Delivery)
 IT: Deve essere D (giorno), T (a orario), M (mattina), A (pomeriggio), E (sera), 6 (sabato), 7 (domenica), B (su prenotazione), W (finestra di consegna), F (entro le 10:00) o Z (consegna in punto PUDO).</t>
         </is>
       </c>
-      <c r="D53" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E53" s="52" t="n">
+      <c r="D54" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E54" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="52" t="inlineStr">
+      <c r="F54" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G53" s="52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="52" t="inlineStr"/>
-      <c r="I53" s="52" t="inlineStr"/>
-      <c r="J53" s="54" t="inlineStr">
-        <is>
-          <t>NON MAPPATO</t>
-        </is>
-      </c>
-      <c r="K53" s="17" t="inlineStr">
-        <is>
-          <t>Come si traduce in servizi SDA (commento Diego 23-Oct)</t>
-        </is>
-      </c>
-      <c r="L53" s="52" t="inlineStr">
-        <is>
-          <t>DF-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="37" t="inlineStr">
+      <c r="G54" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.codici_servizi</t>
+        </is>
+      </c>
+      <c r="H54" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I54" s="56" t="n">
+        <v>255</v>
+      </c>
+      <c r="J54" s="57" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, W, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
+        </is>
+      </c>
+      <c r="L54" s="56" t="inlineStr">
+        <is>
+          <t>DF-05, DF-07, DF-21, DF-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>questo deve essere rimappato dentro il campo no firma se vale uno dei due  S (firma richiesta), N (firma non richiesta),</t>
         </is>
       </c>
-      <c r="B54" s="52" t="inlineStr">
+      <c r="B55" s="56" t="inlineStr">
         <is>
           <t>deliveryService.deliveryType</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>Must be S (Signature required), N (Signature not required), D (Secure drop), I (Secure id), B (Consolidation at the drop-off partner is required) or C (Consolidation at the delivery partner (which is not the initiating partner) is required). B and C are only valid in the case of a return via PUDO!
 IT: Deve essere S (firma richiesta), N (firma non richiesta), D (deposito sicuro), I (identificazione sicura), B (consolidamento presso il partner di drop-off) o C (consolidamento presso il partner di consegna diverso dall'iniziatore). B e C valgono solo per resi via PUDO.</t>
         </is>
       </c>
-      <c r="D54" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E54" s="52" t="n">
+      <c r="D55" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E55" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="52" t="inlineStr">
+      <c r="F55" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G54" s="52" t="inlineStr">
+      <c r="G55" s="56" t="inlineStr">
         <is>
           <t>cliente.no_firma</t>
         </is>
       </c>
-      <c r="H54" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I54" s="52" t="n">
+      <c r="H55" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I55" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="53" t="inlineStr">
+      <c r="J55" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
-      <c r="K54" s="17" t="inlineStr">
+      <c r="K55" s="17" t="inlineStr">
         <is>
           <t>S (firma richiesta) -&gt; "N"; N (firma non richiesta) -&gt; "S"; altri valori -&gt; vuoto (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L54" s="52" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="n"/>
-      <c r="B55" s="52" t="inlineStr">
+      <c r="L55" s="56" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="56" t="inlineStr">
         <is>
           <t>deliveryService.deliveryType</t>
         </is>
       </c>
-      <c r="C55" s="17" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>Must be S (Signature required), N (Signature not required), D (Secure drop), I (Secure id), B (Consolidation at the drop-off partner is required) or C (Consolidation at the delivery partner (which is not the initiating partner) is required). B and C are only valid in the case of a return via PUDO!
 IT: Deve essere S (firma richiesta), N (firma non richiesta), D (deposito sicuro), I (identificazione sicura), B (consolidamento presso il partner di drop-off) o C (consolidamento presso il partner di consegna diverso dall'iniziatore). B e C valgono solo per resi via PUDO.</t>
         </is>
       </c>
-      <c r="D55" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E55" s="52" t="n">
+      <c r="D56" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E56" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="52" t="inlineStr">
+      <c r="F56" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G55" s="52" t="inlineStr">
+      <c r="G56" s="56" t="inlineStr">
         <is>
           <t>spedizione.consegna.modalita</t>
         </is>
       </c>
-      <c r="H55" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I55" s="52" t="n">
+      <c r="H56" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I56" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="54" t="inlineStr">
+      <c r="J56" s="58" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
       </c>
-      <c r="K55" s="17" t="inlineStr">
+      <c r="K56" s="17" t="inlineStr">
         <is>
           <t>Decodifica S/N/D/I/B/C -&gt; modalita SDA</t>
         </is>
       </c>
-      <c r="L55" s="52" t="inlineStr">
+      <c r="L56" s="56" t="inlineStr">
         <is>
           <t>PA-17</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="52" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="n"/>
+      <c r="B57" s="56" t="inlineStr">
         <is>
           <t>deliveryService.secureDeliveryId</t>
         </is>
       </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>Secure drop id or id to be used for secure delivery
 IT: Id del deposito sicuro o id da usare per la consegna sicura.</t>
         </is>
       </c>
-      <c r="D56" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E56" s="52" t="n">
+      <c r="D57" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E57" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="F56" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G56" s="52" t="inlineStr">
+      <c r="F57" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G57" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H56" s="52" t="inlineStr"/>
-      <c r="I56" s="52" t="inlineStr"/>
-      <c r="J56" s="54" t="inlineStr">
+      <c r="H57" s="56" t="inlineStr"/>
+      <c r="I57" s="56" t="inlineStr"/>
+      <c r="J57" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K56" s="17" t="inlineStr">
+      <c r="K57" s="17" t="inlineStr">
         <is>
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L56" s="52" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="n"/>
-      <c r="B57" s="52" t="inlineStr">
+      <c r="L57" s="56" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="n"/>
+      <c r="B58" s="56" t="inlineStr">
         <is>
           <t>deliveryService.deliveryBookInRequired</t>
         </is>
       </c>
-      <c r="C57" s="17" t="inlineStr">
+      <c r="C58" s="17" t="inlineStr">
         <is>
           <t>Logical true or false delivery partner is to arrange delivery book in details
 IT: Vero/falso: il partner di consegna deve concordare la prenotazione della consegna.</t>
         </is>
       </c>
-      <c r="D57" s="52" t="inlineStr">
+      <c r="D58" s="56" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E57" s="52" t="inlineStr"/>
-      <c r="F57" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G57" s="52" t="inlineStr">
+      <c r="E58" s="56" t="inlineStr"/>
+      <c r="F58" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G58" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H57" s="52" t="inlineStr"/>
-      <c r="I57" s="52" t="inlineStr"/>
-      <c r="J57" s="54" t="inlineStr">
+      <c r="H58" s="56" t="inlineStr"/>
+      <c r="I58" s="56" t="inlineStr"/>
+      <c r="J58" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K57" s="17" t="inlineStr">
+      <c r="K58" s="17" t="inlineStr">
         <is>
           <t>Forse servizio accessorio via ce-rules</t>
         </is>
       </c>
-      <c r="L57" s="52" t="inlineStr">
+      <c r="L58" s="56" t="inlineStr">
         <is>
           <t>PA-03</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="17" t="n"/>
-      <c r="B58" s="52" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="56" t="inlineStr">
         <is>
           <t>deliveryService.deliveryTimeWindowStart</t>
         </is>
       </c>
-      <c r="C58" s="17" t="inlineStr">
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>Only to be used on delivery window service. Only to be entered when service is a time specific delivery service such as timed services Format HH:mm:ss
 IT: Solo per il servizio a finestra di consegna e per servizi a orario specifico. Formato HH:mm:ss.</t>
         </is>
       </c>
-      <c r="D58" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E58" s="52" t="n">
+      <c r="D59" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E59" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="F58" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G58" s="52" t="inlineStr">
+      <c r="F59" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G59" s="56" t="inlineStr">
         <is>
           <t>spedizione.consegna.inizio_ora_consegna</t>
         </is>
       </c>
-      <c r="H58" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I58" s="52" t="n">
+      <c r="H59" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I59" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J58" s="53" t="inlineStr">
+      <c r="J59" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
-      <c r="K58" s="17" t="inlineStr">
+      <c r="K59" s="17" t="inlineStr">
         <is>
           <t>HH:mm:ss -&gt; HH:mm</t>
         </is>
       </c>
-      <c r="L58" s="52" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="n"/>
-      <c r="B59" s="52" t="inlineStr">
+      <c r="L59" s="56" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="n"/>
+      <c r="B60" s="56" t="inlineStr">
         <is>
           <t>deliveryService.deliveryTimeWindowEnd</t>
         </is>
       </c>
-      <c r="C59" s="17" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>Only to be used on delivery window service Format HH:mm:ss
 IT: Solo per il servizio a finestra di consegna. Formato HH:mm:ss.</t>
         </is>
       </c>
-      <c r="D59" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E59" s="52" t="n">
+      <c r="D60" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E60" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="F59" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G59" s="52" t="inlineStr">
+      <c r="F60" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G60" s="56" t="inlineStr">
         <is>
           <t>spedizione.consegna.fine_ora_consegna</t>
         </is>
       </c>
-      <c r="H59" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I59" s="52" t="n">
+      <c r="H60" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I60" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J59" s="53" t="inlineStr">
+      <c r="J60" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
-      <c r="K59" s="17" t="inlineStr">
+      <c r="K60" s="17" t="inlineStr">
         <is>
           <t>HH:mm:ss -&gt; HH:mm</t>
         </is>
       </c>
-      <c r="L59" s="52" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="37" t="inlineStr">
+      <c r="L60" s="56" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">chiedere se c'è un servizio consegna dedicato segna tra i punti aperti </t>
         </is>
       </c>
-      <c r="B60" s="52" t="inlineStr">
+      <c r="B61" s="56" t="inlineStr">
         <is>
           <t>deliveryService.deliveryDateWindowStart</t>
         </is>
       </c>
-      <c r="C60" s="17" t="inlineStr">
+      <c r="C61" s="17" t="inlineStr">
         <is>
           <t>Only to be used on delivery window service. Only to be used for date specific delivery service Format yyyy-MM-dd (For example 2000-01-31 for 31.01.2000)
 IT: Solo per il servizio a finestra di consegna con data specifica. Formato yyyy-MM-dd.</t>
         </is>
       </c>
-      <c r="D60" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E60" s="52" t="inlineStr"/>
-      <c r="F60" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G60" s="52" t="inlineStr">
+      <c r="D61" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E61" s="56" t="inlineStr"/>
+      <c r="F61" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G61" s="56" t="inlineStr">
         <is>
           <t>spedizione.consegna.data_consegna</t>
         </is>
       </c>
-      <c r="H60" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I60" s="52" t="n">
+      <c r="H61" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I61" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="J60" s="53" t="inlineStr">
+      <c r="J61" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
-      <c r="K60" s="17" t="inlineStr">
-        <is>
-          <t>yyyy-MM-dd (commento Diego 23-Oct)</t>
-        </is>
-      </c>
-      <c r="L60" s="52" t="inlineStr">
-        <is>
-          <t>DF-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="n"/>
-      <c r="B61" s="52" t="inlineStr">
+      <c r="K61" s="17" t="inlineStr">
+        <is>
+          <t>yyyy-MM-dd (commento Diego 23-Oct). Il servizio T non ha APT (DF-21) (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L61" s="56" t="inlineStr">
+        <is>
+          <t>DF-06, DF-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n"/>
+      <c r="B62" s="56" t="inlineStr">
         <is>
           <t>deliveryService.deliveryDateWindowEnd</t>
         </is>
       </c>
-      <c r="C61" s="17" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>Only to be used on delivery window service Format yyyy-MM-dd (For example 2000-01-31 for 31.01.2000)
 IT: Solo per il servizio a finestra di consegna. Formato yyyy-MM-dd.</t>
         </is>
       </c>
-      <c r="D61" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E61" s="52" t="inlineStr"/>
-      <c r="F61" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G61" s="52" t="inlineStr">
+      <c r="D62" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E62" s="56" t="inlineStr"/>
+      <c r="F62" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G62" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H61" s="52" t="inlineStr"/>
-      <c r="I61" s="52" t="inlineStr"/>
-      <c r="J61" s="54" t="inlineStr">
+      <c r="H62" s="56" t="inlineStr"/>
+      <c r="I62" s="56" t="inlineStr"/>
+      <c r="J62" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K61" s="17" t="inlineStr">
+      <c r="K62" s="17" t="inlineStr">
         <is>
           <t>ICD ha solo data_consegna</t>
         </is>
       </c>
-      <c r="L61" s="52" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="n"/>
-      <c r="B62" s="52" t="inlineStr">
+      <c r="L62" s="56" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="56" t="inlineStr">
         <is>
           <t>deliveryService.completeDeliveryOnly</t>
         </is>
       </c>
-      <c r="C62" s="17" t="inlineStr">
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>If customer requires delivery of all colli in one delivery set as true otherwise false
 IT: Vero se il cliente vuole tutti i colli in un'unica consegna, altrimenti falso.</t>
         </is>
       </c>
-      <c r="D62" s="52" t="inlineStr">
+      <c r="D63" s="56" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E62" s="52" t="inlineStr"/>
-      <c r="F62" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G62" s="52" t="inlineStr">
+      <c r="E63" s="56" t="inlineStr"/>
+      <c r="F63" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G63" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H62" s="52" t="inlineStr"/>
-      <c r="I62" s="52" t="inlineStr"/>
-      <c r="J62" s="54" t="inlineStr">
+      <c r="H63" s="56" t="inlineStr"/>
+      <c r="I63" s="56" t="inlineStr"/>
+      <c r="J63" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K62" s="17" t="inlineStr">
+      <c r="K63" s="17" t="inlineStr">
         <is>
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L62" s="52" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="17" t="n"/>
-      <c r="B63" s="52" t="inlineStr">
+      <c r="L63" s="56" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="56" t="inlineStr">
         <is>
           <t>deliveryService.additionalNotification</t>
         </is>
       </c>
-      <c r="C63" s="17" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>Contact details if a third party needs contacting to inform of delivery
 IT: Dati di contatto di un terzo da avvisare della consegna.</t>
         </is>
       </c>
-      <c r="D63" s="52" t="inlineStr">
+      <c r="D64" s="56" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E63" s="52" t="inlineStr"/>
-      <c r="F63" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G63" s="52" t="inlineStr">
+      <c r="E64" s="56" t="inlineStr"/>
+      <c r="F64" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G64" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H63" s="52" t="inlineStr"/>
-      <c r="I63" s="52" t="inlineStr"/>
-      <c r="J63" s="54" t="inlineStr">
+      <c r="H64" s="56" t="inlineStr"/>
+      <c r="I64" s="56" t="inlineStr"/>
+      <c r="J64" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K63" s="17" t="inlineStr">
+      <c r="K64" s="17" t="inlineStr">
         <is>
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L63" s="52" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[era su spedizione.codici_servizi] c'è la sezione dedicata contrasegno nel tracciato unico, come punto aperto il codice accesorio che dobbiamo inserire </t>
-        </is>
-      </c>
-      <c r="B64" s="52" t="inlineStr">
-        <is>
-          <t>cashOnDeliveryService</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>IT: (Oggetto) Contrassegno: presente se la spedizione è in contrassegno.</t>
-        </is>
-      </c>
-      <c r="D64" s="52" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E64" s="52" t="inlineStr"/>
-      <c r="F64" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G64" s="52" t="inlineStr">
-        <is>
-          <t>spedizione.contrassegno.flag</t>
-        </is>
-      </c>
-      <c r="H64" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I64" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="53" t="inlineStr">
-        <is>
-          <t>TRASFORMATO</t>
-        </is>
-      </c>
-      <c r="K64" s="17" t="inlineStr">
-        <is>
-          <t>"S" se presente, altrimenti "N"</t>
-        </is>
-      </c>
-      <c r="L64" s="52" t="inlineStr"/>
+      <c r="L64" s="56" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n"/>
-      <c r="B65" s="52" t="inlineStr">
+      <c r="B65" s="56" t="inlineStr">
+        <is>
+          <t>cashOnDeliveryService</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>IT: (Oggetto) Contrassegno: presente se la spedizione è in contrassegno.</t>
+        </is>
+      </c>
+      <c r="D65" s="56" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E65" s="56" t="inlineStr"/>
+      <c r="F65" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G65" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.codici_servizi</t>
+        </is>
+      </c>
+      <c r="H65" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I65" s="56" t="n">
+        <v>255</v>
+      </c>
+      <c r="J65" s="57" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
+        </is>
+      </c>
+      <c r="K65" s="17" t="inlineStr">
+        <is>
+          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, W, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
+        </is>
+      </c>
+      <c r="L65" s="56" t="inlineStr">
+        <is>
+          <t>DF-05, DF-07, DF-21, DF-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[era su spedizione.codici_servizi] c'è la sezione dedicata contrasegno nel tracciato unico, come punto aperto il codice accesorio che dobbiamo inserire </t>
+        </is>
+      </c>
+      <c r="B66" s="56" t="inlineStr">
+        <is>
+          <t>cashOnDeliveryService</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>IT: (Oggetto) Contrassegno: presente se la spedizione è in contrassegno.</t>
+        </is>
+      </c>
+      <c r="D66" s="56" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E66" s="56" t="inlineStr"/>
+      <c r="F66" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G66" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.contrassegno.flag</t>
+        </is>
+      </c>
+      <c r="H66" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I66" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="57" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
+        </is>
+      </c>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
+          <t>"S" se presente, altrimenti "N"</t>
+        </is>
+      </c>
+      <c r="L66" s="56" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="n"/>
+      <c r="B67" s="56" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.iban</t>
         </is>
       </c>
-      <c r="C65" s="17" t="inlineStr">
+      <c r="C67" s="17" t="inlineStr">
         <is>
           <t>Must be filled if IdentifierForCODCollection = 3
 IT: Obbligatorio se IdentifierForCODCollection = 3.</t>
         </is>
       </c>
-      <c r="D65" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E65" s="52" t="n">
+      <c r="D67" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E67" s="56" t="n">
         <v>34</v>
       </c>
-      <c r="F65" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G65" s="52" t="inlineStr">
+      <c r="F67" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G67" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H65" s="52" t="inlineStr"/>
-      <c r="I65" s="52" t="inlineStr"/>
-      <c r="J65" s="54" t="inlineStr">
+      <c r="H67" s="56" t="inlineStr"/>
+      <c r="I67" s="56" t="inlineStr"/>
+      <c r="J67" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K65" s="17" t="inlineStr">
+      <c r="K67" s="17" t="inlineStr">
         <is>
           <t>ICD ha IBAN solo in cliente (da SFA)</t>
         </is>
       </c>
-      <c r="L65" s="52" t="inlineStr">
+      <c r="L67" s="56" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="17" t="n"/>
-      <c r="B66" s="52" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="17" t="n"/>
+      <c r="B68" s="56" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.bic</t>
         </is>
       </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <t>Must be filled if IdentifierForCODCollection = 3
 IT: Obbligatorio se IdentifierForCODCollection = 3.</t>
         </is>
       </c>
-      <c r="D66" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E66" s="52" t="n">
+      <c r="D68" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E68" s="56" t="n">
         <v>11</v>
       </c>
-      <c r="F66" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G66" s="52" t="inlineStr">
+      <c r="F68" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G68" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H66" s="52" t="inlineStr"/>
-      <c r="I66" s="52" t="inlineStr"/>
-      <c r="J66" s="54" t="inlineStr">
+      <c r="H68" s="56" t="inlineStr"/>
+      <c r="I68" s="56" t="inlineStr"/>
+      <c r="J68" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K66" s="17" t="inlineStr">
+      <c r="K68" s="17" t="inlineStr">
         <is>
           <t>ICD ha IBAN solo in cliente (da SFA)</t>
         </is>
       </c>
-      <c r="L66" s="52" t="inlineStr">
+      <c r="L68" s="56" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="17" t="n"/>
-      <c r="B67" s="52" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="17" t="n"/>
+      <c r="B69" s="56" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.accountHolder</t>
         </is>
       </c>
-      <c r="C67" s="17" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>Name of the account holder
 IT: Intestatario del conto.</t>
         </is>
       </c>
-      <c r="D67" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E67" s="52" t="n">
+      <c r="D69" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E69" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F67" s="52" t="inlineStr">
+      <c r="F69" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G67" s="52" t="inlineStr">
+      <c r="G69" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H67" s="52" t="inlineStr"/>
-      <c r="I67" s="52" t="inlineStr"/>
-      <c r="J67" s="54" t="inlineStr">
+      <c r="H69" s="56" t="inlineStr"/>
+      <c r="I69" s="56" t="inlineStr"/>
+      <c r="J69" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K67" s="17" t="inlineStr">
+      <c r="K69" s="17" t="inlineStr">
         <is>
           <t>ICD ha IBAN solo in cliente (da SFA)</t>
         </is>
       </c>
-      <c r="L67" s="52" t="inlineStr">
+      <c r="L69" s="56" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="17" t="n"/>
-      <c r="B68" s="52" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="17" t="n"/>
+      <c r="B70" s="56" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.paymentReason</t>
         </is>
       </c>
-      <c r="C68" s="17" t="inlineStr">
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <t>Actually for COD between Post AT and TOF-DE only 13 digits (EURODIS Shipment Nr) used
 IT: Attualmente, per il contrassegno fra Post AT e TOF-DE, si usano solo 13 cifre (numero spedizione EURODIS).</t>
         </is>
       </c>
-      <c r="D68" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E68" s="52" t="n">
+      <c r="D70" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E70" s="56" t="n">
         <v>140</v>
       </c>
-      <c r="F68" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G68" s="52" t="inlineStr">
+      <c r="F70" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G70" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H68" s="52" t="inlineStr"/>
-      <c r="I68" s="52" t="inlineStr"/>
-      <c r="J68" s="54" t="inlineStr">
+      <c r="H70" s="56" t="inlineStr"/>
+      <c r="I70" s="56" t="inlineStr"/>
+      <c r="J70" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K68" s="17" t="inlineStr">
+      <c r="K70" s="17" t="inlineStr">
         <is>
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L68" s="52" t="inlineStr">
+      <c r="L70" s="56" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="17" t="n"/>
-      <c r="B69" s="52" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="17" t="n"/>
+      <c r="B71" s="56" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.paymentReference</t>
         </is>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C71" s="17" t="inlineStr">
         <is>
           <t>Actually for COD between Post AT and TOF-DE only 12 digits (EURODIS Shipment Nr) used
 IT: Attualmente, per il contrassegno fra Post AT e TOF-DE, si usano solo 12 cifre (numero spedizione EURODIS).</t>
         </is>
       </c>
-      <c r="D69" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E69" s="52" t="n">
+      <c r="D71" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E71" s="56" t="n">
         <v>35</v>
       </c>
-      <c r="F69" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G69" s="52" t="inlineStr">
+      <c r="F71" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G71" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H69" s="52" t="inlineStr"/>
-      <c r="I69" s="52" t="inlineStr"/>
-      <c r="J69" s="54" t="inlineStr">
+      <c r="H71" s="56" t="inlineStr"/>
+      <c r="I71" s="56" t="inlineStr"/>
+      <c r="J71" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K69" s="17" t="inlineStr">
+      <c r="K71" s="17" t="inlineStr">
         <is>
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L69" s="52" t="inlineStr">
+      <c r="L71" s="56" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="17" t="n"/>
-      <c r="B70" s="52" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="17" t="n"/>
+      <c r="B72" s="56" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.amount</t>
         </is>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <t>Amount in given currency with two decimals
 IT: Importo nella valuta indicata, con due decimali.</t>
         </is>
       </c>
-      <c r="D70" s="52" t="inlineStr">
+      <c r="D72" s="56" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E70" s="52" t="inlineStr"/>
-      <c r="F70" s="52" t="inlineStr">
+      <c r="E72" s="56" t="inlineStr"/>
+      <c r="F72" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G70" s="52" t="inlineStr">
+      <c r="G72" s="56" t="inlineStr">
         <is>
           <t>spedizione.contrassegno.importo_contrassegno</t>
         </is>
       </c>
-      <c r="H70" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I70" s="52" t="n">
+      <c r="H72" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I72" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="J70" s="55" t="inlineStr">
+      <c r="J72" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
-      <c r="K70" s="17" t="inlineStr">
-        <is>
-          <t>Se currency &lt;&gt; EUR: scarto?</t>
-        </is>
-      </c>
-      <c r="L70" s="52" t="inlineStr">
-        <is>
-          <t>PA-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="17" t="n"/>
-      <c r="B71" s="52" t="inlineStr">
+      <c r="K72" s="17" t="inlineStr">
+        <is>
+          <t>2 decimali, maggiore di 0, max 999999.99 (CSV accessori). Se currency &lt;&gt; EUR: scarto? (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L72" s="56" t="inlineStr">
+        <is>
+          <t>DF-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="n"/>
+      <c r="B73" s="56" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.currency</t>
         </is>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>EUR or other ISO Currency Codes
 IT: EUR o altro codice valuta ISO.</t>
         </is>
       </c>
-      <c r="D71" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E71" s="52" t="n">
+      <c r="D73" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E73" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="F71" s="52" t="inlineStr">
+      <c r="F73" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G71" s="52" t="inlineStr">
+      <c r="G73" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H71" s="52" t="inlineStr"/>
-      <c r="I71" s="52" t="inlineStr"/>
-      <c r="J71" s="54" t="inlineStr">
+      <c r="H73" s="56" t="inlineStr"/>
+      <c r="I73" s="56" t="inlineStr"/>
+      <c r="J73" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
       </c>
-      <c r="K71" s="17" t="inlineStr">
+      <c r="K73" s="17" t="inlineStr">
         <is>
           <t>ICD non ha valuta del contrassegno</t>
         </is>
       </c>
-      <c r="L71" s="52" t="inlineStr">
+      <c r="L73" s="56" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="17" t="n"/>
-      <c r="B72" s="52" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="17" t="n"/>
+      <c r="B74" s="56" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.identifierForCODCollection</t>
         </is>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C74" s="17" t="inlineStr">
         <is>
           <t>COD with cash collection or check collection; Cash collection is standard for Post AT and most partners Must be 3 (Cash) or 5 (Check)
 IT: Contrassegno incassato in contanti o con assegno; i contanti sono lo standard per Post AT e la maggior parte dei partner. Deve essere 3 (contanti) o 5 (assegno).</t>
         </is>
       </c>
-      <c r="D72" s="52" t="inlineStr">
+      <c r="D74" s="56" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E72" s="52" t="inlineStr"/>
-      <c r="F72" s="52" t="inlineStr">
+      <c r="E74" s="56" t="inlineStr"/>
+      <c r="F74" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G72" s="52" t="inlineStr">
+      <c r="G74" s="56" t="inlineStr">
         <is>
           <t>spedizione.contrassegno.tipo_pagamento_contrassegno</t>
         </is>
       </c>
-      <c r="H72" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I72" s="52" t="n">
+      <c r="H74" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I74" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="J72" s="54" t="inlineStr">
+      <c r="J74" s="57" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
+        </is>
+      </c>
+      <c r="K74" s="17" t="inlineStr">
+        <is>
+          <t>3 -&gt; CON, 5 -&gt; ABM (riscontro SDA, da confermare; mai ACM). Non ammesso con Punto Poste (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L74" s="56" t="inlineStr">
+        <is>
+          <t>DF-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="n"/>
+      <c r="B75" s="56" t="inlineStr">
+        <is>
+          <t>customsService</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>IT: (Oggetto) Dati doganali.</t>
+        </is>
+      </c>
+      <c r="D75" s="56" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E75" s="56" t="inlineStr"/>
+      <c r="F75" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.importi.status_doganale</t>
+        </is>
+      </c>
+      <c r="H75" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I75" s="56" t="n">
+        <v>50</v>
+      </c>
+      <c r="J75" s="58" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
       </c>
-      <c r="K72" s="17" t="inlineStr">
-        <is>
-          <t>3 = contanti, 5 = assegno -&gt; codici ICD (CON? ACM/ABM?)</t>
-        </is>
-      </c>
-      <c r="L72" s="52" t="inlineStr">
-        <is>
-          <t>PA-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="n"/>
-      <c r="B73" s="52" t="inlineStr">
-        <is>
-          <t>customsService</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <t>IT: (Oggetto) Dati doganali.</t>
-        </is>
-      </c>
-      <c r="D73" s="52" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E73" s="52" t="inlineStr"/>
-      <c r="F73" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G73" s="52" t="inlineStr">
-        <is>
-          <t>spedizione.importi.status_doganale</t>
-        </is>
-      </c>
-      <c r="H73" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I73" s="52" t="n">
-        <v>50</v>
-      </c>
-      <c r="J73" s="54" t="inlineStr">
-        <is>
-          <t>DA DEFINIRE</t>
-        </is>
-      </c>
-      <c r="K73" s="17" t="inlineStr">
+      <c r="K75" s="17" t="inlineStr">
         <is>
           <t>Spedizioni extra-UE: perimetro?</t>
         </is>
       </c>
-      <c r="L73" s="52" t="inlineStr">
+      <c r="L75" s="56" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="17" t="n"/>
-      <c r="B74" s="52" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="37" t="inlineStr">
+        <is>
+          <t>c'è anche la sezione assicurata</t>
+        </is>
+      </c>
+      <c r="B76" s="56" t="inlineStr">
         <is>
           <t>customsService.commercialValueOfGoods</t>
         </is>
       </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>For insurance reasons; mandatory if not documents
 IT: Per motivi assicurativi; obbligatorio se non si tratta di documenti.</t>
         </is>
       </c>
-      <c r="D74" s="52" t="inlineStr">
+      <c r="D76" s="56" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E74" s="52" t="inlineStr"/>
-      <c r="F74" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G74" s="52" t="inlineStr">
-        <is>
-          <t>spedizione.assicurata.importo_assicurata</t>
-        </is>
-      </c>
-      <c r="H74" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I74" s="52" t="n">
+      <c r="E76" s="56" t="inlineStr"/>
+      <c r="F76" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G76" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.collo.articolo.valore</t>
+        </is>
+      </c>
+      <c r="H76" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I76" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="J74" s="55" t="inlineStr">
-        <is>
-          <t>DIRETTO</t>
-        </is>
-      </c>
-      <c r="K74" s="17" t="inlineStr">
-        <is>
-          <t>Valore merce 'for insurance reasons' secondo lo swagger (commento Diego 23-Oct)</t>
-        </is>
-      </c>
-      <c r="L74" s="52" t="inlineStr">
-        <is>
-          <t>DF-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="17" t="n"/>
-      <c r="B75" s="52" t="inlineStr">
+      <c r="J76" s="57" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
+        </is>
+      </c>
+      <c r="K76" s="17" t="inlineStr">
+        <is>
+          <t>x100 (centesimi)</t>
+        </is>
+      </c>
+      <c r="L76" s="56" t="inlineStr">
+        <is>
+          <t>PA-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="n"/>
+      <c r="B77" s="56" t="inlineStr">
         <is>
           <t>customsService.commercialValueOfGoods</t>
         </is>
       </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="C77" s="17" t="inlineStr">
         <is>
           <t>For insurance reasons; mandatory if not documents
 IT: Per motivi assicurativi; obbligatorio se non si tratta di documenti.</t>
         </is>
       </c>
-      <c r="D75" s="52" t="inlineStr">
+      <c r="D77" s="56" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E75" s="52" t="inlineStr"/>
-      <c r="F75" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G75" s="52" t="inlineStr">
-        <is>
-          <t>spedizione.assicurata.spedizione_assicurata</t>
-        </is>
-      </c>
-      <c r="H75" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I75" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="54" t="inlineStr">
-        <is>
-          <t>DA DEFINIRE</t>
-        </is>
-      </c>
-      <c r="K75" s="17" t="inlineStr">
-        <is>
-          <t>"S" se il valore merce e' presente? (commento Diego 23-Oct)</t>
-        </is>
-      </c>
-      <c r="L75" s="52" t="inlineStr">
-        <is>
-          <t>DF-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="37" t="inlineStr">
-        <is>
-          <t>c'è anche la sezione assicurata</t>
-        </is>
-      </c>
-      <c r="B76" s="52" t="inlineStr">
+      <c r="E77" s="56" t="inlineStr"/>
+      <c r="F77" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.internazionale.valore_spedizione</t>
+        </is>
+      </c>
+      <c r="H77" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I77" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="J77" s="59" t="inlineStr">
+        <is>
+          <t>DIRETTO</t>
+        </is>
+      </c>
+      <c r="K77" s="17" t="inlineStr">
+        <is>
+          <t>In euro</t>
+        </is>
+      </c>
+      <c r="L77" s="56" t="inlineStr">
+        <is>
+          <t>PA-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="n"/>
+      <c r="B78" s="56" t="inlineStr">
         <is>
           <t>customsService.commercialValueOfGoods</t>
         </is>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>For insurance reasons; mandatory if not documents
 IT: Per motivi assicurativi; obbligatorio se non si tratta di documenti.</t>
         </is>
       </c>
-      <c r="D76" s="52" t="inlineStr">
+      <c r="D78" s="56" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E76" s="52" t="inlineStr"/>
-      <c r="F76" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G76" s="52" t="inlineStr">
-        <is>
-          <t>spedizione.collo.articolo.valore</t>
-        </is>
-      </c>
-      <c r="H76" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I76" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="J76" s="53" t="inlineStr">
+      <c r="E78" s="56" t="inlineStr"/>
+      <c r="F78" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" s="56" t="inlineStr">
+        <is>
+          <t>spedizione.valore</t>
+        </is>
+      </c>
+      <c r="H78" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I78" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="J78" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
-      <c r="K76" s="17" t="inlineStr">
-        <is>
-          <t>x100 (centesimi)</t>
-        </is>
-      </c>
-      <c r="L76" s="52" t="inlineStr">
-        <is>
-          <t>PA-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="17" t="n"/>
-      <c r="B77" s="52" t="inlineStr">
-        <is>
-          <t>customsService.commercialValueOfGoods</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
-        <is>
-          <t>For insurance reasons; mandatory if not documents
-IT: Per motivi assicurativi; obbligatorio se non si tratta di documenti.</t>
-        </is>
-      </c>
-      <c r="D77" s="52" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E77" s="52" t="inlineStr"/>
-      <c r="F77" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G77" s="52" t="inlineStr">
-        <is>
-          <t>spedizione.internazionale.valore_spedizione</t>
-        </is>
-      </c>
-      <c r="H77" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I77" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="J77" s="55" t="inlineStr">
-        <is>
-          <t>DIRETTO</t>
-        </is>
-      </c>
-      <c r="K77" s="17" t="inlineStr">
-        <is>
-          <t>In euro</t>
-        </is>
-      </c>
-      <c r="L77" s="52" t="inlineStr">
-        <is>
-          <t>PA-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="17" t="n"/>
-      <c r="B78" s="52" t="inlineStr">
-        <is>
-          <t>customsService.commercialValueOfGoods</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
-        <is>
-          <t>For insurance reasons; mandatory if not documents
-IT: Per motivi assicurativi; obbligatorio se non si tratta di documenti.</t>
-        </is>
-      </c>
-      <c r="D78" s="52" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E78" s="52" t="inlineStr"/>
-      <c r="F78" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G78" s="52" t="inlineStr">
-        <is>
-          <t>spedizione.valore</t>
-        </is>
-      </c>
-      <c r="H78" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I78" s="52" t="n">
-        <v>12</v>
-      </c>
-      <c r="J78" s="53" t="inlineStr">
-        <is>
-          <t>TRASFORMATO</t>
-        </is>
-      </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
           <t>x100 (centesimi), solo se currency = EUR</t>
         </is>
       </c>
-      <c r="L78" s="52" t="inlineStr">
+      <c r="L78" s="56" t="inlineStr">
         <is>
           <t>PA-22</t>
         </is>
@@ -22029,7 +22054,7 @@
     </row>
     <row r="79">
       <c r="A79" s="17" t="n"/>
-      <c r="B79" s="52" t="inlineStr">
+      <c r="B79" s="56" t="inlineStr">
         <is>
           <t>customsService.currency</t>
         </is>
@@ -22040,39 +22065,39 @@
 IT: Codice valuta se il valore commerciale è valorizzato (EUR o altro codice ISO).</t>
         </is>
       </c>
-      <c r="D79" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E79" s="52" t="n">
+      <c r="D79" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E79" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="F79" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G79" s="52" t="inlineStr">
+      <c r="F79" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G79" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.articolo.valuta</t>
         </is>
       </c>
-      <c r="H79" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I79" s="52" t="n">
+      <c r="H79" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I79" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="J79" s="55" t="inlineStr">
+      <c r="J79" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
       <c r="K79" s="17" t="inlineStr"/>
-      <c r="L79" s="52" t="inlineStr">
+      <c r="L79" s="56" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22080,7 +22105,7 @@
     </row>
     <row r="80">
       <c r="A80" s="17" t="n"/>
-      <c r="B80" s="52" t="inlineStr">
+      <c r="B80" s="56" t="inlineStr">
         <is>
           <t>customsService.currency</t>
         </is>
@@ -22091,43 +22116,43 @@
 IT: Codice valuta se il valore commerciale è valorizzato (EUR o altro codice ISO).</t>
         </is>
       </c>
-      <c r="D80" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E80" s="52" t="n">
+      <c r="D80" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E80" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="F80" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G80" s="52" t="inlineStr">
+      <c r="F80" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" s="56" t="inlineStr">
         <is>
           <t>spedizione.internazionale.valuta</t>
         </is>
       </c>
-      <c r="H80" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I80" s="52" t="n">
+      <c r="H80" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I80" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="J80" s="55" t="inlineStr">
+      <c r="J80" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
       <c r="K80" s="17" t="inlineStr"/>
-      <c r="L80" s="52" t="inlineStr"/>
+      <c r="L80" s="56" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="17" t="n"/>
-      <c r="B81" s="52" t="inlineStr">
+      <c r="B81" s="56" t="inlineStr">
         <is>
           <t>customsService.dutyCode</t>
         </is>
@@ -22138,33 +22163,33 @@
 IT: Obbligatorio per extra-UE (= codice della tariffa doganale).</t>
         </is>
       </c>
-      <c r="D81" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E81" s="52" t="n">
+      <c r="D81" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E81" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="F81" s="52" t="inlineStr">
+      <c r="F81" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G81" s="52" t="inlineStr">
+      <c r="G81" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.articolo.codice_taric</t>
         </is>
       </c>
-      <c r="H81" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I81" s="52" t="n">
+      <c r="H81" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I81" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="J81" s="53" t="inlineStr">
+      <c r="J81" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22174,7 +22199,7 @@
           <t>Un solo articolo per spedizione; valore integrale (sorgente 12, ICD 10)</t>
         </is>
       </c>
-      <c r="L81" s="52" t="inlineStr">
+      <c r="L81" s="56" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22182,7 +22207,7 @@
     </row>
     <row r="82">
       <c r="A82" s="17" t="n"/>
-      <c r="B82" s="52" t="inlineStr">
+      <c r="B82" s="56" t="inlineStr">
         <is>
           <t>customsService.sign</t>
         </is>
@@ -22193,27 +22218,27 @@
 IT: Descrizione aggiuntiva facoltativa della spedizione (numero di identificazione/riferimento).</t>
         </is>
       </c>
-      <c r="D82" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E82" s="52" t="n">
+      <c r="D82" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E82" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="F82" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G82" s="52" t="inlineStr">
+      <c r="F82" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G82" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H82" s="52" t="inlineStr"/>
-      <c r="I82" s="52" t="inlineStr"/>
-      <c r="J82" s="54" t="inlineStr">
+      <c r="H82" s="56" t="inlineStr"/>
+      <c r="I82" s="56" t="inlineStr"/>
+      <c r="J82" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22223,7 +22248,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L82" s="52" t="inlineStr">
+      <c r="L82" s="56" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22231,7 +22256,7 @@
     </row>
     <row r="83">
       <c r="A83" s="17" t="n"/>
-      <c r="B83" s="52" t="inlineStr">
+      <c r="B83" s="56" t="inlineStr">
         <is>
           <t>customsService.number</t>
         </is>
@@ -22242,25 +22267,25 @@
 IT: Descrizione aggiuntiva facoltativa della spedizione (numero di identificazione/riferimento).</t>
         </is>
       </c>
-      <c r="D83" s="52" t="inlineStr">
+      <c r="D83" s="56" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E83" s="52" t="inlineStr"/>
-      <c r="F83" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G83" s="52" t="inlineStr">
+      <c r="E83" s="56" t="inlineStr"/>
+      <c r="F83" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G83" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H83" s="52" t="inlineStr"/>
-      <c r="I83" s="52" t="inlineStr"/>
-      <c r="J83" s="54" t="inlineStr">
+      <c r="H83" s="56" t="inlineStr"/>
+      <c r="I83" s="56" t="inlineStr"/>
+      <c r="J83" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22270,7 +22295,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L83" s="52" t="inlineStr">
+      <c r="L83" s="56" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22278,7 +22303,7 @@
     </row>
     <row r="84">
       <c r="A84" s="17" t="n"/>
-      <c r="B84" s="52" t="inlineStr">
+      <c r="B84" s="56" t="inlineStr">
         <is>
           <t>customsService.descriptionOfGoods</t>
         </is>
@@ -22289,39 +22314,39 @@
 IT: Informazione facoltativa sui camion di trasporto, es. per la Svizzera. NB: la descrizione dello swagger non corrisponde al nome del campo ("descrizione merce"), da chiarire con EURODIS.</t>
         </is>
       </c>
-      <c r="D84" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E84" s="52" t="n">
+      <c r="D84" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E84" s="56" t="n">
         <v>20</v>
       </c>
-      <c r="F84" s="52" t="inlineStr">
+      <c r="F84" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G84" s="52" t="inlineStr">
+      <c r="G84" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.articolo.english_descr</t>
         </is>
       </c>
-      <c r="H84" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I84" s="52" t="n">
+      <c r="H84" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I84" s="56" t="n">
         <v>250</v>
       </c>
-      <c r="J84" s="55" t="inlineStr">
+      <c r="J84" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
       <c r="K84" s="17" t="inlineStr"/>
-      <c r="L84" s="52" t="inlineStr">
+      <c r="L84" s="56" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22329,7 +22354,7 @@
     </row>
     <row r="85">
       <c r="A85" s="17" t="n"/>
-      <c r="B85" s="52" t="inlineStr">
+      <c r="B85" s="56" t="inlineStr">
         <is>
           <t>customsService.descriptionOfGoods</t>
         </is>
@@ -22340,33 +22365,33 @@
 IT: Informazione facoltativa sui camion di trasporto, es. per la Svizzera. NB: la descrizione dello swagger non corrisponde al nome del campo ("descrizione merce"), da chiarire con EURODIS.</t>
         </is>
       </c>
-      <c r="D85" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E85" s="52" t="n">
+      <c r="D85" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E85" s="56" t="n">
         <v>20</v>
       </c>
-      <c r="F85" s="52" t="inlineStr">
+      <c r="F85" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G85" s="52" t="inlineStr">
+      <c r="G85" s="56" t="inlineStr">
         <is>
           <t>spedizione.descrizione_contenuto</t>
         </is>
       </c>
-      <c r="H85" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I85" s="52" t="n">
+      <c r="H85" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I85" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="J85" s="55" t="inlineStr">
+      <c r="J85" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -22376,11 +22401,11 @@
           <t>Solo se presente customsService (20 &lt;= 30)</t>
         </is>
       </c>
-      <c r="L85" s="52" t="inlineStr"/>
+      <c r="L85" s="56" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="17" t="n"/>
-      <c r="B86" s="52" t="inlineStr">
+      <c r="B86" s="56" t="inlineStr">
         <is>
           <t>customsService.descriptionOfGoods</t>
         </is>
@@ -22391,43 +22416,43 @@
 IT: Informazione facoltativa sui camion di trasporto, es. per la Svizzera. NB: la descrizione dello swagger non corrisponde al nome del campo ("descrizione merce"), da chiarire con EURODIS.</t>
         </is>
       </c>
-      <c r="D86" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E86" s="52" t="n">
+      <c r="D86" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E86" s="56" t="n">
         <v>20</v>
       </c>
-      <c r="F86" s="52" t="inlineStr">
+      <c r="F86" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G86" s="52" t="inlineStr">
+      <c r="G86" s="56" t="inlineStr">
         <is>
           <t>spedizione.internazionale.descrizione</t>
         </is>
       </c>
-      <c r="H86" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I86" s="52" t="n">
+      <c r="H86" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I86" s="56" t="n">
         <v>255</v>
       </c>
-      <c r="J86" s="55" t="inlineStr">
+      <c r="J86" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
       <c r="K86" s="17" t="inlineStr"/>
-      <c r="L86" s="52" t="inlineStr"/>
+      <c r="L86" s="56" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n"/>
-      <c r="B87" s="52" t="inlineStr">
+      <c r="B87" s="56" t="inlineStr">
         <is>
           <t>hazardousADRServices[]</t>
         </is>
@@ -22437,25 +22462,25 @@
           <t>IT: (Array) Dati delle merci pericolose ADR: classe di pericolo, numero ONU, gruppo di imballaggio, peso lordo ADR, codice galleria, categoria di trasporto, denominazione.</t>
         </is>
       </c>
-      <c r="D87" s="52" t="inlineStr">
+      <c r="D87" s="56" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E87" s="52" t="inlineStr"/>
-      <c r="F87" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G87" s="52" t="inlineStr">
+      <c r="E87" s="56" t="inlineStr"/>
+      <c r="F87" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G87" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H87" s="52" t="inlineStr"/>
-      <c r="I87" s="52" t="inlineStr"/>
-      <c r="J87" s="54" t="inlineStr">
+      <c r="H87" s="56" t="inlineStr"/>
+      <c r="I87" s="56" t="inlineStr"/>
+      <c r="J87" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22465,7 +22490,7 @@
           <t>Nessun oggetto ICD</t>
         </is>
       </c>
-      <c r="L87" s="52" t="inlineStr">
+      <c r="L87" s="56" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22473,7 +22498,7 @@
     </row>
     <row r="88">
       <c r="A88" s="17" t="n"/>
-      <c r="B88" s="52" t="inlineStr">
+      <c r="B88" s="56" t="inlineStr">
         <is>
           <t>hazardousCollis[]</t>
         </is>
@@ -22483,25 +22508,25 @@
           <t>IT: (Array) Colli ADR: numero di colli per tipo e descrizione ADR del tipo di collo.</t>
         </is>
       </c>
-      <c r="D88" s="52" t="inlineStr">
+      <c r="D88" s="56" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E88" s="52" t="inlineStr"/>
-      <c r="F88" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G88" s="52" t="inlineStr">
+      <c r="E88" s="56" t="inlineStr"/>
+      <c r="F88" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G88" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H88" s="52" t="inlineStr"/>
-      <c r="I88" s="52" t="inlineStr"/>
-      <c r="J88" s="54" t="inlineStr">
+      <c r="H88" s="56" t="inlineStr"/>
+      <c r="I88" s="56" t="inlineStr"/>
+      <c r="J88" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22511,7 +22536,7 @@
           <t>Nessun oggetto ICD</t>
         </is>
       </c>
-      <c r="L88" s="52" t="inlineStr">
+      <c r="L88" s="56" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22523,7 +22548,7 @@
           <t xml:space="preserve">traccia tra i punti aperti  che lo abbiamo mappato cosi </t>
         </is>
       </c>
-      <c r="B89" s="52" t="inlineStr">
+      <c r="B89" s="56" t="inlineStr">
         <is>
           <t>consigneePreAdvice.smsPreAdvice</t>
         </is>
@@ -22534,39 +22559,39 @@
 IT: Se vero, ContactSMS in ConsigneeAddress deve essere valorizzato.</t>
         </is>
       </c>
-      <c r="D89" s="52" t="inlineStr">
+      <c r="D89" s="56" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E89" s="52" t="inlineStr"/>
-      <c r="F89" s="52" t="inlineStr">
+      <c r="E89" s="56" t="inlineStr"/>
+      <c r="F89" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G89" s="52" t="inlineStr">
+      <c r="G89" s="56" t="inlineStr">
         <is>
           <t>spedizione.notifiche_sms</t>
         </is>
       </c>
-      <c r="H89" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I89" s="52" t="n"/>
-      <c r="J89" s="53" t="inlineStr">
-        <is>
-          <t>TRASFORMATO</t>
+      <c r="H89" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I89" s="56" t="n"/>
+      <c r="J89" s="58" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
         </is>
       </c>
       <c r="K89" s="17" t="inlineStr">
         <is>
-          <t>true -&gt; "S", false -&gt; "N" (commento Diego 23-Oct: mappato cosi, da confermare)</t>
-        </is>
-      </c>
-      <c r="L89" s="52" t="inlineStr">
+          <t>SDA notifica da sola se ci sono i contatti e non usa RT_65 (riscontro SDA): valutare se non mapparlo (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L89" s="56" t="inlineStr">
         <is>
           <t>DF-09</t>
         </is>
@@ -22578,7 +22603,7 @@
           <t xml:space="preserve">traccia tra i punti aperti  che lo abbiamo mappato cosi </t>
         </is>
       </c>
-      <c r="B90" s="52" t="inlineStr">
+      <c r="B90" s="56" t="inlineStr">
         <is>
           <t>consigneePreAdvice.eMailPreAdvice</t>
         </is>
@@ -22589,39 +22614,39 @@
 IT: Se vero, ContactEMail in ConsigneeAddress deve essere valorizzato.</t>
         </is>
       </c>
-      <c r="D90" s="52" t="inlineStr">
+      <c r="D90" s="56" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E90" s="52" t="inlineStr"/>
-      <c r="F90" s="52" t="inlineStr">
+      <c r="E90" s="56" t="inlineStr"/>
+      <c r="F90" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G90" s="52" t="inlineStr">
+      <c r="G90" s="56" t="inlineStr">
         <is>
           <t>spedizione.notifiche_email</t>
         </is>
       </c>
-      <c r="H90" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I90" s="52" t="n"/>
-      <c r="J90" s="53" t="inlineStr">
-        <is>
-          <t>TRASFORMATO</t>
+      <c r="H90" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I90" s="56" t="n"/>
+      <c r="J90" s="58" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
         </is>
       </c>
       <c r="K90" s="17" t="inlineStr">
         <is>
-          <t>true -&gt; "S", false -&gt; "N" (commento Diego 23-Oct: mappato cosi, da confermare)</t>
-        </is>
-      </c>
-      <c r="L90" s="52" t="inlineStr">
+          <t>SDA notifica da sola se ci sono i contatti e non usa RT_65 (riscontro SDA): valutare se non mapparlo (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L90" s="56" t="inlineStr">
         <is>
           <t>DF-09</t>
         </is>
@@ -22629,7 +22654,7 @@
     </row>
     <row r="91">
       <c r="A91" s="17" t="n"/>
-      <c r="B91" s="52" t="inlineStr">
+      <c r="B91" s="56" t="inlineStr">
         <is>
           <t>consigneePreAdvice.telephonePreAdvice</t>
         </is>
@@ -22640,25 +22665,25 @@
 IT: Se vero, ContactTelephone in ConsigneeAddress deve essere valorizzato.</t>
         </is>
       </c>
-      <c r="D91" s="52" t="inlineStr">
+      <c r="D91" s="56" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E91" s="52" t="inlineStr"/>
-      <c r="F91" s="52" t="inlineStr">
+      <c r="E91" s="56" t="inlineStr"/>
+      <c r="F91" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G91" s="52" t="inlineStr">
+      <c r="G91" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H91" s="52" t="inlineStr"/>
-      <c r="I91" s="52" t="inlineStr"/>
-      <c r="J91" s="54" t="inlineStr">
+      <c r="H91" s="56" t="inlineStr"/>
+      <c r="I91" s="56" t="inlineStr"/>
+      <c r="J91" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22668,7 +22693,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L91" s="52" t="inlineStr">
+      <c r="L91" s="56" t="inlineStr">
         <is>
           <t>PA-18</t>
         </is>
@@ -22676,7 +22701,7 @@
     </row>
     <row r="92">
       <c r="A92" s="17" t="n"/>
-      <c r="B92" s="52" t="inlineStr">
+      <c r="B92" s="56" t="inlineStr">
         <is>
           <t>collis[]</t>
         </is>
@@ -22686,31 +22711,31 @@
           <t>IT: (Array) Dati dei colli: un elemento per collo o pallet.</t>
         </is>
       </c>
-      <c r="D92" s="52" t="inlineStr">
+      <c r="D92" s="56" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E92" s="52" t="inlineStr"/>
-      <c r="F92" s="52" t="inlineStr">
+      <c r="E92" s="56" t="inlineStr"/>
+      <c r="F92" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G92" s="52" t="inlineStr">
+      <c r="G92" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.numero_colli_parz</t>
         </is>
       </c>
-      <c r="H92" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I92" s="52" t="n">
+      <c r="H92" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I92" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J92" s="53" t="inlineStr">
+      <c r="J92" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22720,11 +22745,11 @@
           <t>Progressivo collo</t>
         </is>
       </c>
-      <c r="L92" s="52" t="inlineStr"/>
+      <c r="L92" s="56" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="17" t="n"/>
-      <c r="B93" s="52" t="inlineStr">
+      <c r="B93" s="56" t="inlineStr">
         <is>
           <t>collis[]</t>
         </is>
@@ -22734,31 +22759,31 @@
           <t>IT: (Array) Dati dei colli: un elemento per collo o pallet.</t>
         </is>
       </c>
-      <c r="D93" s="52" t="inlineStr">
+      <c r="D93" s="56" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E93" s="52" t="inlineStr"/>
-      <c r="F93" s="52" t="inlineStr">
+      <c r="E93" s="56" t="inlineStr"/>
+      <c r="F93" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G93" s="52" t="inlineStr">
+      <c r="G93" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.tipo_collo</t>
         </is>
       </c>
-      <c r="H93" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I93" s="52" t="n">
+      <c r="H93" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I93" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J93" s="53" t="inlineStr">
+      <c r="J93" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22768,7 +22793,7 @@
           <t>Solo multicollo: madre/figlio</t>
         </is>
       </c>
-      <c r="L93" s="52" t="inlineStr">
+      <c r="L93" s="56" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -22776,7 +22801,7 @@
     </row>
     <row r="94">
       <c r="A94" s="17" t="n"/>
-      <c r="B94" s="52" t="inlineStr">
+      <c r="B94" s="56" t="inlineStr">
         <is>
           <t>collis[].identifierPalletOrCollo</t>
         </is>
@@ -22787,33 +22812,33 @@
 IT: "P" (pallet), "C" (collo), "P+" (pallet+) o "C+" (collo+).</t>
         </is>
       </c>
-      <c r="D94" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E94" s="52" t="n">
+      <c r="D94" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E94" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="F94" s="52" t="inlineStr">
+      <c r="F94" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G94" s="52" t="inlineStr">
+      <c r="G94" s="56" t="inlineStr">
         <is>
           <t>spedizione.codice_tipo_spedizione</t>
         </is>
       </c>
-      <c r="H94" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I94" s="52" t="n">
+      <c r="H94" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I94" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J94" s="54" t="inlineStr">
+      <c r="J94" s="58" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -22823,11 +22848,11 @@
           <t>Valori ICD "P","C": verificare il significato</t>
         </is>
       </c>
-      <c r="L94" s="52" t="inlineStr"/>
+      <c r="L94" s="56" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="17" t="n"/>
-      <c r="B95" s="52" t="inlineStr">
+      <c r="B95" s="56" t="inlineStr">
         <is>
           <t>collis[].identifierPalletOrCollo</t>
         </is>
@@ -22838,33 +22863,33 @@
 IT: "P" (pallet), "C" (collo), "P+" (pallet+) o "C+" (collo+).</t>
         </is>
       </c>
-      <c r="D95" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E95" s="52" t="n">
+      <c r="D95" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E95" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="F95" s="52" t="inlineStr">
+      <c r="F95" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G95" s="52" t="inlineStr">
+      <c r="G95" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.codice_imballo</t>
         </is>
       </c>
-      <c r="H95" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I95" s="52" t="n">
+      <c r="H95" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I95" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="J95" s="53" t="inlineStr">
+      <c r="J95" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22874,11 +22899,11 @@
           <t>Proposta: P/P+ -&gt; "PL", C/C+ -&gt; "CL"</t>
         </is>
       </c>
-      <c r="L95" s="52" t="inlineStr"/>
+      <c r="L95" s="56" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="17" t="n"/>
-      <c r="B96" s="52" t="inlineStr">
+      <c r="B96" s="56" t="inlineStr">
         <is>
           <t>collis[].weightOfUnit</t>
         </is>
@@ -22889,31 +22914,31 @@
 IT: In chilogrammi.</t>
         </is>
       </c>
-      <c r="D96" s="52" t="inlineStr">
+      <c r="D96" s="56" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E96" s="52" t="inlineStr"/>
-      <c r="F96" s="52" t="inlineStr">
+      <c r="E96" s="56" t="inlineStr"/>
+      <c r="F96" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G96" s="52" t="inlineStr">
+      <c r="G96" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.peso</t>
         </is>
       </c>
-      <c r="H96" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I96" s="52" t="n">
+      <c r="H96" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I96" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="J96" s="53" t="inlineStr">
+      <c r="J96" s="57" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22923,11 +22948,11 @@
           <t>kg -&gt; grammi (x1000): peso 2000 nell'esempio EUD_INVIOFILE</t>
         </is>
       </c>
-      <c r="L96" s="52" t="inlineStr"/>
+      <c r="L96" s="56" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n"/>
-      <c r="B97" s="52" t="inlineStr">
+      <c r="B97" s="56" t="inlineStr">
         <is>
           <t>collis[].europlateBarcode</t>
         </is>
@@ -22938,33 +22963,33 @@
 IT: Barcode EURODIS del collo; valore di default (0) in caso di neighbourhood business.</t>
         </is>
       </c>
-      <c r="D97" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E97" s="52" t="n">
+      <c r="D97" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E97" s="56" t="n">
         <v>24</v>
       </c>
-      <c r="F97" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G97" s="52" t="inlineStr">
+      <c r="F97" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G97" s="56" t="inlineStr">
         <is>
           <t>spedizione.internazionale.id_ldv_itz</t>
         </is>
       </c>
-      <c r="H97" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I97" s="52" t="n">
+      <c r="H97" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I97" s="56" t="n">
         <v>50</v>
       </c>
-      <c r="J97" s="55" t="inlineStr">
+      <c r="J97" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -22974,7 +22999,7 @@
           <t>Decisione 22-Oct. ICD: "previsto per i casi ERS e Eurodis". Campo a livello spedizione, barcode a livello collo: con piu' colli quale si usa?</t>
         </is>
       </c>
-      <c r="L97" s="52" t="inlineStr">
+      <c r="L97" s="56" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -22986,7 +23011,7 @@
           <t>[era su —] dovrebbe essere id_ldv_associata</t>
         </is>
       </c>
-      <c r="B98" s="52" t="inlineStr">
+      <c r="B98" s="56" t="inlineStr">
         <is>
           <t>collis[].referencedEuroplateBarcode</t>
         </is>
@@ -22997,33 +23022,33 @@
 IT: Valorizzato solo se il collo fa parte di un reso: riporta il barcode EURODIS del collo originario.</t>
         </is>
       </c>
-      <c r="D98" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E98" s="52" t="n">
+      <c r="D98" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E98" s="56" t="n">
         <v>24</v>
       </c>
-      <c r="F98" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G98" s="52" t="inlineStr">
+      <c r="F98" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G98" s="56" t="inlineStr">
         <is>
           <t>spedizione.id_ldv_associata</t>
         </is>
       </c>
-      <c r="H98" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I98" s="52" t="n">
+      <c r="H98" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I98" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="J98" s="55" t="inlineStr">
+      <c r="J98" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23033,7 +23058,7 @@
           <t>Solo resi. ICD: campo di spedizione di 3 caratteri, il barcode e' per collo e di 24 (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L98" s="52" t="inlineStr">
+      <c r="L98" s="56" t="inlineStr">
         <is>
           <t>DF-10</t>
         </is>
@@ -23041,7 +23066,7 @@
     </row>
     <row r="99">
       <c r="A99" s="17" t="n"/>
-      <c r="B99" s="52" t="inlineStr">
+      <c r="B99" s="56" t="inlineStr">
         <is>
           <t>collis[].consignorsColloBarcode</t>
         </is>
@@ -23052,33 +23077,33 @@
 IT: Barcode domestico di reso del partner di consegna originario, generato/assegnato dalla soluzione resi EURODIS, oppure barcode del cliente o del partner mittente. Per il neighbourhood business va fornito il barcode domestico del partner secondo la SOP Neighbourhood business.</t>
         </is>
       </c>
-      <c r="D99" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E99" s="52" t="n">
+      <c r="D99" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E99" s="56" t="n">
         <v>50</v>
       </c>
-      <c r="F99" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G99" s="52" t="inlineStr">
+      <c r="F99" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G99" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.id_ldv</t>
         </is>
       </c>
-      <c r="H99" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I99" s="52" t="n">
+      <c r="H99" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I99" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="J99" s="55" t="inlineStr">
+      <c r="J99" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23088,7 +23113,7 @@
           <t>LDV del collo (decisione 22-Oct). Vuoto in EUD_INVIOFILE perche' li' la genera SDA</t>
         </is>
       </c>
-      <c r="L99" s="52" t="inlineStr">
+      <c r="L99" s="56" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -23096,7 +23121,7 @@
     </row>
     <row r="100">
       <c r="A100" s="17" t="n"/>
-      <c r="B100" s="52" t="inlineStr">
+      <c r="B100" s="56" t="inlineStr">
         <is>
           <t>collis[].length</t>
         </is>
@@ -23107,31 +23132,31 @@
 IT: In centimetri.</t>
         </is>
       </c>
-      <c r="D100" s="52" t="inlineStr">
+      <c r="D100" s="56" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E100" s="52" t="inlineStr"/>
-      <c r="F100" s="52" t="inlineStr">
+      <c r="E100" s="56" t="inlineStr"/>
+      <c r="F100" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G100" s="52" t="inlineStr">
+      <c r="G100" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.lunghezza</t>
         </is>
       </c>
-      <c r="H100" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I100" s="52" t="n">
+      <c r="H100" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I100" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J100" s="55" t="inlineStr">
+      <c r="J100" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23141,11 +23166,11 @@
           <t>cm</t>
         </is>
       </c>
-      <c r="L100" s="52" t="inlineStr"/>
+      <c r="L100" s="56" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="17" t="n"/>
-      <c r="B101" s="52" t="inlineStr">
+      <c r="B101" s="56" t="inlineStr">
         <is>
           <t>collis[].width</t>
         </is>
@@ -23156,31 +23181,31 @@
 IT: In centimetri.</t>
         </is>
       </c>
-      <c r="D101" s="52" t="inlineStr">
+      <c r="D101" s="56" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E101" s="52" t="inlineStr"/>
-      <c r="F101" s="52" t="inlineStr">
+      <c r="E101" s="56" t="inlineStr"/>
+      <c r="F101" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G101" s="52" t="inlineStr">
+      <c r="G101" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.profondita</t>
         </is>
       </c>
-      <c r="H101" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I101" s="52" t="n">
+      <c r="H101" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I101" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J101" s="55" t="inlineStr">
+      <c r="J101" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23190,11 +23215,11 @@
           <t>cm</t>
         </is>
       </c>
-      <c r="L101" s="52" t="inlineStr"/>
+      <c r="L101" s="56" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="17" t="n"/>
-      <c r="B102" s="52" t="inlineStr">
+      <c r="B102" s="56" t="inlineStr">
         <is>
           <t>collis[].height</t>
         </is>
@@ -23205,31 +23230,31 @@
 IT: In centimetri.</t>
         </is>
       </c>
-      <c r="D102" s="52" t="inlineStr">
+      <c r="D102" s="56" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E102" s="52" t="inlineStr"/>
-      <c r="F102" s="52" t="inlineStr">
+      <c r="E102" s="56" t="inlineStr"/>
+      <c r="F102" s="56" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G102" s="52" t="inlineStr">
+      <c r="G102" s="56" t="inlineStr">
         <is>
           <t>spedizione.collo.altezza</t>
         </is>
       </c>
-      <c r="H102" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I102" s="52" t="n">
+      <c r="H102" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I102" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="J102" s="55" t="inlineStr">
+      <c r="J102" s="59" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23239,11 +23264,11 @@
           <t>cm</t>
         </is>
       </c>
-      <c r="L102" s="52" t="inlineStr"/>
+      <c r="L102" s="56" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n"/>
-      <c r="B103" s="52" t="inlineStr">
+      <c r="B103" s="56" t="inlineStr">
         <is>
           <t>collis[].volumetric</t>
         </is>
@@ -23254,25 +23279,25 @@
 IT: Metri cubi.</t>
         </is>
       </c>
-      <c r="D103" s="52" t="inlineStr">
+      <c r="D103" s="56" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E103" s="52" t="inlineStr"/>
-      <c r="F103" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G103" s="52" t="inlineStr">
+      <c r="E103" s="56" t="inlineStr"/>
+      <c r="F103" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G103" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H103" s="52" t="inlineStr"/>
-      <c r="I103" s="52" t="inlineStr"/>
-      <c r="J103" s="54" t="inlineStr">
+      <c r="H103" s="56" t="inlineStr"/>
+      <c r="I103" s="56" t="inlineStr"/>
+      <c r="J103" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -23282,11 +23307,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L103" s="52" t="inlineStr"/>
+      <c r="L103" s="56" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="17" t="n"/>
-      <c r="B104" s="52" t="inlineStr">
+      <c r="B104" s="56" t="inlineStr">
         <is>
           <t>collis[].volumetricWeight</t>
         </is>
@@ -23297,25 +23322,25 @@
 IT: In chilogrammi.</t>
         </is>
       </c>
-      <c r="D104" s="52" t="inlineStr">
+      <c r="D104" s="56" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E104" s="52" t="inlineStr"/>
-      <c r="F104" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G104" s="52" t="inlineStr">
+      <c r="E104" s="56" t="inlineStr"/>
+      <c r="F104" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G104" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H104" s="52" t="inlineStr"/>
-      <c r="I104" s="52" t="inlineStr"/>
-      <c r="J104" s="54" t="inlineStr">
+      <c r="H104" s="56" t="inlineStr"/>
+      <c r="I104" s="56" t="inlineStr"/>
+      <c r="J104" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -23325,11 +23350,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L104" s="52" t="inlineStr"/>
+      <c r="L104" s="56" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="17" t="n"/>
-      <c r="B105" s="52" t="inlineStr">
+      <c r="B105" s="56" t="inlineStr">
         <is>
           <t>collis[].boxType / boxDimensionCategory / boxId</t>
         </is>
@@ -23340,25 +23365,25 @@
 IT: Forse obsoleti, da discutere.</t>
         </is>
       </c>
-      <c r="D105" s="52" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E105" s="52" t="inlineStr"/>
-      <c r="F105" s="52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G105" s="52" t="inlineStr">
+      <c r="D105" s="56" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E105" s="56" t="inlineStr"/>
+      <c r="F105" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G105" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H105" s="52" t="inlineStr"/>
-      <c r="I105" s="52" t="inlineStr"/>
-      <c r="J105" s="54" t="inlineStr">
+      <c r="H105" s="56" t="inlineStr"/>
+      <c r="I105" s="56" t="inlineStr"/>
+      <c r="J105" s="58" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -23368,7 +23393,7 @@
           <t>Ignorare</t>
         </is>
       </c>
-      <c r="L105" s="52" t="inlineStr"/>
+      <c r="L105" s="56" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L105"/>
@@ -29507,20 +29532,24 @@
       <c r="H171" t="n">
         <v>255</v>
       </c>
-      <c r="I171" s="44" t="inlineStr">
-        <is>
-          <t>CE-RULES</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
+      <c r="I171" s="47" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>deliveryService.deliveryService, cashOnDeliveryService, consigneeAddress.pudoID</t>
+        </is>
+      </c>
       <c r="K171" s="17" t="inlineStr">
         <is>
-          <t>Da ce-rules con id_ldv. Aperto: come si riflettono servizio di consegna EURODIS e contrassegno (commento Diego 23-Oct)</t>
+          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, W, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>DF-05, DF-07</t>
+          <t>DF-05, DF-07, DF-21, DF-22</t>
         </is>
       </c>
     </row>
@@ -29634,12 +29663,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" s="17" t="inlineStr">
         <is>
-          <t>"CDC-00000014" nell'esempio EUD_INVIOFILE: costante di contratto (F1)?</t>
+          <t>Il ms sync, se vuoto, usa il centro di costo di config; un solo centro statico fornito da Poste (riscontro SDA) (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>PA-23</t>
+          <t>DF-11, PA-23</t>
         </is>
       </c>
     </row>
@@ -30181,7 +30210,7 @@
       </c>
       <c r="K188" s="17" t="inlineStr">
         <is>
-          <t>yyyy-MM-dd (commento Diego 23-Oct: clearanceTimestamp si ignora)</t>
+          <t>yyyy-MM-dd (commento Diego 23-Oct: clearanceTimestamp si ignora). Conflitto: il riscontro SDA mappa clearanceTimestamp -&gt; shipmentDate (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -30497,12 +30526,12 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" s="17" t="inlineStr">
         <is>
-          <t>"APT000902" nell'esempio EUD_INVIOFILE: costante di contratto o derivato?</t>
+          <t>Il ms sync usa questo campo come prodotto e, se vuoto, il valore di config (APT000901, PDB Express) (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>PA-23</t>
+          <t>DF-11, PA-23</t>
         </is>
       </c>
     </row>
@@ -31617,9 +31646,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="I226" s="47" t="inlineStr">
-        <is>
-          <t>TRASFORMATO</t>
+      <c r="I226" s="41" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -31629,7 +31658,7 @@
       </c>
       <c r="K226" s="17" t="inlineStr">
         <is>
-          <t>true -&gt; "S", false -&gt; "N" (commento Diego 23-Oct: mappato cosi, da confermare)</t>
+          <t>SDA notifica da sola se ci sono i contatti e non usa RT_65 (riscontro SDA): valutare se non mapparlo (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -31659,9 +31688,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="I227" s="47" t="inlineStr">
-        <is>
-          <t>TRASFORMATO</t>
+      <c r="I227" s="41" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -31671,7 +31700,7 @@
       </c>
       <c r="K227" s="17" t="inlineStr">
         <is>
-          <t>true -&gt; "S", false -&gt; "N" (commento Diego 23-Oct: mappato cosi, da confermare)</t>
+          <t>SDA notifica da sola se ci sono i contatti e non usa RT_65 (riscontro SDA): valutare se non mapparlo (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -32394,7 +32423,7 @@
       </c>
       <c r="D247" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E247" s="42" t="n"/>
@@ -33884,12 +33913,12 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" s="17" t="inlineStr">
         <is>
-          <t>countryCode va solo in codice_nazione_iso_2 (commento Diego 23-Oct)</t>
+          <t>countryCode va solo in codice_nazione_iso_2 (commento Diego 23-Oct). Attenzione: il ms sync legge il paese BEP da qui e non risolve ISO4; destinatario = ITA1 (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>DF-12</t>
+          <t>DF-12, DF-27</t>
         </is>
       </c>
     </row>
@@ -37840,12 +37869,12 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" s="17" t="inlineStr">
         <is>
-          <t>countryCode va solo in codice_nazione_iso_2 (commento Diego 23-Oct)</t>
+          <t>countryCode va solo in codice_nazione_iso_2 (commento Diego 23-Oct). Attenzione: il ms sync legge il paese BEP da qui e non risolve ISO4; destinatario = ITA1 (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>DF-12</t>
+          <t>DF-12, DF-27</t>
         </is>
       </c>
     </row>
@@ -39922,19 +39951,15 @@
       <c r="H456" t="n">
         <v>1</v>
       </c>
-      <c r="I456" s="41" t="inlineStr">
-        <is>
-          <t>DA DEFINIRE</t>
-        </is>
-      </c>
-      <c r="J456" t="inlineStr">
-        <is>
-          <t>customsService.commercialValueOfGoods</t>
-        </is>
-      </c>
+      <c r="I456" s="45" t="inlineStr">
+        <is>
+          <t>NON VALORIZZATO</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr"/>
       <c r="K456" s="17" t="inlineStr">
         <is>
-          <t>"S" se il valore merce e' presente? (commento Diego 23-Oct)</t>
+          <t>Assicurazione fuori perimetro (riscontro SDA): non valorizzare (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -39967,19 +39992,15 @@
       <c r="H457" t="n">
         <v>10</v>
       </c>
-      <c r="I457" s="46" t="inlineStr">
-        <is>
-          <t>DIRETTO</t>
-        </is>
-      </c>
-      <c r="J457" t="inlineStr">
-        <is>
-          <t>customsService.commercialValueOfGoods</t>
-        </is>
-      </c>
+      <c r="I457" s="45" t="inlineStr">
+        <is>
+          <t>NON VALORIZZATO</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr"/>
       <c r="K457" s="17" t="inlineStr">
         <is>
-          <t>Valore merce 'for insurance reasons' secondo lo swagger (commento Diego 23-Oct)</t>
+          <t>Assicurazione fuori perimetro (riscontro SDA): non usare commercialValueOfGoods (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -40020,10 +40041,14 @@
       <c r="J458" t="inlineStr"/>
       <c r="K458" s="17" t="inlineStr">
         <is>
-          <t>Nessuna sorgente EURODIS</t>
-        </is>
-      </c>
-      <c r="L458" t="inlineStr"/>
+          <t>Assicurazione fuori perimetro (riscontro SDA) (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>DF-08</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="42" t="inlineStr">
@@ -40124,9 +40149,9 @@
       <c r="H461" t="n">
         <v>3</v>
       </c>
-      <c r="I461" s="41" t="inlineStr">
-        <is>
-          <t>DA DEFINIRE</t>
+      <c r="I461" s="47" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -40136,12 +40161,12 @@
       </c>
       <c r="K461" s="17" t="inlineStr">
         <is>
-          <t>3 = contanti, 5 = assegno -&gt; codici ICD (CON? ACM/ABM?)</t>
+          <t>3 -&gt; CON, 5 -&gt; ABM (riscontro SDA, da confermare; mai ACM). Non ammesso con Punto Poste (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>PA-19</t>
+          <t>DF-24</t>
         </is>
       </c>
     </row>
@@ -40181,12 +40206,12 @@
       </c>
       <c r="K462" s="17" t="inlineStr">
         <is>
-          <t>Se currency &lt;&gt; EUR: scarto?</t>
+          <t>2 decimali, maggiore di 0, max 999999.99 (CSV accessori). Se currency &lt;&gt; EUR: scarto? (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>PA-19</t>
+          <t>DF-24</t>
         </is>
       </c>
     </row>
@@ -42543,18 +42568,26 @@
       <c r="H527" t="n">
         <v>11</v>
       </c>
-      <c r="I527" s="39" t="inlineStr">
-        <is>
-          <t>A VALLE</t>
-        </is>
-      </c>
-      <c r="J527" t="inlineStr"/>
+      <c r="I527" s="47" t="inlineStr">
+        <is>
+          <t>TRASFORMATO</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>consigneeAddress.pudoID</t>
+        </is>
+      </c>
       <c r="K527" s="17" t="inlineStr">
         <is>
-          <t>Calcolato a valle</t>
-        </is>
-      </c>
-      <c r="L527" t="inlineStr"/>
+          <t>Solo con deliveryService = Z: PUDO ID, e' il node di APT000947 (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>DF-14, DF-23</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -42580,18 +42613,22 @@
       <c r="H528" t="n">
         <v>50</v>
       </c>
-      <c r="I528" s="39" t="inlineStr">
-        <is>
-          <t>A VALLE</t>
+      <c r="I528" s="41" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
         </is>
       </c>
       <c r="J528" t="inlineStr"/>
       <c r="K528" s="17" t="inlineStr">
         <is>
-          <t>Calcolato a valle</t>
-        </is>
-      </c>
-      <c r="L528" t="inlineStr"/>
+          <t>Nome del Punto Poste: e' il name di APT000947, obbligatorio non vuoto. Sorgente da chiarire: nel flusso via file RT_30_080 contiene il destinatario effettivo (proposta 29-Oct)</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>DF-23</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -42863,12 +42900,12 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" s="17" t="inlineStr">
         <is>
-          <t>Nessuna sorgente EURODIS: default "R" (reso)?</t>
+          <t>Reso = rientro al mittente. APT000930 non mappato finche' non si decide se serve e che valore ha return (A o R) (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>PA-17</t>
+          <t>DF-25</t>
         </is>
       </c>
     </row>
@@ -42982,12 +43019,12 @@
       </c>
       <c r="K538" s="17" t="inlineStr">
         <is>
-          <t>yyyy-MM-dd (commento Diego 23-Oct)</t>
+          <t>yyyy-MM-dd (commento Diego 23-Oct). Il servizio T non ha APT (DF-21) (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>DF-06</t>
+          <t>DF-06, DF-21</t>
         </is>
       </c>
     </row>

--- a/iniziative/136596/ICD_PREADVISING_LDV_EVENT_SOURCE_v11.xlsx
+++ b/iniziative/136596/ICD_PREADVISING_LDV_EVENT_SOURCE_v11.xlsx
@@ -254,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -361,6 +361,18 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -18109,7 +18121,7 @@
     </row>
     <row r="2">
       <c r="A2" s="17" t="n"/>
-      <c r="B2" s="56" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>edReference</t>
         </is>
@@ -18120,31 +18132,31 @@
 IT: Numero univoco della spedizione nella rete EURODIS. Per la definizione di dettaglio vedere il documento A02 del manuale di rete EURODIS.</t>
         </is>
       </c>
-      <c r="D2" s="56" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E2" s="56" t="inlineStr"/>
-      <c r="F2" s="56" t="inlineStr">
+      <c r="E2" s="60" t="inlineStr"/>
+      <c r="F2" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G2" s="56" t="inlineStr">
+      <c r="G2" s="60" t="inlineStr">
         <is>
           <t>spedizione.rif_spedizione</t>
         </is>
       </c>
-      <c r="H2" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="56" t="n">
+      <c r="H2" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="60" t="n">
         <v>25</v>
       </c>
-      <c r="J2" s="57" t="inlineStr">
+      <c r="J2" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -18154,7 +18166,7 @@
           <t>Decisione 22-Oct. Numero decimale (max 13 cifre) -&gt; stringa senza decimali (ICD 25)</t>
         </is>
       </c>
-      <c r="L2" s="56" t="inlineStr">
+      <c r="L2" s="60" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -18162,7 +18174,7 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="n"/>
-      <c r="B3" s="56" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>referencedEurodisShipmentNumber</t>
         </is>
@@ -18173,25 +18185,25 @@
 IT: Numero EURODIS della spedizione originaria. Obbligatorio per i tipi "R", "D" e "A"; condizionato per "P"; facoltativo per "E".</t>
         </is>
       </c>
-      <c r="D3" s="56" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E3" s="56" t="inlineStr"/>
-      <c r="F3" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G3" s="56" t="inlineStr">
+      <c r="E3" s="60" t="inlineStr"/>
+      <c r="F3" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H3" s="56" t="inlineStr"/>
-      <c r="I3" s="56" t="inlineStr"/>
-      <c r="J3" s="58" t="inlineStr">
+      <c r="H3" s="60" t="inlineStr"/>
+      <c r="I3" s="60" t="inlineStr"/>
+      <c r="J3" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18201,7 +18213,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L3" s="56" t="inlineStr">
+      <c r="L3" s="60" t="inlineStr">
         <is>
           <t>PA-17</t>
         </is>
@@ -18213,7 +18225,7 @@
           <t>[era su spedizione.verso] Campo da ingnorare</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>shipmentTypeIndicator</t>
         </is>
@@ -18224,27 +18236,27 @@
 IT: N = normale; A = ordine di ritiro; P = spedizione risultante da un ordine di ritiro; R = reso; X = AUX-PAN; B = spedizione normale in neighbourhood business (NB); D = reso in NB; E = ritiro in NB; C = spedizione B2C (facoltativo, da concordare fra partner mittente e partner di consegna); Y = B2C in NB; L = richiesta di reso; M = reso dal destinatario (solo verso il partner di consegna iniziale; trasmesso come "R" ai partner di transito e consegna, come "E" in NB); W = spedizione distribuita senza EUROPLATE.</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E4" s="56" t="n">
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="56" t="inlineStr">
+      <c r="F4" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G4" s="56" t="inlineStr">
+      <c r="G4" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="56" t="inlineStr"/>
-      <c r="I4" s="56" t="inlineStr"/>
-      <c r="J4" s="58" t="inlineStr">
+      <c r="H4" s="60" t="inlineStr"/>
+      <c r="I4" s="60" t="inlineStr"/>
+      <c r="J4" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18254,7 +18266,7 @@
           <t>Da ignorare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L4" s="56" t="inlineStr"/>
+      <c r="L4" s="60" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="37" t="inlineStr">
@@ -18262,7 +18274,7 @@
           <t>[era su spedizione.codice_prodotto] Campo da ingnorare</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>lineHaulIndicator</t>
         </is>
@@ -18273,27 +18285,27 @@
 IT: Deve essere "N" (normale), "D" (iniezione diretta) o "L" (trazione diretta).</t>
         </is>
       </c>
-      <c r="D5" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E5" s="56" t="n">
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E5" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="56" t="inlineStr">
+      <c r="F5" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G5" s="56" t="inlineStr">
+      <c r="G5" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="56" t="inlineStr"/>
-      <c r="I5" s="56" t="inlineStr"/>
-      <c r="J5" s="58" t="inlineStr">
+      <c r="H5" s="60" t="inlineStr"/>
+      <c r="I5" s="60" t="inlineStr"/>
+      <c r="J5" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18303,7 +18315,7 @@
           <t>Da ignorare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L5" s="56" t="inlineStr"/>
+      <c r="L5" s="60" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="37" t="inlineStr">
@@ -18312,7 +18324,7 @@
 [era su spedizione.ora_spedizione] no questa data ignorala clearanceTimestamp</t>
         </is>
       </c>
-      <c r="B6" s="56" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>clearanceTimestamp</t>
         </is>
@@ -18323,25 +18335,25 @@
 IT: Data e ora di creazione del dataset PAN della spedizione. Es. "2000-01-31T18:30:00.000Z" = 31/01/2000 ore 18:30.</t>
         </is>
       </c>
-      <c r="D6" s="56" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>date-time</t>
         </is>
       </c>
-      <c r="E6" s="56" t="inlineStr"/>
-      <c r="F6" s="56" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr"/>
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G6" s="56" t="inlineStr">
+      <c r="G6" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="56" t="inlineStr"/>
-      <c r="I6" s="56" t="inlineStr"/>
-      <c r="J6" s="58" t="inlineStr">
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
+      <c r="J6" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18351,7 +18363,7 @@
           <t>Da ignorare: per data e ora spedizione si usa entranceTimestamp (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L6" s="56" t="inlineStr"/>
+      <c r="L6" s="60" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="37" t="inlineStr">
@@ -18360,7 +18372,7 @@
 spedizione.ora_spedizione e spedizione.data_spedizione</t>
         </is>
       </c>
-      <c r="B7" s="56" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>entranceTimestamp</t>
         </is>
@@ -18371,31 +18383,31 @@
 IT: Data di ingresso della spedizione nel sistema domestico del partner, cioè quando è stata fisicamente consegnata. Es. "2000-01-31T18:30:00.000Z".</t>
         </is>
       </c>
-      <c r="D7" s="56" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>date-time</t>
         </is>
       </c>
-      <c r="E7" s="56" t="inlineStr"/>
-      <c r="F7" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G7" s="56" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr"/>
+      <c r="F7" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" s="60" t="inlineStr">
         <is>
           <t>spedizione.data_spedizione</t>
         </is>
       </c>
-      <c r="H7" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I7" s="56" t="n">
+      <c r="H7" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="57" t="inlineStr">
+      <c r="J7" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -18405,7 +18417,7 @@
           <t>yyyy-MM-dd (commento Diego 23-Oct: clearanceTimestamp si ignora). Conflitto: il riscontro SDA mappa clearanceTimestamp -&gt; shipmentDate (proposta 29-Oct)</t>
         </is>
       </c>
-      <c r="L7" s="56" t="inlineStr">
+      <c r="L7" s="60" t="inlineStr">
         <is>
           <t>DF-01</t>
         </is>
@@ -18413,7 +18425,7 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="n"/>
-      <c r="B8" s="56" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>entranceTimestamp</t>
         </is>
@@ -18424,31 +18436,31 @@
 IT: Data di ingresso della spedizione nel sistema domestico del partner, cioè quando è stata fisicamente consegnata. Es. "2000-01-31T18:30:00.000Z".</t>
         </is>
       </c>
-      <c r="D8" s="56" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>date-time</t>
         </is>
       </c>
-      <c r="E8" s="56" t="inlineStr"/>
-      <c r="F8" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G8" s="56" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr"/>
+      <c r="F8" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" s="60" t="inlineStr">
         <is>
           <t>spedizione.ora_spedizione</t>
         </is>
       </c>
-      <c r="H8" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I8" s="56" t="n">
+      <c r="H8" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="57" t="inlineStr">
+      <c r="J8" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -18458,7 +18470,7 @@
           <t>HH:mm:ss (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L8" s="56" t="inlineStr">
+      <c r="L8" s="60" t="inlineStr">
         <is>
           <t>DF-01</t>
         </is>
@@ -18466,7 +18478,7 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="n"/>
-      <c r="B9" s="56" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>numberOfHandlingUnits</t>
         </is>
@@ -18477,31 +18489,31 @@
 IT: Totale di colli e pallet. Deve coincidere con il numero di colli trasmessi.</t>
         </is>
       </c>
-      <c r="D9" s="56" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E9" s="56" t="inlineStr"/>
-      <c r="F9" s="56" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr"/>
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G9" s="56" t="inlineStr">
+      <c r="G9" s="60" t="inlineStr">
         <is>
           <t>spedizione.numero_colli</t>
         </is>
       </c>
-      <c r="H9" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="56" t="n">
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="59" t="inlineStr">
+      <c r="J9" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18511,11 +18523,11 @@
           <t>Verificare coerenza con len(collis)</t>
         </is>
       </c>
-      <c r="L9" s="56" t="inlineStr"/>
+      <c r="L9" s="60" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n"/>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>shipmentWeight</t>
         </is>
@@ -18526,29 +18538,29 @@
 IT: Peso in chilogrammi con due decimali.</t>
         </is>
       </c>
-      <c r="D10" s="56" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E10" s="56" t="inlineStr"/>
-      <c r="F10" s="56" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr"/>
+      <c r="F10" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G10" s="56" t="inlineStr">
+      <c r="G10" s="60" t="inlineStr">
         <is>
           <t>spedizione.internazionale.peso</t>
         </is>
       </c>
-      <c r="H10" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="56" t="n"/>
-      <c r="J10" s="57" t="inlineStr">
+      <c r="H10" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="60" t="n"/>
+      <c r="J10" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -18558,11 +18570,11 @@
           <t>kg -&gt; grammi (x1000)</t>
         </is>
       </c>
-      <c r="L10" s="56" t="inlineStr"/>
+      <c r="L10" s="60" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n"/>
-      <c r="B11" s="56" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>consignorsCustomerNumberAtDispatchPartner</t>
         </is>
@@ -18572,27 +18584,27 @@
           <t>IT: (Nessuna descrizione nello swagger) Codice cliente del mittente presso il partner che spedisce.</t>
         </is>
       </c>
-      <c r="D11" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E11" s="56" t="n">
+      <c r="D11" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F11" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G11" s="56" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G11" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="56" t="inlineStr"/>
-      <c r="I11" s="56" t="inlineStr"/>
-      <c r="J11" s="58" t="inlineStr">
+      <c r="H11" s="60" t="inlineStr"/>
+      <c r="I11" s="60" t="inlineStr"/>
+      <c r="J11" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18602,11 +18614,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L11" s="56" t="inlineStr"/>
+      <c r="L11" s="60" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n"/>
-      <c r="B12" s="56" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>consignorsReference</t>
         </is>
@@ -18616,27 +18628,27 @@
           <t>IT: (Nessuna descrizione nello swagger) Riferimento del mittente.</t>
         </is>
       </c>
-      <c r="D12" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E12" s="56" t="n">
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F12" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G12" s="56" t="inlineStr">
+      <c r="F12" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G12" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="56" t="inlineStr"/>
-      <c r="I12" s="56" t="inlineStr"/>
-      <c r="J12" s="58" t="inlineStr">
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
+      <c r="J12" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18646,11 +18658,11 @@
           <t>Nessun campo ICD libero (rif_spedizione e' edReference)</t>
         </is>
       </c>
-      <c r="L12" s="56" t="inlineStr"/>
+      <c r="L12" s="60" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n"/>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>dispatchPartnersDomesticShipmentNumber</t>
         </is>
@@ -18660,33 +18672,33 @@
           <t>IT: (Nessuna descrizione nello swagger) Numero di spedizione domestico del partner che spedisce.</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E13" s="56" t="n">
+      <c r="D13" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E13" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F13" s="56" t="inlineStr">
+      <c r="F13" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G13" s="56" t="inlineStr">
+      <c r="G13" s="60" t="inlineStr">
         <is>
           <t>spedizione.id_ldv_partner_master</t>
         </is>
       </c>
-      <c r="H13" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="56" t="n">
+      <c r="H13" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="60" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="59" t="inlineStr">
+      <c r="J13" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18696,7 +18708,7 @@
           <t>Numero spedizione del partner mittente (35 &lt;= 50)</t>
         </is>
       </c>
-      <c r="L13" s="56" t="inlineStr">
+      <c r="L13" s="60" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -18708,7 +18720,7 @@
           <t xml:space="preserve">non interessa </t>
         </is>
       </c>
-      <c r="B14" s="56" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>truckLicensePlate</t>
         </is>
@@ -18719,27 +18731,27 @@
 IT: Targa del camion (e del rimorchio).</t>
         </is>
       </c>
-      <c r="D14" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E14" s="56" t="n">
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F14" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G14" s="56" t="inlineStr">
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G14" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="56" t="inlineStr"/>
-      <c r="I14" s="56" t="inlineStr"/>
-      <c r="J14" s="58" t="inlineStr">
+      <c r="H14" s="60" t="inlineStr"/>
+      <c r="I14" s="60" t="inlineStr"/>
+      <c r="J14" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18749,7 +18761,7 @@
           <t>Non interessa (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L14" s="56" t="inlineStr"/>
+      <c r="L14" s="60" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="37" t="inlineStr">
@@ -18758,7 +18770,7 @@
 [era su spedizione.internazionale.addebito_oneri] da non mappare</t>
         </is>
       </c>
-      <c r="B15" s="56" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>termsOfDeliveryText</t>
         </is>
@@ -18769,27 +18781,27 @@
 IT: Facoltativo per spedizioni intra-UE, obbligatorio per paesi extra-UE. Deve essere un Incoterm ufficiale DPU o EXW (per ritiri e resi) oppure uno degli Incoterm interni di rete DDC e DDX.</t>
         </is>
       </c>
-      <c r="D15" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E15" s="56" t="n">
+      <c r="D15" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E15" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F15" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G15" s="56" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G15" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="56" t="inlineStr"/>
-      <c r="I15" s="56" t="inlineStr"/>
-      <c r="J15" s="58" t="inlineStr">
+      <c r="H15" s="60" t="inlineStr"/>
+      <c r="I15" s="60" t="inlineStr"/>
+      <c r="J15" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18799,11 +18811,11 @@
           <t>Da non mappare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L15" s="56" t="inlineStr"/>
+      <c r="L15" s="60" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n"/>
-      <c r="B16" s="56" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.contactName</t>
         </is>
@@ -18814,33 +18826,33 @@
 IT: Nome del contatto all'indirizzo, stampato sulla 2a riga indirizzo dell'EUROPLATE. Per le spedizioni PUDO contiene il nome del negozio.</t>
         </is>
       </c>
-      <c r="D16" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E16" s="56" t="n">
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E16" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G16" s="56" t="inlineStr">
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G16" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.rif_contatto</t>
         </is>
       </c>
-      <c r="H16" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" s="56" t="n">
+      <c r="H16" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="J16" s="59" t="inlineStr">
+      <c r="J16" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18850,7 +18862,7 @@
           <t>Valore integrale (sorgente 40, ICD 35): non si tronca</t>
         </is>
       </c>
-      <c r="L16" s="56" t="inlineStr">
+      <c r="L16" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -18858,7 +18870,7 @@
     </row>
     <row r="17">
       <c r="A17" s="17" t="n"/>
-      <c r="B17" s="56" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.contactTelephone</t>
         </is>
@@ -18869,33 +18881,33 @@
 IT: Condizione per il servizio di prenotazione consegna: se il servizio è concordato fra i partner e il flag di prenotazione è presente in DeliveryService.</t>
         </is>
       </c>
-      <c r="D17" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E17" s="56" t="n">
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="F17" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G17" s="56" t="inlineStr">
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G17" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.telefono</t>
         </is>
       </c>
-      <c r="H17" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I17" s="56" t="n">
+      <c r="H17" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I17" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="J17" s="59" t="inlineStr">
+      <c r="J17" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -18905,11 +18917,11 @@
           <t>30 -&gt; 30</t>
         </is>
       </c>
-      <c r="L17" s="56" t="inlineStr"/>
+      <c r="L17" s="60" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n"/>
-      <c r="B18" s="56" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.alternativeContactTelephone</t>
         </is>
@@ -18920,27 +18932,27 @@
 IT: Telefono di contatto alternativo (alfanumerico per ammettere il prefisso internazionale).</t>
         </is>
       </c>
-      <c r="D18" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E18" s="56" t="n">
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E18" s="60" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G18" s="56" t="inlineStr">
+      <c r="F18" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="56" t="inlineStr"/>
-      <c r="I18" s="56" t="inlineStr"/>
-      <c r="J18" s="58" t="inlineStr">
+      <c r="H18" s="60" t="inlineStr"/>
+      <c r="I18" s="60" t="inlineStr"/>
+      <c r="J18" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -18950,7 +18962,7 @@
           <t>Il tracciato non ha un secondo numero di telefono: da chiedere se serve (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L18" s="56" t="inlineStr">
+      <c r="L18" s="60" t="inlineStr">
         <is>
           <t>DF-15</t>
         </is>
@@ -18962,7 +18974,7 @@
           <t xml:space="preserve">[era su spedizione.destinatario.prefisso_cellulare] no consigneeAddress.contactSMS tutto su cellulare </t>
         </is>
       </c>
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.contactSMS</t>
         </is>
@@ -18973,33 +18985,33 @@
 IT: Numero SMS del contatto principale. Formato: prefisso internazionale (+XX) seguito dal numero. Es. +491711234567.</t>
         </is>
       </c>
-      <c r="D19" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E19" s="56" t="n">
+      <c r="D19" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E19" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F19" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G19" s="56" t="inlineStr">
+      <c r="F19" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G19" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.cellulare</t>
         </is>
       </c>
-      <c r="H19" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I19" s="56" t="n">
+      <c r="H19" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="J19" s="59" t="inlineStr">
+      <c r="J19" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19009,7 +19021,7 @@
           <t>Valore integrale, formato +XX... (sorgente 35, ICD 30): non si tronca</t>
         </is>
       </c>
-      <c r="L19" s="56" t="inlineStr">
+      <c r="L19" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19017,7 +19029,7 @@
     </row>
     <row r="20">
       <c r="A20" s="17" t="n"/>
-      <c r="B20" s="56" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.contactEMail</t>
         </is>
@@ -19028,33 +19040,33 @@
 IT: Indirizzo email del contatto principale; vedere anche l'allegato A09 - matrice del servizio di preavviso via email.</t>
         </is>
       </c>
-      <c r="D20" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E20" s="56" t="n">
+      <c r="D20" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E20" s="60" t="n">
         <v>80</v>
       </c>
-      <c r="F20" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G20" s="56" t="inlineStr">
+      <c r="F20" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G20" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.email</t>
         </is>
       </c>
-      <c r="H20" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="56" t="n">
+      <c r="H20" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="60" t="n">
         <v>50</v>
       </c>
-      <c r="J20" s="59" t="inlineStr">
+      <c r="J20" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19064,7 +19076,7 @@
           <t>Valore integrale (sorgente 80, ICD 50): non si tronca</t>
         </is>
       </c>
-      <c r="L20" s="56" t="inlineStr">
+      <c r="L20" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19072,7 +19084,7 @@
     </row>
     <row r="21">
       <c r="A21" s="17" t="n"/>
-      <c r="B21" s="56" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.companyName</t>
         </is>
@@ -19083,33 +19095,33 @@
 IT: Per spedizioni "toB" nome dell'azienda o organizzazione; per spedizioni "toC" nome del destinatario. Stampato sulla 1a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D21" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E21" s="56" t="n">
+      <c r="D21" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F21" s="56" t="inlineStr">
+      <c r="F21" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G21" s="56" t="inlineStr">
+      <c r="G21" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.ragione_sociale</t>
         </is>
       </c>
-      <c r="H21" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I21" s="56" t="n">
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I21" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="J21" s="59" t="inlineStr">
+      <c r="J21" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19119,11 +19131,11 @@
           <t>40 -&gt; 40</t>
         </is>
       </c>
-      <c r="L21" s="56" t="inlineStr"/>
+      <c r="L21" s="60" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n"/>
-      <c r="B22" s="56" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.additionalAddressInfo1</t>
         </is>
@@ -19134,33 +19146,33 @@
 IT: Informazioni aggiuntive sull'indirizzo (reparto, edificio, piano, codice porta, stanza, numero locker...). Stampato sulla 3a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D22" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E22" s="56" t="n">
+      <c r="D22" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F22" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G22" s="56" t="inlineStr">
+      <c r="F22" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G22" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.note1</t>
         </is>
       </c>
-      <c r="H22" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="56" t="n">
+      <c r="H22" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I22" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="J22" s="59" t="inlineStr">
+      <c r="J22" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19170,7 +19182,7 @@
           <t>Valore integrale (sorgente 40): non si tronca</t>
         </is>
       </c>
-      <c r="L22" s="56" t="inlineStr">
+      <c r="L22" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19178,7 +19190,7 @@
     </row>
     <row r="23">
       <c r="A23" s="17" t="n"/>
-      <c r="B23" s="56" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.additionalAddressInfo2</t>
         </is>
@@ -19189,33 +19201,33 @@
 IT: Informazioni aggiuntive sull'indirizzo (reparto, edificio, piano, codice porta, stanza, numero locker...). Stampato sulla 4a riga indirizzo dell'EUROPLATE. Per le spedizioni PUDO contiene PS (Parcel Shop) o PT (Parcel Terminal).</t>
         </is>
       </c>
-      <c r="D23" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E23" s="56" t="n">
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F23" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G23" s="56" t="inlineStr">
+      <c r="F23" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G23" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.note2</t>
         </is>
       </c>
-      <c r="H23" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I23" s="56" t="n">
+      <c r="H23" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I23" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="J23" s="59" t="inlineStr">
+      <c r="J23" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19225,7 +19237,7 @@
           <t>Valore integrale (sorgente 40): non si tronca</t>
         </is>
       </c>
-      <c r="L23" s="56" t="inlineStr">
+      <c r="L23" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19233,7 +19245,7 @@
     </row>
     <row r="24">
       <c r="A24" s="17" t="n"/>
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.street</t>
         </is>
@@ -19244,33 +19256,33 @@
 IT: Via + numero civico, se il civico non è trasmesso a parte nel campo StreetNumber. Stampato sulla 5a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D24" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E24" s="56" t="n">
+      <c r="D24" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E24" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F24" s="56" t="inlineStr">
+      <c r="F24" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G24" s="56" t="inlineStr">
+      <c r="G24" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.indirizzo</t>
         </is>
       </c>
-      <c r="H24" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="56" t="n">
+      <c r="H24" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="J24" s="59" t="inlineStr">
+      <c r="J24" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19280,11 +19292,11 @@
           <t>40 -&gt; 40</t>
         </is>
       </c>
-      <c r="L24" s="56" t="inlineStr"/>
+      <c r="L24" s="60" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n"/>
-      <c r="B25" s="56" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.streetNumber</t>
         </is>
@@ -19295,33 +19307,33 @@
 IT: Numero civico, stampato sulla 5a riga dell'EUROPLATE. Solo se il sistema del partner mittente supporta la trasmissione separata del civico; altrimenti il civico va nello stesso campo della via.</t>
         </is>
       </c>
-      <c r="D25" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E25" s="56" t="n">
+      <c r="D25" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E25" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F25" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G25" s="56" t="inlineStr">
+      <c r="F25" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G25" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.numero_civico</t>
         </is>
       </c>
-      <c r="H25" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I25" s="56" t="n">
+      <c r="H25" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I25" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J25" s="59" t="inlineStr">
+      <c r="J25" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19331,7 +19343,7 @@
           <t>Valore integrale (sorgente 40, ICD 5): non si tronca</t>
         </is>
       </c>
-      <c r="L25" s="56" t="inlineStr">
+      <c r="L25" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19339,7 +19351,7 @@
     </row>
     <row r="26">
       <c r="A26" s="17" t="n"/>
-      <c r="B26" s="56" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.region</t>
         </is>
@@ -19350,33 +19362,33 @@
 IT: Regione, provincia o contea.</t>
         </is>
       </c>
-      <c r="D26" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E26" s="56" t="n">
+      <c r="D26" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E26" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F26" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G26" s="56" t="inlineStr">
+      <c r="F26" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G26" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.provincia</t>
         </is>
       </c>
-      <c r="H26" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I26" s="56" t="n">
+      <c r="H26" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="58" t="inlineStr">
+      <c r="J26" s="62" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -19386,7 +19398,7 @@
           <t>region (40, testo libero) non e' la sigla provincia: valorizzare solo se IT e sigla valida, altrimenti lasciare alla normalizzazione</t>
         </is>
       </c>
-      <c r="L26" s="56" t="inlineStr">
+      <c r="L26" s="60" t="inlineStr">
         <is>
           <t>PA-22</t>
         </is>
@@ -19394,7 +19406,7 @@
     </row>
     <row r="27">
       <c r="A27" s="17" t="n"/>
-      <c r="B27" s="56" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.city</t>
         </is>
@@ -19405,33 +19417,33 @@
 IT: Città o località postale, stampata sulla 6a riga dell'EUROPLATE troncata a 30 caratteri.</t>
         </is>
       </c>
-      <c r="D27" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="56" t="n">
+      <c r="D27" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E27" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F27" s="56" t="inlineStr">
+      <c r="F27" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G27" s="56" t="inlineStr">
+      <c r="G27" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.localita</t>
         </is>
       </c>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I27" s="56" t="n">
+      <c r="I27" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="J27" s="59" t="inlineStr">
+      <c r="J27" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19441,11 +19453,11 @@
           <t>Obbligatorio ICD; obbligatorio anche in EURODIS</t>
         </is>
       </c>
-      <c r="L27" s="56" t="inlineStr"/>
+      <c r="L27" s="60" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n"/>
-      <c r="B28" s="56" t="inlineStr">
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.zipcode</t>
         </is>
@@ -19456,33 +19468,33 @@
 IT: CAP, stampato sulla 6a riga dell'EUROPLATE (alfanumerico per il Regno Unito, senza indicatore di nazione; formato validato, corrispondenza con l'indirizzo no).</t>
         </is>
       </c>
-      <c r="D28" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="56" t="n">
+      <c r="D28" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="60" t="n">
         <v>9</v>
       </c>
-      <c r="F28" s="56" t="inlineStr">
+      <c r="F28" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G28" s="56" t="inlineStr">
+      <c r="G28" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.cap</t>
         </is>
       </c>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I28" s="56" t="n">
+      <c r="I28" s="60" t="n">
         <v>9</v>
       </c>
-      <c r="J28" s="59" t="inlineStr">
+      <c r="J28" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19492,11 +19504,11 @@
           <t>Obbligatorio ICD; obbligatorio anche in EURODIS</t>
         </is>
       </c>
-      <c r="L28" s="56" t="inlineStr"/>
+      <c r="L28" s="60" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>
-      <c r="B29" s="56" t="inlineStr">
+      <c r="B29" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.countryCode</t>
         </is>
@@ -19507,33 +19519,33 @@
 IT: Codice nazione ISO 3166 alpha-2, verificato sul database della piattaforma. Stampato sulla 6a riga dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D29" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E29" s="56" t="n">
+      <c r="D29" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E29" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="56" t="inlineStr">
+      <c r="F29" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G29" s="56" t="inlineStr">
+      <c r="G29" s="60" t="inlineStr">
         <is>
           <t>spedizione.destinatario.codice_nazione_iso_2</t>
         </is>
       </c>
-      <c r="H29" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I29" s="56" t="n">
+      <c r="H29" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="59" t="inlineStr">
+      <c r="J29" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19543,11 +19555,11 @@
           <t>countryCode e' ISO2: va solo qui (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L29" s="56" t="inlineStr"/>
+      <c r="L29" s="60" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n"/>
-      <c r="B30" s="56" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.additionalConsigneeInfo</t>
         </is>
@@ -19558,31 +19570,31 @@
 IT: Informazioni aggiuntive del mittente per il destinatario o istruzioni di consegna.</t>
         </is>
       </c>
-      <c r="D30" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E30" s="56" t="n">
+      <c r="D30" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E30" s="60" t="n">
         <v>70</v>
       </c>
-      <c r="F30" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G30" s="56" t="inlineStr">
+      <c r="F30" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G30" s="60" t="inlineStr">
         <is>
           <t>spedizione.consegna.note</t>
         </is>
       </c>
-      <c r="H30" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="56" t="n"/>
-      <c r="J30" s="57" t="inlineStr">
+      <c r="H30" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="60" t="n"/>
+      <c r="J30" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -19592,11 +19604,11 @@
           <t>Istruzioni di consegna: concatenare i due campi se entrambi presenti (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L30" s="56" t="inlineStr"/>
+      <c r="L30" s="60" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n"/>
-      <c r="B31" s="56" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.gatewayAssigned</t>
         </is>
@@ -19607,27 +19619,27 @@
 IT: Codice del gateway assegnato all'indirizzo (gateway di ingresso per l'indirizzo di consegna, di uscita per quello del mittente), come da manuale di rete A12.</t>
         </is>
       </c>
-      <c r="D31" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E31" s="56" t="n">
+      <c r="D31" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E31" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G31" s="56" t="inlineStr">
+      <c r="F31" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G31" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H31" s="56" t="inlineStr"/>
-      <c r="I31" s="56" t="inlineStr"/>
-      <c r="J31" s="58" t="inlineStr">
+      <c r="H31" s="60" t="inlineStr"/>
+      <c r="I31" s="60" t="inlineStr"/>
+      <c r="J31" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -19637,7 +19649,7 @@
           <t>Da non mappare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L31" s="56" t="inlineStr"/>
+      <c r="L31" s="60" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
@@ -19645,7 +19657,7 @@
           <t xml:space="preserve">[era su —] [era su spedizione.codici_servizi] da non mappare ma mettilo come punto aperto di sevirita bassa </t>
         </is>
       </c>
-      <c r="B32" s="56" t="inlineStr">
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.pudoID</t>
         </is>
@@ -19656,43 +19668,43 @@
 IT: Id della stazione PUDO (punto di ritiro e consegna) per le spedizioni con servizio di consegna Z.</t>
         </is>
       </c>
-      <c r="D32" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E32" s="56" t="n">
+      <c r="D32" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E32" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F32" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G32" s="56" t="inlineStr">
+      <c r="F32" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G32" s="60" t="inlineStr">
         <is>
           <t>spedizione.codici_servizi</t>
         </is>
       </c>
-      <c r="H32" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I32" s="56" t="n">
+      <c r="H32" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I32" s="60" t="n">
         <v>255</v>
       </c>
-      <c r="J32" s="57" t="inlineStr">
+      <c r="J32" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
-          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, W, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
-        </is>
-      </c>
-      <c r="L32" s="56" t="inlineStr">
+          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, W -&gt; APT000908 (matrice di test SDA, da confermare), Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
+        </is>
+      </c>
+      <c r="L32" s="60" t="inlineStr">
         <is>
           <t>DF-05, DF-07, DF-21, DF-22</t>
         </is>
@@ -19700,7 +19712,7 @@
     </row>
     <row r="33">
       <c r="A33" s="17" t="n"/>
-      <c r="B33" s="56" t="inlineStr">
+      <c r="B33" s="60" t="inlineStr">
         <is>
           <t>consigneeAddress.pudoID</t>
         </is>
@@ -19711,33 +19723,33 @@
 IT: Id della stazione PUDO (punto di ritiro e consegna) per le spedizioni con servizio di consegna Z.</t>
         </is>
       </c>
-      <c r="D33" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E33" s="56" t="n">
+      <c r="D33" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E33" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F33" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G33" s="56" t="inlineStr">
+      <c r="F33" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G33" s="60" t="inlineStr">
         <is>
           <t>spedizione.consegna.codice_frazionario</t>
         </is>
       </c>
-      <c r="H33" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="56" t="n">
+      <c r="H33" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="60" t="n">
         <v>11</v>
       </c>
-      <c r="J33" s="57" t="inlineStr">
+      <c r="J33" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -19747,7 +19759,7 @@
           <t>Solo con deliveryService = Z: PUDO ID, e' il node di APT000947 (proposta 29-Oct)</t>
         </is>
       </c>
-      <c r="L33" s="56" t="inlineStr">
+      <c r="L33" s="60" t="inlineStr">
         <is>
           <t>DF-14, DF-23</t>
         </is>
@@ -19755,7 +19767,7 @@
     </row>
     <row r="34">
       <c r="A34" s="17" t="n"/>
-      <c r="B34" s="56" t="inlineStr">
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.contactName</t>
         </is>
@@ -19766,33 +19778,33 @@
 IT: Nome del contatto all'indirizzo, stampato sulla 2a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D34" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E34" s="56" t="n">
+      <c r="D34" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E34" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F34" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G34" s="56" t="inlineStr">
+      <c r="F34" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G34" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.rif_contatto</t>
         </is>
       </c>
-      <c r="H34" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="56" t="n">
+      <c r="H34" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="J34" s="59" t="inlineStr">
+      <c r="J34" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19802,7 +19814,7 @@
           <t>Valore integrale (sorgente 40, ICD 35): non si tronca</t>
         </is>
       </c>
-      <c r="L34" s="56" t="inlineStr">
+      <c r="L34" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19810,7 +19822,7 @@
     </row>
     <row r="35">
       <c r="A35" s="17" t="n"/>
-      <c r="B35" s="56" t="inlineStr">
+      <c r="B35" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.contactTelephone</t>
         </is>
@@ -19821,33 +19833,33 @@
 IT: Condizione per il servizio di prenotazione consegna: se il servizio è concordato fra i partner e il flag di prenotazione è presente in DeliveryService.</t>
         </is>
       </c>
-      <c r="D35" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E35" s="56" t="n">
+      <c r="D35" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E35" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="F35" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G35" s="56" t="inlineStr">
+      <c r="F35" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G35" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.telefono</t>
         </is>
       </c>
-      <c r="H35" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="56" t="n">
+      <c r="H35" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="J35" s="59" t="inlineStr">
+      <c r="J35" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19857,7 +19869,7 @@
           <t>30 -&gt; 30</t>
         </is>
       </c>
-      <c r="L35" s="56" t="inlineStr"/>
+      <c r="L35" s="60" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="37" t="inlineStr">
@@ -19865,7 +19877,7 @@
           <t xml:space="preserve">segna che noi non abbiamo il seconod numero di telegono da chiedere se serve </t>
         </is>
       </c>
-      <c r="B36" s="56" t="inlineStr">
+      <c r="B36" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.alternativeContactTelephone</t>
         </is>
@@ -19876,27 +19888,27 @@
 IT: Telefono di contatto alternativo (alfanumerico per ammettere il prefisso internazionale).</t>
         </is>
       </c>
-      <c r="D36" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E36" s="56" t="n">
+      <c r="D36" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E36" s="60" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G36" s="56" t="inlineStr">
+      <c r="F36" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G36" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H36" s="56" t="inlineStr"/>
-      <c r="I36" s="56" t="inlineStr"/>
-      <c r="J36" s="58" t="inlineStr">
+      <c r="H36" s="60" t="inlineStr"/>
+      <c r="I36" s="60" t="inlineStr"/>
+      <c r="J36" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -19906,7 +19918,7 @@
           <t>Il tracciato non ha un secondo numero di telefono: da chiedere se serve (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L36" s="56" t="inlineStr">
+      <c r="L36" s="60" t="inlineStr">
         <is>
           <t>DF-15</t>
         </is>
@@ -19914,7 +19926,7 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="n"/>
-      <c r="B37" s="56" t="inlineStr">
+      <c r="B37" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.contactSMS</t>
         </is>
@@ -19925,33 +19937,33 @@
 IT: Numero SMS del contatto principale. Formato: prefisso internazionale (+XX) seguito dal numero. Es. +491711234567.</t>
         </is>
       </c>
-      <c r="D37" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E37" s="56" t="n">
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E37" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F37" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G37" s="56" t="inlineStr">
+      <c r="F37" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G37" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.cellulare</t>
         </is>
       </c>
-      <c r="H37" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I37" s="56" t="n">
+      <c r="H37" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I37" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="J37" s="59" t="inlineStr">
+      <c r="J37" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -19961,7 +19973,7 @@
           <t>Valore integrale, formato +XX... (sorgente 35, ICD 30): non si tronca</t>
         </is>
       </c>
-      <c r="L37" s="56" t="inlineStr">
+      <c r="L37" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -19969,7 +19981,7 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n"/>
-      <c r="B38" s="56" t="inlineStr">
+      <c r="B38" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.contactEMail</t>
         </is>
@@ -19980,33 +19992,33 @@
 IT: Indirizzo email del contatto principale; vedere anche l'allegato A09 - matrice del servizio di preavviso via email.</t>
         </is>
       </c>
-      <c r="D38" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E38" s="56" t="n">
+      <c r="D38" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E38" s="60" t="n">
         <v>80</v>
       </c>
-      <c r="F38" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G38" s="56" t="inlineStr">
+      <c r="F38" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G38" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.email</t>
         </is>
       </c>
-      <c r="H38" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" s="56" t="n">
+      <c r="H38" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="60" t="n">
         <v>50</v>
       </c>
-      <c r="J38" s="59" t="inlineStr">
+      <c r="J38" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20016,7 +20028,7 @@
           <t>Valore integrale (sorgente 80, ICD 50): non si tronca</t>
         </is>
       </c>
-      <c r="L38" s="56" t="inlineStr">
+      <c r="L38" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -20024,7 +20036,7 @@
     </row>
     <row r="39">
       <c r="A39" s="17" t="n"/>
-      <c r="B39" s="56" t="inlineStr">
+      <c r="B39" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.companyName</t>
         </is>
@@ -20035,31 +20047,31 @@
 IT: Per spedizioni "toB" nome dell'azienda o organizzazione; per spedizioni "toC" nome del destinatario. Stampato sulla 1a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D39" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E39" s="56" t="n">
+      <c r="D39" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E39" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F39" s="56" t="inlineStr">
+      <c r="F39" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G39" s="56" t="inlineStr">
+      <c r="G39" s="60" t="inlineStr">
         <is>
           <t>cliente.ragione_sociale</t>
         </is>
       </c>
-      <c r="H39" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="56" t="n"/>
-      <c r="J39" s="59" t="inlineStr">
+      <c r="H39" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="60" t="n"/>
+      <c r="J39" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20069,11 +20081,11 @@
           <t>nell'esempio EUD_INVIOFILE coincide con la ragione sociale del mittente</t>
         </is>
       </c>
-      <c r="L39" s="56" t="inlineStr"/>
+      <c r="L39" s="60" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n"/>
-      <c r="B40" s="56" t="inlineStr">
+      <c r="B40" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.companyName</t>
         </is>
@@ -20084,33 +20096,33 @@
 IT: Per spedizioni "toB" nome dell'azienda o organizzazione; per spedizioni "toC" nome del destinatario. Stampato sulla 1a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D40" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E40" s="56" t="n">
+      <c r="D40" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E40" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F40" s="56" t="inlineStr">
+      <c r="F40" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G40" s="56" t="inlineStr">
+      <c r="G40" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.ragione_sociale</t>
         </is>
       </c>
-      <c r="H40" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I40" s="56" t="n">
+      <c r="H40" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I40" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="J40" s="59" t="inlineStr">
+      <c r="J40" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20120,11 +20132,11 @@
           <t>40 -&gt; 40</t>
         </is>
       </c>
-      <c r="L40" s="56" t="inlineStr"/>
+      <c r="L40" s="60" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n"/>
-      <c r="B41" s="56" t="inlineStr">
+      <c r="B41" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.additionalAddressInfo1</t>
         </is>
@@ -20135,33 +20147,33 @@
 IT: Informazioni aggiuntive sull'indirizzo (reparto, edificio, piano, codice porta, stanza, numero locker...). Stampato sulla 3a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D41" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E41" s="56" t="n">
+      <c r="D41" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F41" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G41" s="56" t="inlineStr">
+      <c r="F41" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G41" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.note1</t>
         </is>
       </c>
-      <c r="H41" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="56" t="n">
+      <c r="H41" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="J41" s="59" t="inlineStr">
+      <c r="J41" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20171,7 +20183,7 @@
           <t>Valore integrale (sorgente 40): non si tronca</t>
         </is>
       </c>
-      <c r="L41" s="56" t="inlineStr">
+      <c r="L41" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -20179,7 +20191,7 @@
     </row>
     <row r="42">
       <c r="A42" s="17" t="n"/>
-      <c r="B42" s="56" t="inlineStr">
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.additionalAddressInfo2</t>
         </is>
@@ -20190,33 +20202,33 @@
 IT: Informazioni aggiuntive sull'indirizzo (reparto, edificio, piano, codice porta, stanza, numero locker...). Stampato sulla 4a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D42" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E42" s="56" t="n">
+      <c r="D42" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E42" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F42" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G42" s="56" t="inlineStr">
+      <c r="F42" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.note2</t>
         </is>
       </c>
-      <c r="H42" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="56" t="n">
+      <c r="H42" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="J42" s="59" t="inlineStr">
+      <c r="J42" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20226,7 +20238,7 @@
           <t>Valore integrale (sorgente 40): non si tronca</t>
         </is>
       </c>
-      <c r="L42" s="56" t="inlineStr">
+      <c r="L42" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -20234,7 +20246,7 @@
     </row>
     <row r="43">
       <c r="A43" s="17" t="n"/>
-      <c r="B43" s="56" t="inlineStr">
+      <c r="B43" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.street</t>
         </is>
@@ -20245,33 +20257,33 @@
 IT: Via + numero civico, se il civico non è trasmesso a parte nel campo StreetNumber. Stampato sulla 5a riga indirizzo dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D43" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E43" s="56" t="n">
+      <c r="D43" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E43" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F43" s="56" t="inlineStr">
+      <c r="F43" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G43" s="56" t="inlineStr">
+      <c r="G43" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.indirizzo</t>
         </is>
       </c>
-      <c r="H43" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="56" t="n">
+      <c r="H43" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="J43" s="59" t="inlineStr">
+      <c r="J43" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20281,11 +20293,11 @@
           <t>40 -&gt; 40</t>
         </is>
       </c>
-      <c r="L43" s="56" t="inlineStr"/>
+      <c r="L43" s="60" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n"/>
-      <c r="B44" s="56" t="inlineStr">
+      <c r="B44" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.streetNumber</t>
         </is>
@@ -20296,33 +20308,33 @@
 IT: Numero civico, stampato sulla 5a riga dell'EUROPLATE. Solo se il sistema del partner mittente supporta la trasmissione separata del civico; altrimenti il civico va nello stesso campo della via.</t>
         </is>
       </c>
-      <c r="D44" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E44" s="56" t="n">
+      <c r="D44" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E44" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F44" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G44" s="56" t="inlineStr">
+      <c r="F44" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G44" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.numero_civico</t>
         </is>
       </c>
-      <c r="H44" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I44" s="56" t="n">
+      <c r="H44" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="59" t="inlineStr">
+      <c r="J44" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20332,7 +20344,7 @@
           <t>Valore integrale (sorgente 40, ICD 5): non si tronca</t>
         </is>
       </c>
-      <c r="L44" s="56" t="inlineStr">
+      <c r="L44" s="60" t="inlineStr">
         <is>
           <t>PA-16</t>
         </is>
@@ -20340,7 +20352,7 @@
     </row>
     <row r="45">
       <c r="A45" s="17" t="n"/>
-      <c r="B45" s="56" t="inlineStr">
+      <c r="B45" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.region</t>
         </is>
@@ -20351,33 +20363,33 @@
 IT: Regione, provincia o contea.</t>
         </is>
       </c>
-      <c r="D45" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E45" s="56" t="n">
+      <c r="D45" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E45" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F45" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G45" s="56" t="inlineStr">
+      <c r="F45" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G45" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.provincia</t>
         </is>
       </c>
-      <c r="H45" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="56" t="n">
+      <c r="H45" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="58" t="inlineStr">
+      <c r="J45" s="62" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -20387,7 +20399,7 @@
           <t>region (40, testo libero) non e' la sigla provincia: valorizzare solo se IT e sigla valida, altrimenti lasciare alla normalizzazione</t>
         </is>
       </c>
-      <c r="L45" s="56" t="inlineStr">
+      <c r="L45" s="60" t="inlineStr">
         <is>
           <t>PA-22</t>
         </is>
@@ -20395,7 +20407,7 @@
     </row>
     <row r="46">
       <c r="A46" s="17" t="n"/>
-      <c r="B46" s="56" t="inlineStr">
+      <c r="B46" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.city</t>
         </is>
@@ -20406,33 +20418,33 @@
 IT: Città o località postale, stampata sulla 6a riga dell'EUROPLATE troncata a 30 caratteri.</t>
         </is>
       </c>
-      <c r="D46" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E46" s="56" t="n">
+      <c r="D46" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E46" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F46" s="56" t="inlineStr">
+      <c r="F46" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G46" s="56" t="inlineStr">
+      <c r="G46" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.localita</t>
         </is>
       </c>
-      <c r="H46" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I46" s="56" t="n">
+      <c r="H46" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="J46" s="59" t="inlineStr">
+      <c r="J46" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20442,11 +20454,11 @@
           <t>35 -&gt; 40</t>
         </is>
       </c>
-      <c r="L46" s="56" t="inlineStr"/>
+      <c r="L46" s="60" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n"/>
-      <c r="B47" s="56" t="inlineStr">
+      <c r="B47" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.zipcode</t>
         </is>
@@ -20457,33 +20469,33 @@
 IT: CAP, stampato sulla 6a riga dell'EUROPLATE (alfanumerico per il Regno Unito, senza indicatore di nazione; formato validato, corrispondenza con l'indirizzo no).</t>
         </is>
       </c>
-      <c r="D47" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E47" s="56" t="n">
+      <c r="D47" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E47" s="60" t="n">
         <v>9</v>
       </c>
-      <c r="F47" s="56" t="inlineStr">
+      <c r="F47" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G47" s="56" t="inlineStr">
+      <c r="G47" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.cap</t>
         </is>
       </c>
-      <c r="H47" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I47" s="56" t="n">
+      <c r="H47" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="60" t="n">
         <v>9</v>
       </c>
-      <c r="J47" s="59" t="inlineStr">
+      <c r="J47" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20493,7 +20505,7 @@
           <t>9 -&gt; 9. CAP esteri ammessi</t>
         </is>
       </c>
-      <c r="L47" s="56" t="inlineStr"/>
+      <c r="L47" s="60" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="37" t="inlineStr">
@@ -20502,7 +20514,7 @@
 [era su spedizione.tipo_spedizione] questo è proprio sbagliato non centra nulla tipo_spedizione</t>
         </is>
       </c>
-      <c r="B48" s="56" t="inlineStr">
+      <c r="B48" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.countryCode</t>
         </is>
@@ -20513,33 +20525,33 @@
 IT: Codice nazione ISO 3166 alpha-2, verificato sul database della piattaforma. Stampato sulla 6a riga dell'EUROPLATE.</t>
         </is>
       </c>
-      <c r="D48" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E48" s="56" t="n">
+      <c r="D48" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E48" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="56" t="inlineStr">
+      <c r="F48" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G48" s="56" t="inlineStr">
+      <c r="G48" s="60" t="inlineStr">
         <is>
           <t>spedizione.mittente.codice_nazione_iso_2</t>
         </is>
       </c>
-      <c r="H48" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I48" s="56" t="n">
+      <c r="H48" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I48" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="59" t="inlineStr">
+      <c r="J48" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -20549,7 +20561,7 @@
           <t>countryCode e' ISO2: va solo qui (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L48" s="56" t="inlineStr"/>
+      <c r="L48" s="60" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="37" t="inlineStr">
@@ -20557,7 +20569,7 @@
           <t xml:space="preserve">[era su —] dovrsti avere note anche dentro consegna </t>
         </is>
       </c>
-      <c r="B49" s="56" t="inlineStr">
+      <c r="B49" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.additionalConsigneeInfo</t>
         </is>
@@ -20568,31 +20580,31 @@
 IT: Informazioni aggiuntive del mittente per il destinatario o istruzioni di consegna.</t>
         </is>
       </c>
-      <c r="D49" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E49" s="56" t="n">
+      <c r="D49" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E49" s="60" t="n">
         <v>70</v>
       </c>
-      <c r="F49" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G49" s="56" t="inlineStr">
+      <c r="F49" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G49" s="60" t="inlineStr">
         <is>
           <t>spedizione.consegna.note</t>
         </is>
       </c>
-      <c r="H49" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I49" s="56" t="n"/>
-      <c r="J49" s="57" t="inlineStr">
+      <c r="H49" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I49" s="60" t="n"/>
+      <c r="J49" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -20602,7 +20614,7 @@
           <t>Istruzioni di consegna: concatenare i due campi se entrambi presenti (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L49" s="56" t="inlineStr"/>
+      <c r="L49" s="60" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="37" t="inlineStr">
@@ -20610,7 +20622,7 @@
           <t>no n mappare</t>
         </is>
       </c>
-      <c r="B50" s="56" t="inlineStr">
+      <c r="B50" s="60" t="inlineStr">
         <is>
           <t>shipperAddress.gatewayAssigned</t>
         </is>
@@ -20621,27 +20633,27 @@
 IT: Codice del gateway assegnato all'indirizzo (gateway di ingresso per l'indirizzo di consegna, di uscita per quello del mittente), come da manuale di rete A12.</t>
         </is>
       </c>
-      <c r="D50" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E50" s="56" t="n">
+      <c r="D50" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E50" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F50" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G50" s="56" t="inlineStr">
+      <c r="F50" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G50" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H50" s="56" t="inlineStr"/>
-      <c r="I50" s="56" t="inlineStr"/>
-      <c r="J50" s="58" t="inlineStr">
+      <c r="H50" s="60" t="inlineStr"/>
+      <c r="I50" s="60" t="inlineStr"/>
+      <c r="J50" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -20651,11 +20663,11 @@
           <t>Da non mappare (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L50" s="56" t="inlineStr"/>
+      <c r="L50" s="60" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n"/>
-      <c r="B51" s="56" t="inlineStr">
+      <c r="B51" s="60" t="inlineStr">
         <is>
           <t>returnAddress</t>
         </is>
@@ -20665,25 +20677,25 @@
           <t>IT: (Oggetto) Indirizzo di reso.</t>
         </is>
       </c>
-      <c r="D51" s="56" t="inlineStr">
+      <c r="D51" s="60" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E51" s="56" t="inlineStr"/>
-      <c r="F51" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G51" s="56" t="inlineStr">
+      <c r="E51" s="60" t="inlineStr"/>
+      <c r="F51" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G51" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H51" s="56" t="inlineStr"/>
-      <c r="I51" s="56" t="inlineStr"/>
-      <c r="J51" s="58" t="inlineStr">
+      <c r="H51" s="60" t="inlineStr"/>
+      <c r="I51" s="60" t="inlineStr"/>
+      <c r="J51" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -20693,7 +20705,7 @@
           <t>Nessun oggetto ICD per indirizzo di reso</t>
         </is>
       </c>
-      <c r="L51" s="56" t="inlineStr">
+      <c r="L51" s="60" t="inlineStr">
         <is>
           <t>PA-17</t>
         </is>
@@ -20701,7 +20713,7 @@
     </row>
     <row r="52">
       <c r="A52" s="17" t="n"/>
-      <c r="B52" s="56" t="inlineStr">
+      <c r="B52" s="60" t="inlineStr">
         <is>
           <t>remunerationAddress</t>
         </is>
@@ -20711,25 +20723,25 @@
           <t>IT: (Oggetto) Indirizzo di fatturazione/remunerazione.</t>
         </is>
       </c>
-      <c r="D52" s="56" t="inlineStr">
+      <c r="D52" s="60" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E52" s="56" t="inlineStr"/>
-      <c r="F52" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G52" s="56" t="inlineStr">
+      <c r="E52" s="60" t="inlineStr"/>
+      <c r="F52" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G52" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H52" s="56" t="inlineStr"/>
-      <c r="I52" s="56" t="inlineStr"/>
-      <c r="J52" s="58" t="inlineStr">
+      <c r="H52" s="60" t="inlineStr"/>
+      <c r="I52" s="60" t="inlineStr"/>
+      <c r="J52" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -20739,11 +20751,11 @@
           <t>Nessun oggetto ICD</t>
         </is>
       </c>
-      <c r="L52" s="56" t="inlineStr"/>
+      <c r="L52" s="60" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n"/>
-      <c r="B53" s="56" t="inlineStr">
+      <c r="B53" s="60" t="inlineStr">
         <is>
           <t>bookingInAddress</t>
         </is>
@@ -20753,25 +20765,25 @@
           <t>IT: (Oggetto) Indirizzo per la prenotazione della consegna.</t>
         </is>
       </c>
-      <c r="D53" s="56" t="inlineStr">
+      <c r="D53" s="60" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E53" s="56" t="inlineStr"/>
-      <c r="F53" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G53" s="56" t="inlineStr">
+      <c r="E53" s="60" t="inlineStr"/>
+      <c r="F53" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G53" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H53" s="56" t="inlineStr"/>
-      <c r="I53" s="56" t="inlineStr"/>
-      <c r="J53" s="58" t="inlineStr">
+      <c r="H53" s="60" t="inlineStr"/>
+      <c r="I53" s="60" t="inlineStr"/>
+      <c r="J53" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -20781,7 +20793,7 @@
           <t>Nessun oggetto ICD</t>
         </is>
       </c>
-      <c r="L53" s="56" t="inlineStr"/>
+      <c r="L53" s="60" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="37" t="inlineStr">
@@ -20790,7 +20802,7 @@
 [era su spedizione.codici_servizi] punto aperto</t>
         </is>
       </c>
-      <c r="B54" s="56" t="inlineStr">
+      <c r="B54" s="60" t="inlineStr">
         <is>
           <t>deliveryService.deliveryService</t>
         </is>
@@ -20801,43 +20813,43 @@
 IT: Deve essere D (giorno), T (a orario), M (mattina), A (pomeriggio), E (sera), 6 (sabato), 7 (domenica), B (su prenotazione), W (finestra di consegna), F (entro le 10:00) o Z (consegna in punto PUDO).</t>
         </is>
       </c>
-      <c r="D54" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E54" s="56" t="n">
+      <c r="D54" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E54" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="56" t="inlineStr">
+      <c r="F54" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G54" s="56" t="inlineStr">
+      <c r="G54" s="60" t="inlineStr">
         <is>
           <t>spedizione.codici_servizi</t>
         </is>
       </c>
-      <c r="H54" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I54" s="56" t="n">
+      <c r="H54" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I54" s="60" t="n">
         <v>255</v>
       </c>
-      <c r="J54" s="57" t="inlineStr">
+      <c r="J54" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
       <c r="K54" s="17" t="inlineStr">
         <is>
-          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, W, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
-        </is>
-      </c>
-      <c r="L54" s="56" t="inlineStr">
+          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, W -&gt; APT000908 (matrice di test SDA, da confermare), Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
+        </is>
+      </c>
+      <c r="L54" s="60" t="inlineStr">
         <is>
           <t>DF-05, DF-07, DF-21, DF-22</t>
         </is>
@@ -20849,7 +20861,7 @@
           <t>questo deve essere rimappato dentro il campo no firma se vale uno dei due  S (firma richiesta), N (firma non richiesta),</t>
         </is>
       </c>
-      <c r="B55" s="56" t="inlineStr">
+      <c r="B55" s="60" t="inlineStr">
         <is>
           <t>deliveryService.deliveryType</t>
         </is>
@@ -20860,33 +20872,33 @@
 IT: Deve essere S (firma richiesta), N (firma non richiesta), D (deposito sicuro), I (identificazione sicura), B (consolidamento presso il partner di drop-off) o C (consolidamento presso il partner di consegna diverso dall'iniziatore). B e C valgono solo per resi via PUDO.</t>
         </is>
       </c>
-      <c r="D55" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E55" s="56" t="n">
+      <c r="D55" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E55" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="56" t="inlineStr">
+      <c r="F55" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G55" s="56" t="inlineStr">
+      <c r="G55" s="60" t="inlineStr">
         <is>
           <t>cliente.no_firma</t>
         </is>
       </c>
-      <c r="H55" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I55" s="56" t="n">
+      <c r="H55" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I55" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="57" t="inlineStr">
+      <c r="J55" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -20896,11 +20908,11 @@
           <t>S (firma richiesta) -&gt; "N"; N (firma non richiesta) -&gt; "S"; altri valori -&gt; vuoto (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L55" s="56" t="inlineStr"/>
+      <c r="L55" s="60" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="n"/>
-      <c r="B56" s="56" t="inlineStr">
+      <c r="B56" s="60" t="inlineStr">
         <is>
           <t>deliveryService.deliveryType</t>
         </is>
@@ -20911,33 +20923,33 @@
 IT: Deve essere S (firma richiesta), N (firma non richiesta), D (deposito sicuro), I (identificazione sicura), B (consolidamento presso il partner di drop-off) o C (consolidamento presso il partner di consegna diverso dall'iniziatore). B e C valgono solo per resi via PUDO.</t>
         </is>
       </c>
-      <c r="D56" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E56" s="56" t="n">
+      <c r="D56" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E56" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="56" t="inlineStr">
+      <c r="F56" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G56" s="56" t="inlineStr">
+      <c r="G56" s="60" t="inlineStr">
         <is>
           <t>spedizione.consegna.modalita</t>
         </is>
       </c>
-      <c r="H56" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I56" s="56" t="n">
+      <c r="H56" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I56" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="58" t="inlineStr">
+      <c r="J56" s="62" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -20947,7 +20959,7 @@
           <t>Decodifica S/N/D/I/B/C -&gt; modalita SDA</t>
         </is>
       </c>
-      <c r="L56" s="56" t="inlineStr">
+      <c r="L56" s="60" t="inlineStr">
         <is>
           <t>PA-17</t>
         </is>
@@ -20955,7 +20967,7 @@
     </row>
     <row r="57">
       <c r="A57" s="17" t="n"/>
-      <c r="B57" s="56" t="inlineStr">
+      <c r="B57" s="60" t="inlineStr">
         <is>
           <t>deliveryService.secureDeliveryId</t>
         </is>
@@ -20966,27 +20978,27 @@
 IT: Id del deposito sicuro o id da usare per la consegna sicura.</t>
         </is>
       </c>
-      <c r="D57" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E57" s="56" t="n">
+      <c r="D57" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E57" s="60" t="n">
         <v>40</v>
       </c>
-      <c r="F57" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G57" s="56" t="inlineStr">
+      <c r="F57" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G57" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H57" s="56" t="inlineStr"/>
-      <c r="I57" s="56" t="inlineStr"/>
-      <c r="J57" s="58" t="inlineStr">
+      <c r="H57" s="60" t="inlineStr"/>
+      <c r="I57" s="60" t="inlineStr"/>
+      <c r="J57" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -20996,11 +21008,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L57" s="56" t="inlineStr"/>
+      <c r="L57" s="60" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="17" t="n"/>
-      <c r="B58" s="56" t="inlineStr">
+      <c r="B58" s="60" t="inlineStr">
         <is>
           <t>deliveryService.deliveryBookInRequired</t>
         </is>
@@ -21011,25 +21023,25 @@
 IT: Vero/falso: il partner di consegna deve concordare la prenotazione della consegna.</t>
         </is>
       </c>
-      <c r="D58" s="56" t="inlineStr">
+      <c r="D58" s="60" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E58" s="56" t="inlineStr"/>
-      <c r="F58" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G58" s="56" t="inlineStr">
+      <c r="E58" s="60" t="inlineStr"/>
+      <c r="F58" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G58" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H58" s="56" t="inlineStr"/>
-      <c r="I58" s="56" t="inlineStr"/>
-      <c r="J58" s="58" t="inlineStr">
+      <c r="H58" s="60" t="inlineStr"/>
+      <c r="I58" s="60" t="inlineStr"/>
+      <c r="J58" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21039,7 +21051,7 @@
           <t>Forse servizio accessorio via ce-rules</t>
         </is>
       </c>
-      <c r="L58" s="56" t="inlineStr">
+      <c r="L58" s="60" t="inlineStr">
         <is>
           <t>PA-03</t>
         </is>
@@ -21047,7 +21059,7 @@
     </row>
     <row r="59">
       <c r="A59" s="17" t="n"/>
-      <c r="B59" s="56" t="inlineStr">
+      <c r="B59" s="60" t="inlineStr">
         <is>
           <t>deliveryService.deliveryTimeWindowStart</t>
         </is>
@@ -21058,33 +21070,33 @@
 IT: Solo per il servizio a finestra di consegna e per servizi a orario specifico. Formato HH:mm:ss.</t>
         </is>
       </c>
-      <c r="D59" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E59" s="56" t="n">
+      <c r="D59" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E59" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="F59" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G59" s="56" t="inlineStr">
+      <c r="F59" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G59" s="60" t="inlineStr">
         <is>
           <t>spedizione.consegna.inizio_ora_consegna</t>
         </is>
       </c>
-      <c r="H59" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I59" s="56" t="n">
+      <c r="H59" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I59" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J59" s="57" t="inlineStr">
+      <c r="J59" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -21094,11 +21106,11 @@
           <t>HH:mm:ss -&gt; HH:mm</t>
         </is>
       </c>
-      <c r="L59" s="56" t="inlineStr"/>
+      <c r="L59" s="60" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="17" t="n"/>
-      <c r="B60" s="56" t="inlineStr">
+      <c r="B60" s="60" t="inlineStr">
         <is>
           <t>deliveryService.deliveryTimeWindowEnd</t>
         </is>
@@ -21109,33 +21121,33 @@
 IT: Solo per il servizio a finestra di consegna. Formato HH:mm:ss.</t>
         </is>
       </c>
-      <c r="D60" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E60" s="56" t="n">
+      <c r="D60" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E60" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="F60" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G60" s="56" t="inlineStr">
+      <c r="F60" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G60" s="60" t="inlineStr">
         <is>
           <t>spedizione.consegna.fine_ora_consegna</t>
         </is>
       </c>
-      <c r="H60" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I60" s="56" t="n">
+      <c r="H60" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I60" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J60" s="57" t="inlineStr">
+      <c r="J60" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -21145,7 +21157,7 @@
           <t>HH:mm:ss -&gt; HH:mm</t>
         </is>
       </c>
-      <c r="L60" s="56" t="inlineStr"/>
+      <c r="L60" s="60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="37" t="inlineStr">
@@ -21153,7 +21165,7 @@
           <t xml:space="preserve">chiedere se c'è un servizio consegna dedicato segna tra i punti aperti </t>
         </is>
       </c>
-      <c r="B61" s="56" t="inlineStr">
+      <c r="B61" s="60" t="inlineStr">
         <is>
           <t>deliveryService.deliveryDateWindowStart</t>
         </is>
@@ -21164,31 +21176,31 @@
 IT: Solo per il servizio a finestra di consegna con data specifica. Formato yyyy-MM-dd.</t>
         </is>
       </c>
-      <c r="D61" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E61" s="56" t="inlineStr"/>
-      <c r="F61" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G61" s="56" t="inlineStr">
+      <c r="D61" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E61" s="60" t="inlineStr"/>
+      <c r="F61" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G61" s="60" t="inlineStr">
         <is>
           <t>spedizione.consegna.data_consegna</t>
         </is>
       </c>
-      <c r="H61" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I61" s="56" t="n">
+      <c r="H61" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I61" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="J61" s="57" t="inlineStr">
+      <c r="J61" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -21198,7 +21210,7 @@
           <t>yyyy-MM-dd (commento Diego 23-Oct). Il servizio T non ha APT (DF-21) (proposta 29-Oct)</t>
         </is>
       </c>
-      <c r="L61" s="56" t="inlineStr">
+      <c r="L61" s="60" t="inlineStr">
         <is>
           <t>DF-06, DF-21</t>
         </is>
@@ -21206,7 +21218,7 @@
     </row>
     <row r="62">
       <c r="A62" s="17" t="n"/>
-      <c r="B62" s="56" t="inlineStr">
+      <c r="B62" s="60" t="inlineStr">
         <is>
           <t>deliveryService.deliveryDateWindowEnd</t>
         </is>
@@ -21217,25 +21229,25 @@
 IT: Solo per il servizio a finestra di consegna. Formato yyyy-MM-dd.</t>
         </is>
       </c>
-      <c r="D62" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E62" s="56" t="inlineStr"/>
-      <c r="F62" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G62" s="56" t="inlineStr">
+      <c r="D62" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E62" s="60" t="inlineStr"/>
+      <c r="F62" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G62" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H62" s="56" t="inlineStr"/>
-      <c r="I62" s="56" t="inlineStr"/>
-      <c r="J62" s="58" t="inlineStr">
+      <c r="H62" s="60" t="inlineStr"/>
+      <c r="I62" s="60" t="inlineStr"/>
+      <c r="J62" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21245,11 +21257,11 @@
           <t>ICD ha solo data_consegna</t>
         </is>
       </c>
-      <c r="L62" s="56" t="inlineStr"/>
+      <c r="L62" s="60" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n"/>
-      <c r="B63" s="56" t="inlineStr">
+      <c r="B63" s="60" t="inlineStr">
         <is>
           <t>deliveryService.completeDeliveryOnly</t>
         </is>
@@ -21260,25 +21272,25 @@
 IT: Vero se il cliente vuole tutti i colli in un'unica consegna, altrimenti falso.</t>
         </is>
       </c>
-      <c r="D63" s="56" t="inlineStr">
+      <c r="D63" s="60" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E63" s="56" t="inlineStr"/>
-      <c r="F63" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G63" s="56" t="inlineStr">
+      <c r="E63" s="60" t="inlineStr"/>
+      <c r="F63" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G63" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H63" s="56" t="inlineStr"/>
-      <c r="I63" s="56" t="inlineStr"/>
-      <c r="J63" s="58" t="inlineStr">
+      <c r="H63" s="60" t="inlineStr"/>
+      <c r="I63" s="60" t="inlineStr"/>
+      <c r="J63" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21288,11 +21300,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L63" s="56" t="inlineStr"/>
+      <c r="L63" s="60" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="17" t="n"/>
-      <c r="B64" s="56" t="inlineStr">
+      <c r="B64" s="60" t="inlineStr">
         <is>
           <t>deliveryService.additionalNotification</t>
         </is>
@@ -21303,25 +21315,25 @@
 IT: Dati di contatto di un terzo da avvisare della consegna.</t>
         </is>
       </c>
-      <c r="D64" s="56" t="inlineStr">
+      <c r="D64" s="60" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E64" s="56" t="inlineStr"/>
-      <c r="F64" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G64" s="56" t="inlineStr">
+      <c r="E64" s="60" t="inlineStr"/>
+      <c r="F64" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G64" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H64" s="56" t="inlineStr"/>
-      <c r="I64" s="56" t="inlineStr"/>
-      <c r="J64" s="58" t="inlineStr">
+      <c r="H64" s="60" t="inlineStr"/>
+      <c r="I64" s="60" t="inlineStr"/>
+      <c r="J64" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21331,11 +21343,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L64" s="56" t="inlineStr"/>
+      <c r="L64" s="60" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n"/>
-      <c r="B65" s="56" t="inlineStr">
+      <c r="B65" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService</t>
         </is>
@@ -21345,41 +21357,41 @@
           <t>IT: (Oggetto) Contrassegno: presente se la spedizione è in contrassegno.</t>
         </is>
       </c>
-      <c r="D65" s="56" t="inlineStr">
+      <c r="D65" s="60" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E65" s="56" t="inlineStr"/>
-      <c r="F65" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G65" s="56" t="inlineStr">
+      <c r="E65" s="60" t="inlineStr"/>
+      <c r="F65" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G65" s="60" t="inlineStr">
         <is>
           <t>spedizione.codici_servizi</t>
         </is>
       </c>
-      <c r="H65" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I65" s="56" t="n">
+      <c r="H65" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I65" s="60" t="n">
         <v>255</v>
       </c>
-      <c r="J65" s="57" t="inlineStr">
+      <c r="J65" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
       </c>
       <c r="K65" s="17" t="inlineStr">
         <is>
-          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, W, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
-        </is>
-      </c>
-      <c r="L65" s="56" t="inlineStr">
+          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, W -&gt; APT000908 (matrice di test SDA, da confermare), Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
+        </is>
+      </c>
+      <c r="L65" s="60" t="inlineStr">
         <is>
           <t>DF-05, DF-07, DF-21, DF-22</t>
         </is>
@@ -21391,7 +21403,7 @@
           <t xml:space="preserve">[era su spedizione.codici_servizi] c'è la sezione dedicata contrasegno nel tracciato unico, come punto aperto il codice accesorio che dobbiamo inserire </t>
         </is>
       </c>
-      <c r="B66" s="56" t="inlineStr">
+      <c r="B66" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService</t>
         </is>
@@ -21401,31 +21413,31 @@
           <t>IT: (Oggetto) Contrassegno: presente se la spedizione è in contrassegno.</t>
         </is>
       </c>
-      <c r="D66" s="56" t="inlineStr">
+      <c r="D66" s="60" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E66" s="56" t="inlineStr"/>
-      <c r="F66" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G66" s="56" t="inlineStr">
+      <c r="E66" s="60" t="inlineStr"/>
+      <c r="F66" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G66" s="60" t="inlineStr">
         <is>
           <t>spedizione.contrassegno.flag</t>
         </is>
       </c>
-      <c r="H66" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I66" s="56" t="n">
+      <c r="H66" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I66" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="J66" s="57" t="inlineStr">
+      <c r="J66" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -21435,11 +21447,11 @@
           <t>"S" se presente, altrimenti "N"</t>
         </is>
       </c>
-      <c r="L66" s="56" t="inlineStr"/>
+      <c r="L66" s="60" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n"/>
-      <c r="B67" s="56" t="inlineStr">
+      <c r="B67" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.iban</t>
         </is>
@@ -21450,27 +21462,27 @@
 IT: Obbligatorio se IdentifierForCODCollection = 3.</t>
         </is>
       </c>
-      <c r="D67" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E67" s="56" t="n">
+      <c r="D67" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E67" s="60" t="n">
         <v>34</v>
       </c>
-      <c r="F67" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G67" s="56" t="inlineStr">
+      <c r="F67" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G67" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H67" s="56" t="inlineStr"/>
-      <c r="I67" s="56" t="inlineStr"/>
-      <c r="J67" s="58" t="inlineStr">
+      <c r="H67" s="60" t="inlineStr"/>
+      <c r="I67" s="60" t="inlineStr"/>
+      <c r="J67" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21480,7 +21492,7 @@
           <t>ICD ha IBAN solo in cliente (da SFA)</t>
         </is>
       </c>
-      <c r="L67" s="56" t="inlineStr">
+      <c r="L67" s="60" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
@@ -21488,7 +21500,7 @@
     </row>
     <row r="68">
       <c r="A68" s="17" t="n"/>
-      <c r="B68" s="56" t="inlineStr">
+      <c r="B68" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.bic</t>
         </is>
@@ -21499,27 +21511,27 @@
 IT: Obbligatorio se IdentifierForCODCollection = 3.</t>
         </is>
       </c>
-      <c r="D68" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E68" s="56" t="n">
+      <c r="D68" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E68" s="60" t="n">
         <v>11</v>
       </c>
-      <c r="F68" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G68" s="56" t="inlineStr">
+      <c r="F68" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G68" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H68" s="56" t="inlineStr"/>
-      <c r="I68" s="56" t="inlineStr"/>
-      <c r="J68" s="58" t="inlineStr">
+      <c r="H68" s="60" t="inlineStr"/>
+      <c r="I68" s="60" t="inlineStr"/>
+      <c r="J68" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21529,7 +21541,7 @@
           <t>ICD ha IBAN solo in cliente (da SFA)</t>
         </is>
       </c>
-      <c r="L68" s="56" t="inlineStr">
+      <c r="L68" s="60" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
@@ -21537,7 +21549,7 @@
     </row>
     <row r="69">
       <c r="A69" s="17" t="n"/>
-      <c r="B69" s="56" t="inlineStr">
+      <c r="B69" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.accountHolder</t>
         </is>
@@ -21548,27 +21560,27 @@
 IT: Intestatario del conto.</t>
         </is>
       </c>
-      <c r="D69" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E69" s="56" t="n">
+      <c r="D69" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E69" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F69" s="56" t="inlineStr">
+      <c r="F69" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G69" s="56" t="inlineStr">
+      <c r="G69" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H69" s="56" t="inlineStr"/>
-      <c r="I69" s="56" t="inlineStr"/>
-      <c r="J69" s="58" t="inlineStr">
+      <c r="H69" s="60" t="inlineStr"/>
+      <c r="I69" s="60" t="inlineStr"/>
+      <c r="J69" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21578,7 +21590,7 @@
           <t>ICD ha IBAN solo in cliente (da SFA)</t>
         </is>
       </c>
-      <c r="L69" s="56" t="inlineStr">
+      <c r="L69" s="60" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
@@ -21586,7 +21598,7 @@
     </row>
     <row r="70">
       <c r="A70" s="17" t="n"/>
-      <c r="B70" s="56" t="inlineStr">
+      <c r="B70" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.paymentReason</t>
         </is>
@@ -21597,27 +21609,27 @@
 IT: Attualmente, per il contrassegno fra Post AT e TOF-DE, si usano solo 13 cifre (numero spedizione EURODIS).</t>
         </is>
       </c>
-      <c r="D70" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E70" s="56" t="n">
+      <c r="D70" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E70" s="60" t="n">
         <v>140</v>
       </c>
-      <c r="F70" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G70" s="56" t="inlineStr">
+      <c r="F70" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G70" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H70" s="56" t="inlineStr"/>
-      <c r="I70" s="56" t="inlineStr"/>
-      <c r="J70" s="58" t="inlineStr">
+      <c r="H70" s="60" t="inlineStr"/>
+      <c r="I70" s="60" t="inlineStr"/>
+      <c r="J70" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21627,7 +21639,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L70" s="56" t="inlineStr">
+      <c r="L70" s="60" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
@@ -21635,7 +21647,7 @@
     </row>
     <row r="71">
       <c r="A71" s="17" t="n"/>
-      <c r="B71" s="56" t="inlineStr">
+      <c r="B71" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.paymentReference</t>
         </is>
@@ -21646,27 +21658,27 @@
 IT: Attualmente, per il contrassegno fra Post AT e TOF-DE, si usano solo 12 cifre (numero spedizione EURODIS).</t>
         </is>
       </c>
-      <c r="D71" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E71" s="56" t="n">
+      <c r="D71" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E71" s="60" t="n">
         <v>35</v>
       </c>
-      <c r="F71" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G71" s="56" t="inlineStr">
+      <c r="F71" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G71" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H71" s="56" t="inlineStr"/>
-      <c r="I71" s="56" t="inlineStr"/>
-      <c r="J71" s="58" t="inlineStr">
+      <c r="H71" s="60" t="inlineStr"/>
+      <c r="I71" s="60" t="inlineStr"/>
+      <c r="J71" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21676,7 +21688,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L71" s="56" t="inlineStr">
+      <c r="L71" s="60" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
@@ -21684,7 +21696,7 @@
     </row>
     <row r="72">
       <c r="A72" s="17" t="n"/>
-      <c r="B72" s="56" t="inlineStr">
+      <c r="B72" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.amount</t>
         </is>
@@ -21695,31 +21707,31 @@
 IT: Importo nella valuta indicata, con due decimali.</t>
         </is>
       </c>
-      <c r="D72" s="56" t="inlineStr">
+      <c r="D72" s="60" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E72" s="56" t="inlineStr"/>
-      <c r="F72" s="56" t="inlineStr">
+      <c r="E72" s="60" t="inlineStr"/>
+      <c r="F72" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G72" s="56" t="inlineStr">
+      <c r="G72" s="60" t="inlineStr">
         <is>
           <t>spedizione.contrassegno.importo_contrassegno</t>
         </is>
       </c>
-      <c r="H72" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I72" s="56" t="n">
+      <c r="H72" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I72" s="60" t="n">
         <v>9</v>
       </c>
-      <c r="J72" s="59" t="inlineStr">
+      <c r="J72" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -21729,7 +21741,7 @@
           <t>2 decimali, maggiore di 0, max 999999.99 (CSV accessori). Se currency &lt;&gt; EUR: scarto? (proposta 29-Oct)</t>
         </is>
       </c>
-      <c r="L72" s="56" t="inlineStr">
+      <c r="L72" s="60" t="inlineStr">
         <is>
           <t>DF-24</t>
         </is>
@@ -21737,7 +21749,7 @@
     </row>
     <row r="73">
       <c r="A73" s="17" t="n"/>
-      <c r="B73" s="56" t="inlineStr">
+      <c r="B73" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.currency</t>
         </is>
@@ -21748,27 +21760,27 @@
 IT: EUR o altro codice valuta ISO.</t>
         </is>
       </c>
-      <c r="D73" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E73" s="56" t="n">
+      <c r="D73" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E73" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F73" s="56" t="inlineStr">
+      <c r="F73" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G73" s="56" t="inlineStr">
+      <c r="G73" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H73" s="56" t="inlineStr"/>
-      <c r="I73" s="56" t="inlineStr"/>
-      <c r="J73" s="58" t="inlineStr">
+      <c r="H73" s="60" t="inlineStr"/>
+      <c r="I73" s="60" t="inlineStr"/>
+      <c r="J73" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -21778,7 +21790,7 @@
           <t>ICD non ha valuta del contrassegno</t>
         </is>
       </c>
-      <c r="L73" s="56" t="inlineStr">
+      <c r="L73" s="60" t="inlineStr">
         <is>
           <t>PA-19</t>
         </is>
@@ -21786,7 +21798,7 @@
     </row>
     <row r="74">
       <c r="A74" s="17" t="n"/>
-      <c r="B74" s="56" t="inlineStr">
+      <c r="B74" s="60" t="inlineStr">
         <is>
           <t>cashOnDeliveryService.identifierForCODCollection</t>
         </is>
@@ -21797,31 +21809,31 @@
 IT: Contrassegno incassato in contanti o con assegno; i contanti sono lo standard per Post AT e la maggior parte dei partner. Deve essere 3 (contanti) o 5 (assegno).</t>
         </is>
       </c>
-      <c r="D74" s="56" t="inlineStr">
+      <c r="D74" s="60" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E74" s="56" t="inlineStr"/>
-      <c r="F74" s="56" t="inlineStr">
+      <c r="E74" s="60" t="inlineStr"/>
+      <c r="F74" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G74" s="56" t="inlineStr">
+      <c r="G74" s="60" t="inlineStr">
         <is>
           <t>spedizione.contrassegno.tipo_pagamento_contrassegno</t>
         </is>
       </c>
-      <c r="H74" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I74" s="56" t="n">
+      <c r="H74" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I74" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="J74" s="57" t="inlineStr">
+      <c r="J74" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -21831,7 +21843,7 @@
           <t>3 -&gt; CON, 5 -&gt; ABM (riscontro SDA, da confermare; mai ACM). Non ammesso con Punto Poste (proposta 29-Oct)</t>
         </is>
       </c>
-      <c r="L74" s="56" t="inlineStr">
+      <c r="L74" s="60" t="inlineStr">
         <is>
           <t>DF-24</t>
         </is>
@@ -21839,7 +21851,7 @@
     </row>
     <row r="75">
       <c r="A75" s="17" t="n"/>
-      <c r="B75" s="56" t="inlineStr">
+      <c r="B75" s="60" t="inlineStr">
         <is>
           <t>customsService</t>
         </is>
@@ -21849,31 +21861,31 @@
           <t>IT: (Oggetto) Dati doganali.</t>
         </is>
       </c>
-      <c r="D75" s="56" t="inlineStr">
+      <c r="D75" s="60" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E75" s="56" t="inlineStr"/>
-      <c r="F75" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G75" s="56" t="inlineStr">
+      <c r="E75" s="60" t="inlineStr"/>
+      <c r="F75" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" s="60" t="inlineStr">
         <is>
           <t>spedizione.importi.status_doganale</t>
         </is>
       </c>
-      <c r="H75" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I75" s="56" t="n">
+      <c r="H75" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I75" s="60" t="n">
         <v>50</v>
       </c>
-      <c r="J75" s="58" t="inlineStr">
+      <c r="J75" s="62" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -21883,7 +21895,7 @@
           <t>Spedizioni extra-UE: perimetro?</t>
         </is>
       </c>
-      <c r="L75" s="56" t="inlineStr">
+      <c r="L75" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -21895,7 +21907,7 @@
           <t>c'è anche la sezione assicurata</t>
         </is>
       </c>
-      <c r="B76" s="56" t="inlineStr">
+      <c r="B76" s="60" t="inlineStr">
         <is>
           <t>customsService.commercialValueOfGoods</t>
         </is>
@@ -21906,31 +21918,31 @@
 IT: Per motivi assicurativi; obbligatorio se non si tratta di documenti.</t>
         </is>
       </c>
-      <c r="D76" s="56" t="inlineStr">
+      <c r="D76" s="60" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E76" s="56" t="inlineStr"/>
-      <c r="F76" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G76" s="56" t="inlineStr">
+      <c r="E76" s="60" t="inlineStr"/>
+      <c r="F76" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G76" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.articolo.valore</t>
         </is>
       </c>
-      <c r="H76" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I76" s="56" t="n">
+      <c r="H76" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I76" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="J76" s="57" t="inlineStr">
+      <c r="J76" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -21940,7 +21952,7 @@
           <t>x100 (centesimi)</t>
         </is>
       </c>
-      <c r="L76" s="56" t="inlineStr">
+      <c r="L76" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -21948,7 +21960,7 @@
     </row>
     <row r="77">
       <c r="A77" s="17" t="n"/>
-      <c r="B77" s="56" t="inlineStr">
+      <c r="B77" s="60" t="inlineStr">
         <is>
           <t>customsService.commercialValueOfGoods</t>
         </is>
@@ -21959,31 +21971,31 @@
 IT: Per motivi assicurativi; obbligatorio se non si tratta di documenti.</t>
         </is>
       </c>
-      <c r="D77" s="56" t="inlineStr">
+      <c r="D77" s="60" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E77" s="56" t="inlineStr"/>
-      <c r="F77" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G77" s="56" t="inlineStr">
+      <c r="E77" s="60" t="inlineStr"/>
+      <c r="F77" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" s="60" t="inlineStr">
         <is>
           <t>spedizione.internazionale.valore_spedizione</t>
         </is>
       </c>
-      <c r="H77" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I77" s="56" t="n">
+      <c r="H77" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I77" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="J77" s="59" t="inlineStr">
+      <c r="J77" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -21993,7 +22005,7 @@
           <t>In euro</t>
         </is>
       </c>
-      <c r="L77" s="56" t="inlineStr">
+      <c r="L77" s="60" t="inlineStr">
         <is>
           <t>PA-22</t>
         </is>
@@ -22001,7 +22013,7 @@
     </row>
     <row r="78">
       <c r="A78" s="17" t="n"/>
-      <c r="B78" s="56" t="inlineStr">
+      <c r="B78" s="60" t="inlineStr">
         <is>
           <t>customsService.commercialValueOfGoods</t>
         </is>
@@ -22012,31 +22024,31 @@
 IT: Per motivi assicurativi; obbligatorio se non si tratta di documenti.</t>
         </is>
       </c>
-      <c r="D78" s="56" t="inlineStr">
+      <c r="D78" s="60" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E78" s="56" t="inlineStr"/>
-      <c r="F78" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G78" s="56" t="inlineStr">
+      <c r="E78" s="60" t="inlineStr"/>
+      <c r="F78" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" s="60" t="inlineStr">
         <is>
           <t>spedizione.valore</t>
         </is>
       </c>
-      <c r="H78" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I78" s="56" t="n">
+      <c r="H78" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I78" s="60" t="n">
         <v>12</v>
       </c>
-      <c r="J78" s="57" t="inlineStr">
+      <c r="J78" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22046,7 +22058,7 @@
           <t>x100 (centesimi), solo se currency = EUR</t>
         </is>
       </c>
-      <c r="L78" s="56" t="inlineStr">
+      <c r="L78" s="60" t="inlineStr">
         <is>
           <t>PA-22</t>
         </is>
@@ -22054,7 +22066,7 @@
     </row>
     <row r="79">
       <c r="A79" s="17" t="n"/>
-      <c r="B79" s="56" t="inlineStr">
+      <c r="B79" s="60" t="inlineStr">
         <is>
           <t>customsService.currency</t>
         </is>
@@ -22065,39 +22077,39 @@
 IT: Codice valuta se il valore commerciale è valorizzato (EUR o altro codice ISO).</t>
         </is>
       </c>
-      <c r="D79" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E79" s="56" t="n">
+      <c r="D79" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E79" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F79" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G79" s="56" t="inlineStr">
+      <c r="F79" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G79" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.articolo.valuta</t>
         </is>
       </c>
-      <c r="H79" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I79" s="56" t="n">
+      <c r="H79" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I79" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="J79" s="59" t="inlineStr">
+      <c r="J79" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
       <c r="K79" s="17" t="inlineStr"/>
-      <c r="L79" s="56" t="inlineStr">
+      <c r="L79" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22105,7 +22117,7 @@
     </row>
     <row r="80">
       <c r="A80" s="17" t="n"/>
-      <c r="B80" s="56" t="inlineStr">
+      <c r="B80" s="60" t="inlineStr">
         <is>
           <t>customsService.currency</t>
         </is>
@@ -22116,43 +22128,43 @@
 IT: Codice valuta se il valore commerciale è valorizzato (EUR o altro codice ISO).</t>
         </is>
       </c>
-      <c r="D80" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E80" s="56" t="n">
+      <c r="D80" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E80" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F80" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G80" s="56" t="inlineStr">
+      <c r="F80" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" s="60" t="inlineStr">
         <is>
           <t>spedizione.internazionale.valuta</t>
         </is>
       </c>
-      <c r="H80" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I80" s="56" t="n">
+      <c r="H80" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I80" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="J80" s="59" t="inlineStr">
+      <c r="J80" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
       <c r="K80" s="17" t="inlineStr"/>
-      <c r="L80" s="56" t="inlineStr"/>
+      <c r="L80" s="60" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="17" t="n"/>
-      <c r="B81" s="56" t="inlineStr">
+      <c r="B81" s="60" t="inlineStr">
         <is>
           <t>customsService.dutyCode</t>
         </is>
@@ -22163,33 +22175,33 @@
 IT: Obbligatorio per extra-UE (= codice della tariffa doganale).</t>
         </is>
       </c>
-      <c r="D81" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E81" s="56" t="n">
+      <c r="D81" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E81" s="60" t="n">
         <v>12</v>
       </c>
-      <c r="F81" s="56" t="inlineStr">
+      <c r="F81" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G81" s="56" t="inlineStr">
+      <c r="G81" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.articolo.codice_taric</t>
         </is>
       </c>
-      <c r="H81" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I81" s="56" t="n">
+      <c r="H81" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I81" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="J81" s="57" t="inlineStr">
+      <c r="J81" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22199,7 +22211,7 @@
           <t>Un solo articolo per spedizione; valore integrale (sorgente 12, ICD 10)</t>
         </is>
       </c>
-      <c r="L81" s="56" t="inlineStr">
+      <c r="L81" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22207,7 +22219,7 @@
     </row>
     <row r="82">
       <c r="A82" s="17" t="n"/>
-      <c r="B82" s="56" t="inlineStr">
+      <c r="B82" s="60" t="inlineStr">
         <is>
           <t>customsService.sign</t>
         </is>
@@ -22218,27 +22230,27 @@
 IT: Descrizione aggiuntiva facoltativa della spedizione (numero di identificazione/riferimento).</t>
         </is>
       </c>
-      <c r="D82" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E82" s="56" t="n">
+      <c r="D82" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E82" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="F82" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G82" s="56" t="inlineStr">
+      <c r="F82" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G82" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H82" s="56" t="inlineStr"/>
-      <c r="I82" s="56" t="inlineStr"/>
-      <c r="J82" s="58" t="inlineStr">
+      <c r="H82" s="60" t="inlineStr"/>
+      <c r="I82" s="60" t="inlineStr"/>
+      <c r="J82" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22248,7 +22260,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L82" s="56" t="inlineStr">
+      <c r="L82" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22256,7 +22268,7 @@
     </row>
     <row r="83">
       <c r="A83" s="17" t="n"/>
-      <c r="B83" s="56" t="inlineStr">
+      <c r="B83" s="60" t="inlineStr">
         <is>
           <t>customsService.number</t>
         </is>
@@ -22267,25 +22279,25 @@
 IT: Descrizione aggiuntiva facoltativa della spedizione (numero di identificazione/riferimento).</t>
         </is>
       </c>
-      <c r="D83" s="56" t="inlineStr">
+      <c r="D83" s="60" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E83" s="56" t="inlineStr"/>
-      <c r="F83" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G83" s="56" t="inlineStr">
+      <c r="E83" s="60" t="inlineStr"/>
+      <c r="F83" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G83" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H83" s="56" t="inlineStr"/>
-      <c r="I83" s="56" t="inlineStr"/>
-      <c r="J83" s="58" t="inlineStr">
+      <c r="H83" s="60" t="inlineStr"/>
+      <c r="I83" s="60" t="inlineStr"/>
+      <c r="J83" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22295,7 +22307,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L83" s="56" t="inlineStr">
+      <c r="L83" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22303,7 +22315,7 @@
     </row>
     <row r="84">
       <c r="A84" s="17" t="n"/>
-      <c r="B84" s="56" t="inlineStr">
+      <c r="B84" s="60" t="inlineStr">
         <is>
           <t>customsService.descriptionOfGoods</t>
         </is>
@@ -22314,39 +22326,39 @@
 IT: Informazione facoltativa sui camion di trasporto, es. per la Svizzera. NB: la descrizione dello swagger non corrisponde al nome del campo ("descrizione merce"), da chiarire con EURODIS.</t>
         </is>
       </c>
-      <c r="D84" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E84" s="56" t="n">
+      <c r="D84" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E84" s="60" t="n">
         <v>20</v>
       </c>
-      <c r="F84" s="56" t="inlineStr">
+      <c r="F84" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G84" s="56" t="inlineStr">
+      <c r="G84" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.articolo.english_descr</t>
         </is>
       </c>
-      <c r="H84" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I84" s="56" t="n">
+      <c r="H84" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I84" s="60" t="n">
         <v>250</v>
       </c>
-      <c r="J84" s="59" t="inlineStr">
+      <c r="J84" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
       <c r="K84" s="17" t="inlineStr"/>
-      <c r="L84" s="56" t="inlineStr">
+      <c r="L84" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22354,7 +22366,7 @@
     </row>
     <row r="85">
       <c r="A85" s="17" t="n"/>
-      <c r="B85" s="56" t="inlineStr">
+      <c r="B85" s="60" t="inlineStr">
         <is>
           <t>customsService.descriptionOfGoods</t>
         </is>
@@ -22365,33 +22377,33 @@
 IT: Informazione facoltativa sui camion di trasporto, es. per la Svizzera. NB: la descrizione dello swagger non corrisponde al nome del campo ("descrizione merce"), da chiarire con EURODIS.</t>
         </is>
       </c>
-      <c r="D85" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E85" s="56" t="n">
+      <c r="D85" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E85" s="60" t="n">
         <v>20</v>
       </c>
-      <c r="F85" s="56" t="inlineStr">
+      <c r="F85" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G85" s="56" t="inlineStr">
+      <c r="G85" s="60" t="inlineStr">
         <is>
           <t>spedizione.descrizione_contenuto</t>
         </is>
       </c>
-      <c r="H85" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I85" s="56" t="n">
+      <c r="H85" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I85" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="J85" s="59" t="inlineStr">
+      <c r="J85" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -22401,11 +22413,11 @@
           <t>Solo se presente customsService (20 &lt;= 30)</t>
         </is>
       </c>
-      <c r="L85" s="56" t="inlineStr"/>
+      <c r="L85" s="60" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="17" t="n"/>
-      <c r="B86" s="56" t="inlineStr">
+      <c r="B86" s="60" t="inlineStr">
         <is>
           <t>customsService.descriptionOfGoods</t>
         </is>
@@ -22416,43 +22428,43 @@
 IT: Informazione facoltativa sui camion di trasporto, es. per la Svizzera. NB: la descrizione dello swagger non corrisponde al nome del campo ("descrizione merce"), da chiarire con EURODIS.</t>
         </is>
       </c>
-      <c r="D86" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E86" s="56" t="n">
+      <c r="D86" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E86" s="60" t="n">
         <v>20</v>
       </c>
-      <c r="F86" s="56" t="inlineStr">
+      <c r="F86" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G86" s="56" t="inlineStr">
+      <c r="G86" s="60" t="inlineStr">
         <is>
           <t>spedizione.internazionale.descrizione</t>
         </is>
       </c>
-      <c r="H86" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I86" s="56" t="n">
+      <c r="H86" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I86" s="60" t="n">
         <v>255</v>
       </c>
-      <c r="J86" s="59" t="inlineStr">
+      <c r="J86" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
       </c>
       <c r="K86" s="17" t="inlineStr"/>
-      <c r="L86" s="56" t="inlineStr"/>
+      <c r="L86" s="60" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n"/>
-      <c r="B87" s="56" t="inlineStr">
+      <c r="B87" s="60" t="inlineStr">
         <is>
           <t>hazardousADRServices[]</t>
         </is>
@@ -22462,25 +22474,25 @@
           <t>IT: (Array) Dati delle merci pericolose ADR: classe di pericolo, numero ONU, gruppo di imballaggio, peso lordo ADR, codice galleria, categoria di trasporto, denominazione.</t>
         </is>
       </c>
-      <c r="D87" s="56" t="inlineStr">
+      <c r="D87" s="60" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E87" s="56" t="inlineStr"/>
-      <c r="F87" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G87" s="56" t="inlineStr">
+      <c r="E87" s="60" t="inlineStr"/>
+      <c r="F87" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G87" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H87" s="56" t="inlineStr"/>
-      <c r="I87" s="56" t="inlineStr"/>
-      <c r="J87" s="58" t="inlineStr">
+      <c r="H87" s="60" t="inlineStr"/>
+      <c r="I87" s="60" t="inlineStr"/>
+      <c r="J87" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22490,7 +22502,7 @@
           <t>Nessun oggetto ICD</t>
         </is>
       </c>
-      <c r="L87" s="56" t="inlineStr">
+      <c r="L87" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22498,7 +22510,7 @@
     </row>
     <row r="88">
       <c r="A88" s="17" t="n"/>
-      <c r="B88" s="56" t="inlineStr">
+      <c r="B88" s="60" t="inlineStr">
         <is>
           <t>hazardousCollis[]</t>
         </is>
@@ -22508,25 +22520,25 @@
           <t>IT: (Array) Colli ADR: numero di colli per tipo e descrizione ADR del tipo di collo.</t>
         </is>
       </c>
-      <c r="D88" s="56" t="inlineStr">
+      <c r="D88" s="60" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E88" s="56" t="inlineStr"/>
-      <c r="F88" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G88" s="56" t="inlineStr">
+      <c r="E88" s="60" t="inlineStr"/>
+      <c r="F88" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G88" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H88" s="56" t="inlineStr"/>
-      <c r="I88" s="56" t="inlineStr"/>
-      <c r="J88" s="58" t="inlineStr">
+      <c r="H88" s="60" t="inlineStr"/>
+      <c r="I88" s="60" t="inlineStr"/>
+      <c r="J88" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22536,7 +22548,7 @@
           <t>Nessun oggetto ICD</t>
         </is>
       </c>
-      <c r="L88" s="56" t="inlineStr">
+      <c r="L88" s="60" t="inlineStr">
         <is>
           <t>PA-13</t>
         </is>
@@ -22548,7 +22560,7 @@
           <t xml:space="preserve">traccia tra i punti aperti  che lo abbiamo mappato cosi </t>
         </is>
       </c>
-      <c r="B89" s="56" t="inlineStr">
+      <c r="B89" s="60" t="inlineStr">
         <is>
           <t>consigneePreAdvice.smsPreAdvice</t>
         </is>
@@ -22559,29 +22571,29 @@
 IT: Se vero, ContactSMS in ConsigneeAddress deve essere valorizzato.</t>
         </is>
       </c>
-      <c r="D89" s="56" t="inlineStr">
+      <c r="D89" s="60" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E89" s="56" t="inlineStr"/>
-      <c r="F89" s="56" t="inlineStr">
+      <c r="E89" s="60" t="inlineStr"/>
+      <c r="F89" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G89" s="56" t="inlineStr">
+      <c r="G89" s="60" t="inlineStr">
         <is>
           <t>spedizione.notifiche_sms</t>
         </is>
       </c>
-      <c r="H89" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I89" s="56" t="n"/>
-      <c r="J89" s="58" t="inlineStr">
+      <c r="H89" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I89" s="60" t="n"/>
+      <c r="J89" s="62" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -22591,7 +22603,7 @@
           <t>SDA notifica da sola se ci sono i contatti e non usa RT_65 (riscontro SDA): valutare se non mapparlo (proposta 29-Oct)</t>
         </is>
       </c>
-      <c r="L89" s="56" t="inlineStr">
+      <c r="L89" s="60" t="inlineStr">
         <is>
           <t>DF-09</t>
         </is>
@@ -22603,7 +22615,7 @@
           <t xml:space="preserve">traccia tra i punti aperti  che lo abbiamo mappato cosi </t>
         </is>
       </c>
-      <c r="B90" s="56" t="inlineStr">
+      <c r="B90" s="60" t="inlineStr">
         <is>
           <t>consigneePreAdvice.eMailPreAdvice</t>
         </is>
@@ -22614,29 +22626,29 @@
 IT: Se vero, ContactEMail in ConsigneeAddress deve essere valorizzato.</t>
         </is>
       </c>
-      <c r="D90" s="56" t="inlineStr">
+      <c r="D90" s="60" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E90" s="56" t="inlineStr"/>
-      <c r="F90" s="56" t="inlineStr">
+      <c r="E90" s="60" t="inlineStr"/>
+      <c r="F90" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G90" s="56" t="inlineStr">
+      <c r="G90" s="60" t="inlineStr">
         <is>
           <t>spedizione.notifiche_email</t>
         </is>
       </c>
-      <c r="H90" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I90" s="56" t="n"/>
-      <c r="J90" s="58" t="inlineStr">
+      <c r="H90" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I90" s="60" t="n"/>
+      <c r="J90" s="62" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -22646,7 +22658,7 @@
           <t>SDA notifica da sola se ci sono i contatti e non usa RT_65 (riscontro SDA): valutare se non mapparlo (proposta 29-Oct)</t>
         </is>
       </c>
-      <c r="L90" s="56" t="inlineStr">
+      <c r="L90" s="60" t="inlineStr">
         <is>
           <t>DF-09</t>
         </is>
@@ -22654,7 +22666,7 @@
     </row>
     <row r="91">
       <c r="A91" s="17" t="n"/>
-      <c r="B91" s="56" t="inlineStr">
+      <c r="B91" s="60" t="inlineStr">
         <is>
           <t>consigneePreAdvice.telephonePreAdvice</t>
         </is>
@@ -22665,25 +22677,25 @@
 IT: Se vero, ContactTelephone in ConsigneeAddress deve essere valorizzato.</t>
         </is>
       </c>
-      <c r="D91" s="56" t="inlineStr">
+      <c r="D91" s="60" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E91" s="56" t="inlineStr"/>
-      <c r="F91" s="56" t="inlineStr">
+      <c r="E91" s="60" t="inlineStr"/>
+      <c r="F91" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G91" s="56" t="inlineStr">
+      <c r="G91" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H91" s="56" t="inlineStr"/>
-      <c r="I91" s="56" t="inlineStr"/>
-      <c r="J91" s="58" t="inlineStr">
+      <c r="H91" s="60" t="inlineStr"/>
+      <c r="I91" s="60" t="inlineStr"/>
+      <c r="J91" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -22693,7 +22705,7 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L91" s="56" t="inlineStr">
+      <c r="L91" s="60" t="inlineStr">
         <is>
           <t>PA-18</t>
         </is>
@@ -22701,7 +22713,7 @@
     </row>
     <row r="92">
       <c r="A92" s="17" t="n"/>
-      <c r="B92" s="56" t="inlineStr">
+      <c r="B92" s="60" t="inlineStr">
         <is>
           <t>collis[]</t>
         </is>
@@ -22711,31 +22723,31 @@
           <t>IT: (Array) Dati dei colli: un elemento per collo o pallet.</t>
         </is>
       </c>
-      <c r="D92" s="56" t="inlineStr">
+      <c r="D92" s="60" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E92" s="56" t="inlineStr"/>
-      <c r="F92" s="56" t="inlineStr">
+      <c r="E92" s="60" t="inlineStr"/>
+      <c r="F92" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G92" s="56" t="inlineStr">
+      <c r="G92" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.numero_colli_parz</t>
         </is>
       </c>
-      <c r="H92" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I92" s="56" t="n">
+      <c r="H92" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I92" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J92" s="57" t="inlineStr">
+      <c r="J92" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22745,11 +22757,11 @@
           <t>Progressivo collo</t>
         </is>
       </c>
-      <c r="L92" s="56" t="inlineStr"/>
+      <c r="L92" s="60" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="17" t="n"/>
-      <c r="B93" s="56" t="inlineStr">
+      <c r="B93" s="60" t="inlineStr">
         <is>
           <t>collis[]</t>
         </is>
@@ -22759,31 +22771,31 @@
           <t>IT: (Array) Dati dei colli: un elemento per collo o pallet.</t>
         </is>
       </c>
-      <c r="D93" s="56" t="inlineStr">
+      <c r="D93" s="60" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E93" s="56" t="inlineStr"/>
-      <c r="F93" s="56" t="inlineStr">
+      <c r="E93" s="60" t="inlineStr"/>
+      <c r="F93" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G93" s="56" t="inlineStr">
+      <c r="G93" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.tipo_collo</t>
         </is>
       </c>
-      <c r="H93" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I93" s="56" t="n">
+      <c r="H93" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I93" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="J93" s="57" t="inlineStr">
+      <c r="J93" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22793,7 +22805,7 @@
           <t>Solo multicollo: madre/figlio</t>
         </is>
       </c>
-      <c r="L93" s="56" t="inlineStr">
+      <c r="L93" s="60" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -22801,7 +22813,7 @@
     </row>
     <row r="94">
       <c r="A94" s="17" t="n"/>
-      <c r="B94" s="56" t="inlineStr">
+      <c r="B94" s="60" t="inlineStr">
         <is>
           <t>collis[].identifierPalletOrCollo</t>
         </is>
@@ -22812,33 +22824,33 @@
 IT: "P" (pallet), "C" (collo), "P+" (pallet+) o "C+" (collo+).</t>
         </is>
       </c>
-      <c r="D94" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E94" s="56" t="n">
+      <c r="D94" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E94" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F94" s="56" t="inlineStr">
+      <c r="F94" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G94" s="56" t="inlineStr">
+      <c r="G94" s="60" t="inlineStr">
         <is>
           <t>spedizione.codice_tipo_spedizione</t>
         </is>
       </c>
-      <c r="H94" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I94" s="56" t="n">
+      <c r="H94" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I94" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="J94" s="58" t="inlineStr">
+      <c r="J94" s="62" t="inlineStr">
         <is>
           <t>DA DEFINIRE</t>
         </is>
@@ -22848,11 +22860,11 @@
           <t>Valori ICD "P","C": verificare il significato</t>
         </is>
       </c>
-      <c r="L94" s="56" t="inlineStr"/>
+      <c r="L94" s="60" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="17" t="n"/>
-      <c r="B95" s="56" t="inlineStr">
+      <c r="B95" s="60" t="inlineStr">
         <is>
           <t>collis[].identifierPalletOrCollo</t>
         </is>
@@ -22863,33 +22875,33 @@
 IT: "P" (pallet), "C" (collo), "P+" (pallet+) o "C+" (collo+).</t>
         </is>
       </c>
-      <c r="D95" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E95" s="56" t="n">
+      <c r="D95" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E95" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F95" s="56" t="inlineStr">
+      <c r="F95" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G95" s="56" t="inlineStr">
+      <c r="G95" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.codice_imballo</t>
         </is>
       </c>
-      <c r="H95" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I95" s="56" t="n">
+      <c r="H95" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I95" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="J95" s="57" t="inlineStr">
+      <c r="J95" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22899,11 +22911,11 @@
           <t>Proposta: P/P+ -&gt; "PL", C/C+ -&gt; "CL"</t>
         </is>
       </c>
-      <c r="L95" s="56" t="inlineStr"/>
+      <c r="L95" s="60" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="17" t="n"/>
-      <c r="B96" s="56" t="inlineStr">
+      <c r="B96" s="60" t="inlineStr">
         <is>
           <t>collis[].weightOfUnit</t>
         </is>
@@ -22914,31 +22926,31 @@
 IT: In chilogrammi.</t>
         </is>
       </c>
-      <c r="D96" s="56" t="inlineStr">
+      <c r="D96" s="60" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E96" s="56" t="inlineStr"/>
-      <c r="F96" s="56" t="inlineStr">
+      <c r="E96" s="60" t="inlineStr"/>
+      <c r="F96" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G96" s="56" t="inlineStr">
+      <c r="G96" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.peso</t>
         </is>
       </c>
-      <c r="H96" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I96" s="56" t="n">
+      <c r="H96" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I96" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="J96" s="57" t="inlineStr">
+      <c r="J96" s="61" t="inlineStr">
         <is>
           <t>TRASFORMATO</t>
         </is>
@@ -22948,11 +22960,11 @@
           <t>kg -&gt; grammi (x1000): peso 2000 nell'esempio EUD_INVIOFILE</t>
         </is>
       </c>
-      <c r="L96" s="56" t="inlineStr"/>
+      <c r="L96" s="60" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n"/>
-      <c r="B97" s="56" t="inlineStr">
+      <c r="B97" s="60" t="inlineStr">
         <is>
           <t>collis[].europlateBarcode</t>
         </is>
@@ -22963,33 +22975,33 @@
 IT: Barcode EURODIS del collo; valore di default (0) in caso di neighbourhood business.</t>
         </is>
       </c>
-      <c r="D97" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E97" s="56" t="n">
+      <c r="D97" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E97" s="60" t="n">
         <v>24</v>
       </c>
-      <c r="F97" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G97" s="56" t="inlineStr">
+      <c r="F97" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G97" s="60" t="inlineStr">
         <is>
           <t>spedizione.internazionale.id_ldv_itz</t>
         </is>
       </c>
-      <c r="H97" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I97" s="56" t="n">
+      <c r="H97" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I97" s="60" t="n">
         <v>50</v>
       </c>
-      <c r="J97" s="59" t="inlineStr">
+      <c r="J97" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -22999,7 +23011,7 @@
           <t>Decisione 22-Oct. ICD: "previsto per i casi ERS e Eurodis". Campo a livello spedizione, barcode a livello collo: con piu' colli quale si usa?</t>
         </is>
       </c>
-      <c r="L97" s="56" t="inlineStr">
+      <c r="L97" s="60" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -23011,7 +23023,7 @@
           <t>[era su —] dovrebbe essere id_ldv_associata</t>
         </is>
       </c>
-      <c r="B98" s="56" t="inlineStr">
+      <c r="B98" s="60" t="inlineStr">
         <is>
           <t>collis[].referencedEuroplateBarcode</t>
         </is>
@@ -23022,33 +23034,33 @@
 IT: Valorizzato solo se il collo fa parte di un reso: riporta il barcode EURODIS del collo originario.</t>
         </is>
       </c>
-      <c r="D98" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E98" s="56" t="n">
+      <c r="D98" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E98" s="60" t="n">
         <v>24</v>
       </c>
-      <c r="F98" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G98" s="56" t="inlineStr">
+      <c r="F98" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G98" s="60" t="inlineStr">
         <is>
           <t>spedizione.id_ldv_associata</t>
         </is>
       </c>
-      <c r="H98" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I98" s="56" t="n">
+      <c r="H98" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I98" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="J98" s="59" t="inlineStr">
+      <c r="J98" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23058,7 +23070,7 @@
           <t>Solo resi. ICD: campo di spedizione di 3 caratteri, il barcode e' per collo e di 24 (commento Diego 23-Oct)</t>
         </is>
       </c>
-      <c r="L98" s="56" t="inlineStr">
+      <c r="L98" s="60" t="inlineStr">
         <is>
           <t>DF-10</t>
         </is>
@@ -23066,7 +23078,7 @@
     </row>
     <row r="99">
       <c r="A99" s="17" t="n"/>
-      <c r="B99" s="56" t="inlineStr">
+      <c r="B99" s="60" t="inlineStr">
         <is>
           <t>collis[].consignorsColloBarcode</t>
         </is>
@@ -23077,33 +23089,33 @@
 IT: Barcode domestico di reso del partner di consegna originario, generato/assegnato dalla soluzione resi EURODIS, oppure barcode del cliente o del partner mittente. Per il neighbourhood business va fornito il barcode domestico del partner secondo la SOP Neighbourhood business.</t>
         </is>
       </c>
-      <c r="D99" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E99" s="56" t="n">
+      <c r="D99" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E99" s="60" t="n">
         <v>50</v>
       </c>
-      <c r="F99" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G99" s="56" t="inlineStr">
+      <c r="F99" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G99" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.id_ldv</t>
         </is>
       </c>
-      <c r="H99" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I99" s="56" t="n">
+      <c r="H99" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I99" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="J99" s="59" t="inlineStr">
+      <c r="J99" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23113,7 +23125,7 @@
           <t>LDV del collo (decisione 22-Oct). Vuoto in EUD_INVIOFILE perche' li' la genera SDA</t>
         </is>
       </c>
-      <c r="L99" s="56" t="inlineStr">
+      <c r="L99" s="60" t="inlineStr">
         <is>
           <t>PA-11</t>
         </is>
@@ -23121,7 +23133,7 @@
     </row>
     <row r="100">
       <c r="A100" s="17" t="n"/>
-      <c r="B100" s="56" t="inlineStr">
+      <c r="B100" s="60" t="inlineStr">
         <is>
           <t>collis[].length</t>
         </is>
@@ -23132,31 +23144,31 @@
 IT: In centimetri.</t>
         </is>
       </c>
-      <c r="D100" s="56" t="inlineStr">
+      <c r="D100" s="60" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E100" s="56" t="inlineStr"/>
-      <c r="F100" s="56" t="inlineStr">
+      <c r="E100" s="60" t="inlineStr"/>
+      <c r="F100" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G100" s="56" t="inlineStr">
+      <c r="G100" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.lunghezza</t>
         </is>
       </c>
-      <c r="H100" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I100" s="56" t="n">
+      <c r="H100" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I100" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J100" s="59" t="inlineStr">
+      <c r="J100" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23166,11 +23178,11 @@
           <t>cm</t>
         </is>
       </c>
-      <c r="L100" s="56" t="inlineStr"/>
+      <c r="L100" s="60" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="17" t="n"/>
-      <c r="B101" s="56" t="inlineStr">
+      <c r="B101" s="60" t="inlineStr">
         <is>
           <t>collis[].width</t>
         </is>
@@ -23181,31 +23193,31 @@
 IT: In centimetri.</t>
         </is>
       </c>
-      <c r="D101" s="56" t="inlineStr">
+      <c r="D101" s="60" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E101" s="56" t="inlineStr"/>
-      <c r="F101" s="56" t="inlineStr">
+      <c r="E101" s="60" t="inlineStr"/>
+      <c r="F101" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G101" s="56" t="inlineStr">
+      <c r="G101" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.profondita</t>
         </is>
       </c>
-      <c r="H101" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I101" s="56" t="n">
+      <c r="H101" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I101" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J101" s="59" t="inlineStr">
+      <c r="J101" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23215,11 +23227,11 @@
           <t>cm</t>
         </is>
       </c>
-      <c r="L101" s="56" t="inlineStr"/>
+      <c r="L101" s="60" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="17" t="n"/>
-      <c r="B102" s="56" t="inlineStr">
+      <c r="B102" s="60" t="inlineStr">
         <is>
           <t>collis[].height</t>
         </is>
@@ -23230,31 +23242,31 @@
 IT: In centimetri.</t>
         </is>
       </c>
-      <c r="D102" s="56" t="inlineStr">
+      <c r="D102" s="60" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E102" s="56" t="inlineStr"/>
-      <c r="F102" s="56" t="inlineStr">
+      <c r="E102" s="60" t="inlineStr"/>
+      <c r="F102" s="60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G102" s="56" t="inlineStr">
+      <c r="G102" s="60" t="inlineStr">
         <is>
           <t>spedizione.collo.altezza</t>
         </is>
       </c>
-      <c r="H102" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I102" s="56" t="n">
+      <c r="H102" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I102" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="J102" s="59" t="inlineStr">
+      <c r="J102" s="63" t="inlineStr">
         <is>
           <t>DIRETTO</t>
         </is>
@@ -23264,11 +23276,11 @@
           <t>cm</t>
         </is>
       </c>
-      <c r="L102" s="56" t="inlineStr"/>
+      <c r="L102" s="60" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n"/>
-      <c r="B103" s="56" t="inlineStr">
+      <c r="B103" s="60" t="inlineStr">
         <is>
           <t>collis[].volumetric</t>
         </is>
@@ -23279,25 +23291,25 @@
 IT: Metri cubi.</t>
         </is>
       </c>
-      <c r="D103" s="56" t="inlineStr">
+      <c r="D103" s="60" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E103" s="56" t="inlineStr"/>
-      <c r="F103" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G103" s="56" t="inlineStr">
+      <c r="E103" s="60" t="inlineStr"/>
+      <c r="F103" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G103" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H103" s="56" t="inlineStr"/>
-      <c r="I103" s="56" t="inlineStr"/>
-      <c r="J103" s="58" t="inlineStr">
+      <c r="H103" s="60" t="inlineStr"/>
+      <c r="I103" s="60" t="inlineStr"/>
+      <c r="J103" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -23307,11 +23319,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L103" s="56" t="inlineStr"/>
+      <c r="L103" s="60" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="17" t="n"/>
-      <c r="B104" s="56" t="inlineStr">
+      <c r="B104" s="60" t="inlineStr">
         <is>
           <t>collis[].volumetricWeight</t>
         </is>
@@ -23322,25 +23334,25 @@
 IT: In chilogrammi.</t>
         </is>
       </c>
-      <c r="D104" s="56" t="inlineStr">
+      <c r="D104" s="60" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E104" s="56" t="inlineStr"/>
-      <c r="F104" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G104" s="56" t="inlineStr">
+      <c r="E104" s="60" t="inlineStr"/>
+      <c r="F104" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G104" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H104" s="56" t="inlineStr"/>
-      <c r="I104" s="56" t="inlineStr"/>
-      <c r="J104" s="58" t="inlineStr">
+      <c r="H104" s="60" t="inlineStr"/>
+      <c r="I104" s="60" t="inlineStr"/>
+      <c r="J104" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -23350,11 +23362,11 @@
           <t>Nessun campo ICD</t>
         </is>
       </c>
-      <c r="L104" s="56" t="inlineStr"/>
+      <c r="L104" s="60" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="17" t="n"/>
-      <c r="B105" s="56" t="inlineStr">
+      <c r="B105" s="60" t="inlineStr">
         <is>
           <t>collis[].boxType / boxDimensionCategory / boxId</t>
         </is>
@@ -23365,25 +23377,25 @@
 IT: Forse obsoleti, da discutere.</t>
         </is>
       </c>
-      <c r="D105" s="56" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E105" s="56" t="inlineStr"/>
-      <c r="F105" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G105" s="56" t="inlineStr">
+      <c r="D105" s="60" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E105" s="60" t="inlineStr"/>
+      <c r="F105" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G105" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H105" s="56" t="inlineStr"/>
-      <c r="I105" s="56" t="inlineStr"/>
-      <c r="J105" s="58" t="inlineStr">
+      <c r="H105" s="60" t="inlineStr"/>
+      <c r="I105" s="60" t="inlineStr"/>
+      <c r="J105" s="62" t="inlineStr">
         <is>
           <t>NON MAPPATO</t>
         </is>
@@ -23393,7 +23405,7 @@
           <t>Ignorare</t>
         </is>
       </c>
-      <c r="L105" s="56" t="inlineStr"/>
+      <c r="L105" s="60" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L105"/>
@@ -29544,7 +29556,7 @@
       </c>
       <c r="K171" s="17" t="inlineStr">
         <is>
-          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, W, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
+          <t>Lista APT separata da pipe (proposta 29-Oct): 6 -&gt; APT000910, E -&gt; APT000911, F -&gt; APT000906, M -&gt; APT000907, B -&gt; APT000908, W -&gt; APT000908 (matrice di test SDA, da confermare), Z + pudoID -&gt; APT000947, cashOnDeliveryService presente -&gt; APT000918. APT000945 (multicollo) NON si scrive: lo aggiunge il ms sync. A = spedizione normale. Valori D, 7, T non coperti (DF-21); fuori perimetro: assicurazione, Locker, Uffici Postali</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -42621,7 +42633,7 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" s="17" t="inlineStr">
         <is>
-          <t>Nome del Punto Poste: e' il name di APT000947, obbligatorio non vuoto. Sorgente da chiarire: nel flusso via file RT_30_080 contiene il destinatario effettivo (proposta 29-Oct)</t>
+          <t>Nome del Punto Poste: e' il name di APT000947, obbligatorio non vuoto. Nel flusso via file il nome e' in RT_30_030, opzionale e non garantito (RT_30_080 e' il destinatario effettivo): cosa fare se manca (proposta 29-Oct)</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
